--- a/SQO dry run/djg test SQO BLOE output summary.xlsx
+++ b/SQO dry run/djg test SQO BLOE output summary.xlsx
@@ -1328,7 +1328,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
         <v>33.7531</v>
@@ -3910,7 +3910,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>
@@ -33925,7 +33925,7 @@
         <v>247</v>
       </c>
       <c r="N4" t="n">
-        <v>0.783815126834742</v>
+        <v>0.783909583250663</v>
       </c>
       <c r="O4" t="s">
         <v>20</v>
@@ -34027,7 +34027,7 @@
         <v>247</v>
       </c>
       <c r="N6" t="n">
-        <v>0.146443444492175</v>
+        <v>0.146506415436122</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
@@ -34080,7 +34080,7 @@
         <v>247</v>
       </c>
       <c r="N7" t="n">
-        <v>0.477573181825702</v>
+        <v>0.477636152769649</v>
       </c>
       <c r="O7" t="s">
         <v>20</v>
@@ -34339,7 +34339,7 @@
         <v>247</v>
       </c>
       <c r="N12" t="n">
-        <v>0.135727045992582</v>
+        <v>0.13588447335245</v>
       </c>
       <c r="O12" t="s">
         <v>42</v>
@@ -34390,7 +34390,7 @@
         <v>247</v>
       </c>
       <c r="N13" t="n">
-        <v>0.198812057995999</v>
+        <v>0.198906514411919</v>
       </c>
       <c r="O13" t="s">
         <v>26</v>
@@ -34441,7 +34441,7 @@
         <v>247</v>
       </c>
       <c r="N14" t="n">
-        <v>0.253779978397227</v>
+        <v>0.253842949341174</v>
       </c>
       <c r="O14" t="s">
         <v>26</v>
@@ -34494,7 +34494,7 @@
         <v>247</v>
       </c>
       <c r="N15" t="n">
-        <v>0.638594957380046</v>
+        <v>0.639224666819517</v>
       </c>
       <c r="O15" t="s">
         <v>20</v>
@@ -34596,7 +34596,7 @@
         <v>247</v>
       </c>
       <c r="N17" t="n">
-        <v>0.259151551570071</v>
+        <v>0.259277493457965</v>
       </c>
       <c r="O17" t="s">
         <v>26</v>
@@ -34647,7 +34647,7 @@
         <v>247</v>
       </c>
       <c r="N18" t="n">
-        <v>0.224791974104863</v>
+        <v>0.22485494504881</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -34902,7 +34902,7 @@
         <v>247</v>
       </c>
       <c r="N23" t="n">
-        <v>0.728279567902097</v>
+        <v>0.728342538846044</v>
       </c>
       <c r="O23" t="s">
         <v>20</v>
@@ -35514,7 +35514,7 @@
         <v>247</v>
       </c>
       <c r="N35" t="n">
-        <v>0.196011063596979</v>
+        <v>0.196074034540926</v>
       </c>
       <c r="O35" t="s">
         <v>26</v>
@@ -35667,7 +35667,7 @@
         <v>247</v>
       </c>
       <c r="N38" t="n">
-        <v>0.214536758417583</v>
+        <v>0.214946069553239</v>
       </c>
       <c r="O38" t="s">
         <v>26</v>
@@ -35718,7 +35718,7 @@
         <v>247</v>
       </c>
       <c r="N39" t="n">
-        <v>0.186979603307179</v>
+        <v>0.187011088779152</v>
       </c>
       <c r="O39" t="s">
         <v>26</v>
@@ -35769,7 +35769,7 @@
         <v>247</v>
       </c>
       <c r="N40" t="n">
-        <v>0.214845331709676</v>
+        <v>0.215128700957437</v>
       </c>
       <c r="O40" t="s">
         <v>26</v>
@@ -35922,7 +35922,7 @@
         <v>247</v>
       </c>
       <c r="N43" t="n">
-        <v>0.366293299122094</v>
+        <v>0.366734095729723</v>
       </c>
       <c r="O43" t="s">
         <v>20</v>
@@ -36240,7 +36240,7 @@
         <v>247</v>
       </c>
       <c r="N49" t="n">
-        <v>0.239490238460826</v>
+        <v>0.241347881307264</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
@@ -36293,13 +36293,13 @@
         <v>247</v>
       </c>
       <c r="N50" t="n">
-        <v>0.158136500806268</v>
+        <v>0.160277512900468</v>
       </c>
       <c r="O50" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P50" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="s">
         <v>246</v>
@@ -36501,7 +36501,7 @@
         <v>247</v>
       </c>
       <c r="N54" t="n">
-        <v>0.330229334458456</v>
+        <v>0.33026081993043</v>
       </c>
       <c r="O54" t="s">
         <v>20</v>
@@ -36656,7 +36656,7 @@
         <v>247</v>
       </c>
       <c r="N57" t="n">
-        <v>0.168276792719169</v>
+        <v>0.168308278191142</v>
       </c>
       <c r="O57" t="s">
         <v>26</v>
@@ -36911,7 +36911,7 @@
         <v>247</v>
       </c>
       <c r="N62" t="n">
-        <v>0.104950598898418</v>
+        <v>0.105296939090127</v>
       </c>
       <c r="O62" t="s">
         <v>42</v>
@@ -36962,7 +36962,7 @@
         <v>247</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0723904300215725</v>
+        <v>0.0724219154935461</v>
       </c>
       <c r="O63" t="s">
         <v>38</v>
@@ -37574,7 +37574,7 @@
         <v>247</v>
       </c>
       <c r="N75" t="n">
-        <v>0.524702963892162</v>
+        <v>0.524923362195977</v>
       </c>
       <c r="O75" t="s">
         <v>20</v>
@@ -37982,7 +37982,7 @@
         <v>247</v>
       </c>
       <c r="N83" t="n">
-        <v>0.137229114036872</v>
+        <v>0.137260599508845</v>
       </c>
       <c r="O83" t="s">
         <v>42</v>
@@ -38137,7 +38137,7 @@
         <v>247</v>
       </c>
       <c r="N86" t="n">
-        <v>0.215093626859196</v>
+        <v>0.21512511233117</v>
       </c>
       <c r="O86" t="s">
         <v>26</v>
@@ -38296,7 +38296,7 @@
         <v>247</v>
       </c>
       <c r="N89" t="n">
-        <v>0.103402413575569</v>
+        <v>0.103433899047543</v>
       </c>
       <c r="O89" t="s">
         <v>42</v>
@@ -38349,7 +38349,7 @@
         <v>247</v>
       </c>
       <c r="N90" t="n">
-        <v>0.349267520078283</v>
+        <v>0.349299005550257</v>
       </c>
       <c r="O90" t="s">
         <v>20</v>
@@ -38506,7 +38506,7 @@
         <v>247</v>
       </c>
       <c r="N93" t="n">
-        <v>0.300395550544629</v>
+        <v>0.300427036016602</v>
       </c>
       <c r="O93" t="s">
         <v>20</v>
@@ -38612,7 +38612,7 @@
         <v>247</v>
       </c>
       <c r="N95" t="n">
-        <v>0.210788654012118</v>
+        <v>0.210820139484092</v>
       </c>
       <c r="O95" t="s">
         <v>26</v>
@@ -38665,7 +38665,7 @@
         <v>247</v>
       </c>
       <c r="N96" t="n">
-        <v>0.234494422592932</v>
+        <v>0.234557393536879</v>
       </c>
       <c r="O96" t="s">
         <v>26</v>
@@ -38820,7 +38820,7 @@
         <v>247</v>
       </c>
       <c r="N99" t="n">
-        <v>0.16844947228901</v>
+        <v>0.168480957760984</v>
       </c>
       <c r="O99" t="s">
         <v>26</v>
@@ -38979,7 +38979,7 @@
         <v>247</v>
       </c>
       <c r="N102" t="n">
-        <v>0.192895096977581</v>
+        <v>0.192926582449555</v>
       </c>
       <c r="O102" t="s">
         <v>26</v>
@@ -39136,7 +39136,7 @@
         <v>247</v>
       </c>
       <c r="N105" t="n">
-        <v>0.192046084340278</v>
+        <v>0.192077569812251</v>
       </c>
       <c r="O105" t="s">
         <v>26</v>
@@ -39240,7 +39240,7 @@
         <v>247</v>
       </c>
       <c r="N107" t="n">
-        <v>0.142430048704356</v>
+        <v>0.14246153417633</v>
       </c>
       <c r="O107" t="s">
         <v>42</v>
@@ -39344,7 +39344,7 @@
         <v>247</v>
       </c>
       <c r="N109" t="n">
-        <v>0.134647407795603</v>
+        <v>0.134678893267576</v>
       </c>
       <c r="O109" t="s">
         <v>42</v>
@@ -39497,7 +39497,7 @@
         <v>247</v>
       </c>
       <c r="N112" t="n">
-        <v>0.48675944288504</v>
+        <v>0.487011326660829</v>
       </c>
       <c r="O112" t="s">
         <v>20</v>
@@ -39905,7 +39905,7 @@
         <v>247</v>
       </c>
       <c r="N120" t="n">
-        <v>0.449302909754944</v>
+        <v>0.449491822586785</v>
       </c>
       <c r="O120" t="s">
         <v>20</v>
@@ -41239,7 +41239,7 @@
         <v>247</v>
       </c>
       <c r="N146" t="n">
-        <v>0.0530505857874207</v>
+        <v>0.0531135567313678</v>
       </c>
       <c r="O146" t="s">
         <v>38</v>
@@ -41663,7 +41663,7 @@
         <v>247</v>
       </c>
       <c r="N154" t="n">
-        <v>0.254146143610553</v>
+        <v>0.254177629082527</v>
       </c>
       <c r="O154" t="s">
         <v>26</v>
@@ -42246,7 +42246,7 @@
         <v>247</v>
       </c>
       <c r="N165" t="n">
-        <v>0.433129645799303</v>
+        <v>0.43319261674325</v>
       </c>
       <c r="O165" t="s">
         <v>20</v>
@@ -42352,7 +42352,7 @@
         <v>247</v>
       </c>
       <c r="N167" t="n">
-        <v>0.389858059082601</v>
+        <v>0.39029885569023</v>
       </c>
       <c r="O167" t="s">
         <v>20</v>
@@ -42927,7 +42927,7 @@
         <v>247</v>
       </c>
       <c r="N178" t="n">
-        <v>0.136524704896059</v>
+        <v>0.136619161311979</v>
       </c>
       <c r="O178" t="s">
         <v>42</v>
@@ -42980,7 +42980,7 @@
         <v>247</v>
       </c>
       <c r="N179" t="n">
-        <v>0.172259073151793</v>
+        <v>0.172510956927581</v>
       </c>
       <c r="O179" t="s">
         <v>26</v>
@@ -43033,7 +43033,7 @@
         <v>247</v>
       </c>
       <c r="N180" t="n">
-        <v>0.170327733841888</v>
+        <v>0.170359219313862</v>
       </c>
       <c r="O180" t="s">
         <v>26</v>
@@ -43086,7 +43086,7 @@
         <v>247</v>
       </c>
       <c r="N181" t="n">
-        <v>0.274407862230798</v>
+        <v>0.274974600726321</v>
       </c>
       <c r="O181" t="s">
         <v>20</v>
@@ -43139,7 +43139,7 @@
         <v>247</v>
       </c>
       <c r="N182" t="n">
-        <v>0.383594451381829</v>
+        <v>0.383751878741697</v>
       </c>
       <c r="O182" t="s">
         <v>20</v>
@@ -43192,7 +43192,7 @@
         <v>247</v>
       </c>
       <c r="N183" t="n">
-        <v>0.0722966278492255</v>
+        <v>0.0730837646485635</v>
       </c>
       <c r="O183" t="s">
         <v>38</v>
@@ -43349,7 +43349,7 @@
         <v>247</v>
       </c>
       <c r="N186" t="n">
-        <v>0.260383337744749</v>
+        <v>0.260698192464484</v>
       </c>
       <c r="O186" t="s">
         <v>26</v>
@@ -43453,7 +43453,7 @@
         <v>247</v>
       </c>
       <c r="N188" t="n">
-        <v>0.3142484359757</v>
+        <v>0.314279921447674</v>
       </c>
       <c r="O188" t="s">
         <v>20</v>
@@ -43504,7 +43504,7 @@
         <v>247</v>
       </c>
       <c r="N189" t="n">
-        <v>0.164890069214232</v>
+        <v>0.164921554686205</v>
       </c>
       <c r="O189" t="s">
         <v>26</v>
@@ -43555,7 +43555,7 @@
         <v>247</v>
       </c>
       <c r="N190" t="n">
-        <v>0.270786153664888</v>
+        <v>0.273619846142505</v>
       </c>
       <c r="O190" t="s">
         <v>20</v>
@@ -43814,7 +43814,7 @@
         <v>247</v>
       </c>
       <c r="N195" t="n">
-        <v>0.162477773204947</v>
+        <v>0.162603715092841</v>
       </c>
       <c r="O195" t="s">
         <v>26</v>
@@ -44555,13 +44555,13 @@
         <v>248</v>
       </c>
       <c r="N5" t="n">
-        <v>1.3656</v>
+        <v>1.2139</v>
       </c>
       <c r="O5" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q5"/>
     </row>
@@ -44904,7 +44904,7 @@
         <v>248</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4744</v>
+        <v>0.4405</v>
       </c>
       <c r="O12" t="s">
         <v>42</v>
@@ -46425,7 +46425,7 @@
         <v>248</v>
       </c>
       <c r="N43" t="n">
-        <v>1.1458</v>
+        <v>0.8594</v>
       </c>
       <c r="O43" t="s">
         <v>26</v>
@@ -52854,7 +52854,7 @@
         <v>248</v>
       </c>
       <c r="N172" t="n">
-        <v>0.6562</v>
+        <v>0.6093</v>
       </c>
       <c r="O172" t="s">
         <v>42</v>
@@ -54651,7 +54651,7 @@
         <v>1</v>
       </c>
       <c r="I3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J3"/>
       <c r="K3"/>
@@ -57363,7 +57363,7 @@
         <v>2</v>
       </c>
       <c r="H48" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I48" t="n">
         <v>3</v>

--- a/SQO dry run/djg test SQO BLOE output summary.xlsx
+++ b/SQO dry run/djg test SQO BLOE output summary.xlsx
@@ -2632,10 +2632,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -2644,7 +2644,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
@@ -3211,7 +3211,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -5625,7 +5625,7 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
@@ -8679,7 +8679,7 @@
         <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
         <v>2</v>
@@ -9024,7 +9024,7 @@
         <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
         <v>2</v>
@@ -9316,7 +9316,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
         <v>3</v>
@@ -9431,7 +9431,7 @@
         <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
         <v>4</v>
@@ -9963,7 +9963,7 @@
         <v>2</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -10069,13 +10069,13 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G155" t="n">
         <v>2</v>
@@ -11780,7 +11780,7 @@
         <v>2</v>
       </c>
       <c r="H184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>3</v>
@@ -12006,7 +12006,7 @@
         <v>26</v>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>2</v>
@@ -13128,7 +13128,7 @@
         <v>242</v>
       </c>
       <c r="N3" t="n">
-        <v>15.0835121731415</v>
+        <v>15.0836032595324</v>
       </c>
       <c r="O3" t="s">
         <v>20</v>
@@ -13177,7 +13177,7 @@
         <v>242</v>
       </c>
       <c r="N4" t="n">
-        <v>12.1137966502506</v>
+        <v>11.8483309845804</v>
       </c>
       <c r="O4" t="s">
         <v>20</v>
@@ -13226,7 +13226,7 @@
         <v>242</v>
       </c>
       <c r="N5" t="n">
-        <v>13.9117533415191</v>
+        <v>14.9581463094241</v>
       </c>
       <c r="O5" t="s">
         <v>20</v>
@@ -13275,7 +13275,7 @@
         <v>242</v>
       </c>
       <c r="N6" t="n">
-        <v>14.2984796995644</v>
+        <v>14.2996494693632</v>
       </c>
       <c r="O6" t="s">
         <v>20</v>
@@ -13326,7 +13326,7 @@
         <v>242</v>
       </c>
       <c r="N7" t="n">
-        <v>12.5256070876902</v>
+        <v>12.9304384921341</v>
       </c>
       <c r="O7" t="s">
         <v>20</v>
@@ -13375,7 +13375,7 @@
         <v>242</v>
       </c>
       <c r="N8" t="n">
-        <v>8.32587934085862</v>
+        <v>8.6039757528745</v>
       </c>
       <c r="O8" t="s">
         <v>20</v>
@@ -13426,7 +13426,7 @@
         <v>242</v>
       </c>
       <c r="N9" t="n">
-        <v>8.3297123292416</v>
+        <v>8.33034038326227</v>
       </c>
       <c r="O9" t="s">
         <v>20</v>
@@ -13475,7 +13475,7 @@
         <v>242</v>
       </c>
       <c r="N10" t="n">
-        <v>6.89794102129035</v>
+        <v>8.71087727574399</v>
       </c>
       <c r="O10" t="s">
         <v>20</v>
@@ -13524,7 +13524,7 @@
         <v>242</v>
       </c>
       <c r="N11" t="n">
-        <v>7.13429758410547</v>
+        <v>9.7956661477616</v>
       </c>
       <c r="O11" t="s">
         <v>20</v>
@@ -13575,7 +13575,7 @@
         <v>242</v>
       </c>
       <c r="N12" t="n">
-        <v>9.40947000478344</v>
+        <v>9.40985735776787</v>
       </c>
       <c r="O12" t="s">
         <v>20</v>
@@ -13624,7 +13624,7 @@
         <v>242</v>
       </c>
       <c r="N13" t="n">
-        <v>9.02482959811105</v>
+        <v>11.1803875811964</v>
       </c>
       <c r="O13" t="s">
         <v>20</v>
@@ -13673,7 +13673,7 @@
         <v>242</v>
       </c>
       <c r="N14" t="n">
-        <v>13.4161053559657</v>
+        <v>12.3372551759701</v>
       </c>
       <c r="O14" t="s">
         <v>20</v>
@@ -13724,7 +13724,7 @@
         <v>242</v>
       </c>
       <c r="N15" t="n">
-        <v>25.1492945972641</v>
+        <v>25.3364034931308</v>
       </c>
       <c r="O15" t="s">
         <v>20</v>
@@ -13773,7 +13773,7 @@
         <v>242</v>
       </c>
       <c r="N16" t="n">
-        <v>32.7883730254763</v>
+        <v>32.7913138150571</v>
       </c>
       <c r="O16" t="s">
         <v>20</v>
@@ -13822,7 +13822,7 @@
         <v>242</v>
       </c>
       <c r="N17" t="n">
-        <v>36.350454212711</v>
+        <v>33.9697703600652</v>
       </c>
       <c r="O17" t="s">
         <v>20</v>
@@ -13871,7 +13871,7 @@
         <v>242</v>
       </c>
       <c r="N18" t="n">
-        <v>42.407445046611</v>
+        <v>42.4469265154747</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -13920,7 +13920,7 @@
         <v>242</v>
       </c>
       <c r="N19" t="n">
-        <v>26.5993771057528</v>
+        <v>26.7370411270221</v>
       </c>
       <c r="O19" t="s">
         <v>20</v>
@@ -13969,7 +13969,7 @@
         <v>242</v>
       </c>
       <c r="N20" t="n">
-        <v>17.8454048383822</v>
+        <v>21.0239865128028</v>
       </c>
       <c r="O20" t="s">
         <v>20</v>
@@ -14018,7 +14018,7 @@
         <v>242</v>
       </c>
       <c r="N21" t="n">
-        <v>32.0488155283212</v>
+        <v>32.2459417423192</v>
       </c>
       <c r="O21" t="s">
         <v>20</v>
@@ -14067,7 +14067,7 @@
         <v>242</v>
       </c>
       <c r="N22" t="n">
-        <v>18.7435227586434</v>
+        <v>21.5044390504018</v>
       </c>
       <c r="O22" t="s">
         <v>20</v>
@@ -14116,7 +14116,7 @@
         <v>242</v>
       </c>
       <c r="N23" t="n">
-        <v>22.8819283339274</v>
+        <v>26.6014204428507</v>
       </c>
       <c r="O23" t="s">
         <v>20</v>
@@ -14165,7 +14165,7 @@
         <v>242</v>
       </c>
       <c r="N24" t="n">
-        <v>34.7453661386161</v>
+        <v>34.4437640570911</v>
       </c>
       <c r="O24" t="s">
         <v>20</v>
@@ -14214,7 +14214,7 @@
         <v>242</v>
       </c>
       <c r="N25" t="n">
-        <v>27.2582157948085</v>
+        <v>27.2610128313953</v>
       </c>
       <c r="O25" t="s">
         <v>20</v>
@@ -14263,7 +14263,7 @@
         <v>242</v>
       </c>
       <c r="N26" t="n">
-        <v>33.3987902247781</v>
+        <v>32.5280831150206</v>
       </c>
       <c r="O26" t="s">
         <v>20</v>
@@ -14312,7 +14312,7 @@
         <v>242</v>
       </c>
       <c r="N27" t="n">
-        <v>44.9967123841401</v>
+        <v>45.0007456972099</v>
       </c>
       <c r="O27" t="s">
         <v>26</v>
@@ -14361,7 +14361,7 @@
         <v>242</v>
       </c>
       <c r="N28" t="n">
-        <v>24.062074209176</v>
+        <v>21.5154834181272</v>
       </c>
       <c r="O28" t="s">
         <v>20</v>
@@ -14410,7 +14410,7 @@
         <v>242</v>
       </c>
       <c r="N29" t="n">
-        <v>42.3141744493955</v>
+        <v>42.0953502737836</v>
       </c>
       <c r="O29" t="s">
         <v>26</v>
@@ -14459,7 +14459,7 @@
         <v>242</v>
       </c>
       <c r="N30" t="n">
-        <v>37.3861784606946</v>
+        <v>37.1629962032474</v>
       </c>
       <c r="O30" t="s">
         <v>20</v>
@@ -14508,7 +14508,7 @@
         <v>242</v>
       </c>
       <c r="N31" t="n">
-        <v>47.2595503811971</v>
+        <v>47.2634331434995</v>
       </c>
       <c r="O31" t="s">
         <v>26</v>
@@ -14557,7 +14557,7 @@
         <v>242</v>
       </c>
       <c r="N32" t="n">
-        <v>44.8646018075336</v>
+        <v>44.8694650103138</v>
       </c>
       <c r="O32" t="s">
         <v>26</v>
@@ -14606,7 +14606,7 @@
         <v>242</v>
       </c>
       <c r="N33" t="n">
-        <v>43.5472187847445</v>
+        <v>43.5512192647488</v>
       </c>
       <c r="O33" t="s">
         <v>26</v>
@@ -14655,7 +14655,7 @@
         <v>242</v>
       </c>
       <c r="N34" t="n">
-        <v>50.968570704329</v>
+        <v>50.550905851502</v>
       </c>
       <c r="O34" t="s">
         <v>42</v>
@@ -14704,7 +14704,7 @@
         <v>242</v>
       </c>
       <c r="N35" t="n">
-        <v>32.243751427066</v>
+        <v>32.1763609084533</v>
       </c>
       <c r="O35" t="s">
         <v>20</v>
@@ -14753,7 +14753,7 @@
         <v>242</v>
       </c>
       <c r="N36" t="n">
-        <v>55.8141715934328</v>
+        <v>57.4863757949222</v>
       </c>
       <c r="O36" t="s">
         <v>42</v>
@@ -14802,7 +14802,7 @@
         <v>242</v>
       </c>
       <c r="N37" t="n">
-        <v>44.2308941636457</v>
+        <v>43.7748376827739</v>
       </c>
       <c r="O37" t="s">
         <v>26</v>
@@ -14851,7 +14851,7 @@
         <v>242</v>
       </c>
       <c r="N38" t="n">
-        <v>39.5021026403308</v>
+        <v>36.0283921978724</v>
       </c>
       <c r="O38" t="s">
         <v>20</v>
@@ -14900,7 +14900,7 @@
         <v>242</v>
       </c>
       <c r="N39" t="n">
-        <v>45.7559329178156</v>
+        <v>46.2484492144239</v>
       </c>
       <c r="O39" t="s">
         <v>26</v>
@@ -14949,7 +14949,7 @@
         <v>242</v>
       </c>
       <c r="N40" t="n">
-        <v>34.480188689579</v>
+        <v>31.1032825790809</v>
       </c>
       <c r="O40" t="s">
         <v>20</v>
@@ -14998,7 +14998,7 @@
         <v>242</v>
       </c>
       <c r="N41" t="n">
-        <v>58.0793879941918</v>
+        <v>58.0832165471716</v>
       </c>
       <c r="O41" t="s">
         <v>42</v>
@@ -15047,7 +15047,7 @@
         <v>242</v>
       </c>
       <c r="N42" t="n">
-        <v>60.9540669023094</v>
+        <v>60.9581009717345</v>
       </c>
       <c r="O42" t="s">
         <v>42</v>
@@ -15096,7 +15096,7 @@
         <v>242</v>
       </c>
       <c r="N43" t="n">
-        <v>32.77020951736</v>
+        <v>32.7738773952884</v>
       </c>
       <c r="O43" t="s">
         <v>20</v>
@@ -15147,7 +15147,7 @@
         <v>242</v>
       </c>
       <c r="N44" t="n">
-        <v>51.8263386730003</v>
+        <v>51.8313447398407</v>
       </c>
       <c r="O44" t="s">
         <v>42</v>
@@ -15198,7 +15198,7 @@
         <v>242</v>
       </c>
       <c r="N45" t="n">
-        <v>60.3555344134806</v>
+        <v>60.3613581672103</v>
       </c>
       <c r="O45" t="s">
         <v>42</v>
@@ -15249,7 +15249,7 @@
         <v>242</v>
       </c>
       <c r="N46" t="n">
-        <v>58.5727683598368</v>
+        <v>58.5769595569426</v>
       </c>
       <c r="O46" t="s">
         <v>42</v>
@@ -15300,7 +15300,7 @@
         <v>242</v>
       </c>
       <c r="N47" t="n">
-        <v>34.6166210092699</v>
+        <v>34.3151407398848</v>
       </c>
       <c r="O47" t="s">
         <v>20</v>
@@ -15351,7 +15351,7 @@
         <v>242</v>
       </c>
       <c r="N48" t="n">
-        <v>34.7825054167021</v>
+        <v>34.4495839027007</v>
       </c>
       <c r="O48" t="s">
         <v>20</v>
@@ -15402,7 +15402,7 @@
         <v>242</v>
       </c>
       <c r="N49" t="n">
-        <v>44.0357694849263</v>
+        <v>44.0394315292482</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
@@ -15453,7 +15453,7 @@
         <v>242</v>
       </c>
       <c r="N50" t="n">
-        <v>54.2386015325113</v>
+        <v>54.593701476202</v>
       </c>
       <c r="O50" t="s">
         <v>42</v>
@@ -15504,7 +15504,7 @@
         <v>242</v>
       </c>
       <c r="N51" t="n">
-        <v>35.8847263538009</v>
+        <v>35.2484843681082</v>
       </c>
       <c r="O51" t="s">
         <v>20</v>
@@ -15553,7 +15553,7 @@
         <v>242</v>
       </c>
       <c r="N52" t="n">
-        <v>36.2158303405904</v>
+        <v>38.5797223342776</v>
       </c>
       <c r="O52" t="s">
         <v>20</v>
@@ -15602,7 +15602,7 @@
         <v>242</v>
       </c>
       <c r="N53" t="n">
-        <v>33.8497968767349</v>
+        <v>33.7706148627681</v>
       </c>
       <c r="O53" t="s">
         <v>20</v>
@@ -15653,7 +15653,7 @@
         <v>242</v>
       </c>
       <c r="N54" t="n">
-        <v>40.8734564870964</v>
+        <v>41.1151784188755</v>
       </c>
       <c r="O54" t="s">
         <v>26</v>
@@ -15704,7 +15704,7 @@
         <v>242</v>
       </c>
       <c r="N55" t="n">
-        <v>57.6523819222388</v>
+        <v>57.6570724356769</v>
       </c>
       <c r="O55" t="s">
         <v>42</v>
@@ -15753,7 +15753,7 @@
         <v>242</v>
       </c>
       <c r="N56" t="n">
-        <v>51.7196535149094</v>
+        <v>51.7245077283966</v>
       </c>
       <c r="O56" t="s">
         <v>42</v>
@@ -15802,7 +15802,7 @@
         <v>242</v>
       </c>
       <c r="N57" t="n">
-        <v>43.9226507179291</v>
+        <v>44.2645082796971</v>
       </c>
       <c r="O57" t="s">
         <v>26</v>
@@ -15851,7 +15851,7 @@
         <v>242</v>
       </c>
       <c r="N58" t="n">
-        <v>49.8113383496228</v>
+        <v>49.2997982397531</v>
       </c>
       <c r="O58" t="s">
         <v>42</v>
@@ -15900,7 +15900,7 @@
         <v>242</v>
       </c>
       <c r="N59" t="n">
-        <v>36.4369680986238</v>
+        <v>36.161433812764</v>
       </c>
       <c r="O59" t="s">
         <v>20</v>
@@ -15949,7 +15949,7 @@
         <v>242</v>
       </c>
       <c r="N60" t="n">
-        <v>55.111627776202</v>
+        <v>55.1159647984134</v>
       </c>
       <c r="O60" t="s">
         <v>42</v>
@@ -15998,7 +15998,7 @@
         <v>242</v>
       </c>
       <c r="N61" t="n">
-        <v>26.354523282968</v>
+        <v>24.1729318414282</v>
       </c>
       <c r="O61" t="s">
         <v>20</v>
@@ -16047,7 +16047,7 @@
         <v>242</v>
       </c>
       <c r="N62" t="n">
-        <v>46.8685468193033</v>
+        <v>46.8718604742481</v>
       </c>
       <c r="O62" t="s">
         <v>26</v>
@@ -16096,7 +16096,7 @@
         <v>242</v>
       </c>
       <c r="N63" t="n">
-        <v>57.355496186753</v>
+        <v>57.8461293200658</v>
       </c>
       <c r="O63" t="s">
         <v>42</v>
@@ -16145,7 +16145,7 @@
         <v>242</v>
       </c>
       <c r="N64" t="n">
-        <v>61.4518235110778</v>
+        <v>62.6880989195223</v>
       </c>
       <c r="O64" t="s">
         <v>42</v>
@@ -16194,7 +16194,7 @@
         <v>242</v>
       </c>
       <c r="N65" t="n">
-        <v>37.8216472178391</v>
+        <v>37.8755232951499</v>
       </c>
       <c r="O65" t="s">
         <v>20</v>
@@ -16243,7 +16243,7 @@
         <v>242</v>
       </c>
       <c r="N66" t="n">
-        <v>37.8850192357862</v>
+        <v>37.1326695672326</v>
       </c>
       <c r="O66" t="s">
         <v>20</v>
@@ -16292,7 +16292,7 @@
         <v>242</v>
       </c>
       <c r="N67" t="n">
-        <v>33.7332198823278</v>
+        <v>33.640809042433</v>
       </c>
       <c r="O67" t="s">
         <v>20</v>
@@ -16341,7 +16341,7 @@
         <v>242</v>
       </c>
       <c r="N68" t="n">
-        <v>32.6005197925927</v>
+        <v>32.6033919720096</v>
       </c>
       <c r="O68" t="s">
         <v>20</v>
@@ -16390,7 +16390,7 @@
         <v>242</v>
       </c>
       <c r="N69" t="n">
-        <v>48.6600414375087</v>
+        <v>47.9152613664558</v>
       </c>
       <c r="O69" t="s">
         <v>26</v>
@@ -16439,7 +16439,7 @@
         <v>242</v>
       </c>
       <c r="N70" t="n">
-        <v>39.3004160993685</v>
+        <v>37.4402703602602</v>
       </c>
       <c r="O70" t="s">
         <v>20</v>
@@ -16488,7 +16488,7 @@
         <v>242</v>
       </c>
       <c r="N71" t="n">
-        <v>34.2786035957176</v>
+        <v>34.2825329082141</v>
       </c>
       <c r="O71" t="s">
         <v>20</v>
@@ -16537,7 +16537,7 @@
         <v>242</v>
       </c>
       <c r="N72" t="n">
-        <v>31.3191146996047</v>
+        <v>31.2955291311754</v>
       </c>
       <c r="O72" t="s">
         <v>20</v>
@@ -16586,7 +16586,7 @@
         <v>242</v>
       </c>
       <c r="N73" t="n">
-        <v>37.741279233437</v>
+        <v>37.7445607249094</v>
       </c>
       <c r="O73" t="s">
         <v>20</v>
@@ -16635,7 +16635,7 @@
         <v>242</v>
       </c>
       <c r="N74" t="n">
-        <v>35.084232763802</v>
+        <v>33.9284286782615</v>
       </c>
       <c r="O74" t="s">
         <v>20</v>
@@ -16684,7 +16684,7 @@
         <v>242</v>
       </c>
       <c r="N75" t="n">
-        <v>40.569624719579</v>
+        <v>40.3290087302363</v>
       </c>
       <c r="O75" t="s">
         <v>26</v>
@@ -16733,7 +16733,7 @@
         <v>242</v>
       </c>
       <c r="N76" t="n">
-        <v>40.0247396797661</v>
+        <v>40.6459863739937</v>
       </c>
       <c r="O76" t="s">
         <v>26</v>
@@ -16782,7 +16782,7 @@
         <v>242</v>
       </c>
       <c r="N77" t="n">
-        <v>50.7645465283262</v>
+        <v>49.7426953088351</v>
       </c>
       <c r="O77" t="s">
         <v>42</v>
@@ -16831,7 +16831,7 @@
         <v>242</v>
       </c>
       <c r="N78" t="n">
-        <v>53.0902871170182</v>
+        <v>53.5737911776543</v>
       </c>
       <c r="O78" t="s">
         <v>42</v>
@@ -16880,7 +16880,7 @@
         <v>242</v>
       </c>
       <c r="N79" t="n">
-        <v>52.270352748859</v>
+        <v>53.0463318602157</v>
       </c>
       <c r="O79" t="s">
         <v>42</v>
@@ -16929,7 +16929,7 @@
         <v>242</v>
       </c>
       <c r="N80" t="n">
-        <v>48.0404053013533</v>
+        <v>48.6449093133248</v>
       </c>
       <c r="O80" t="s">
         <v>26</v>
@@ -16978,7 +16978,7 @@
         <v>242</v>
       </c>
       <c r="N81" t="n">
-        <v>31.8375</v>
+        <v>31.8428644411</v>
       </c>
       <c r="O81" t="s">
         <v>20</v>
@@ -17027,7 +17027,7 @@
         <v>242</v>
       </c>
       <c r="N82" t="n">
-        <v>58.87137976088</v>
+        <v>58.876742472547</v>
       </c>
       <c r="O82" t="s">
         <v>42</v>
@@ -17076,7 +17076,7 @@
         <v>242</v>
       </c>
       <c r="N83" t="n">
-        <v>57.2921486848901</v>
+        <v>56.2859324071618</v>
       </c>
       <c r="O83" t="s">
         <v>42</v>
@@ -17125,7 +17125,7 @@
         <v>242</v>
       </c>
       <c r="N84" t="n">
-        <v>52.9357739141486</v>
+        <v>52.5511471646297</v>
       </c>
       <c r="O84" t="s">
         <v>42</v>
@@ -17174,7 +17174,7 @@
         <v>242</v>
       </c>
       <c r="N85" t="n">
-        <v>43.1207280752279</v>
+        <v>43.1252283222651</v>
       </c>
       <c r="O85" t="s">
         <v>26</v>
@@ -17225,7 +17225,7 @@
         <v>242</v>
       </c>
       <c r="N86" t="n">
-        <v>23.1899768146899</v>
+        <v>23.1922086297616</v>
       </c>
       <c r="O86" t="s">
         <v>20</v>
@@ -17276,7 +17276,7 @@
         <v>242</v>
       </c>
       <c r="N87" t="n">
-        <v>31.9036720933467</v>
+        <v>31.9065688221437</v>
       </c>
       <c r="O87" t="s">
         <v>20</v>
@@ -17327,7 +17327,7 @@
         <v>242</v>
       </c>
       <c r="N88" t="n">
-        <v>11.2064495439365</v>
+        <v>13.270951521794</v>
       </c>
       <c r="O88" t="s">
         <v>20</v>
@@ -17378,7 +17378,7 @@
         <v>242</v>
       </c>
       <c r="N89" t="n">
-        <v>31.3956585433204</v>
+        <v>31.3979309943615</v>
       </c>
       <c r="O89" t="s">
         <v>20</v>
@@ -17429,7 +17429,7 @@
         <v>242</v>
       </c>
       <c r="N90" t="n">
-        <v>24.5549195255789</v>
+        <v>24.5572040188634</v>
       </c>
       <c r="O90" t="s">
         <v>20</v>
@@ -17478,7 +17478,7 @@
         <v>242</v>
       </c>
       <c r="N91" t="n">
-        <v>12.1942230028456</v>
+        <v>12.1961031744486</v>
       </c>
       <c r="O91" t="s">
         <v>20</v>
@@ -17529,7 +17529,7 @@
         <v>242</v>
       </c>
       <c r="N92" t="n">
-        <v>10.1692205962436</v>
+        <v>10.1705453968361</v>
       </c>
       <c r="O92" t="s">
         <v>20</v>
@@ -17580,7 +17580,7 @@
         <v>242</v>
       </c>
       <c r="N93" t="n">
-        <v>4.86165972694654</v>
+        <v>4.78397879213011</v>
       </c>
       <c r="O93" t="s">
         <v>20</v>
@@ -17631,7 +17631,7 @@
         <v>242</v>
       </c>
       <c r="N94" t="n">
-        <v>16.3825449000804</v>
+        <v>17.9115639941559</v>
       </c>
       <c r="O94" t="s">
         <v>20</v>
@@ -17682,7 +17682,7 @@
         <v>242</v>
       </c>
       <c r="N95" t="n">
-        <v>16.4384752895061</v>
+        <v>17.5891857612011</v>
       </c>
       <c r="O95" t="s">
         <v>20</v>
@@ -17733,7 +17733,7 @@
         <v>242</v>
       </c>
       <c r="N96" t="n">
-        <v>11.6011179093738</v>
+        <v>13.6005680792401</v>
       </c>
       <c r="O96" t="s">
         <v>20</v>
@@ -17782,7 +17782,7 @@
         <v>242</v>
       </c>
       <c r="N97" t="n">
-        <v>7.54409449147013</v>
+        <v>7.66273193633289</v>
       </c>
       <c r="O97" t="s">
         <v>20</v>
@@ -17831,7 +17831,7 @@
         <v>242</v>
       </c>
       <c r="N98" t="n">
-        <v>13.0743521518572</v>
+        <v>13.0752456213904</v>
       </c>
       <c r="O98" t="s">
         <v>20</v>
@@ -17882,7 +17882,7 @@
         <v>242</v>
       </c>
       <c r="N99" t="n">
-        <v>9.84978070834879</v>
+        <v>9.85051761058418</v>
       </c>
       <c r="O99" t="s">
         <v>20</v>
@@ -17933,7 +17933,7 @@
         <v>242</v>
       </c>
       <c r="N100" t="n">
-        <v>34.6138399416805</v>
+        <v>34.6184031988465</v>
       </c>
       <c r="O100" t="s">
         <v>20</v>
@@ -17984,7 +17984,7 @@
         <v>242</v>
       </c>
       <c r="N101" t="n">
-        <v>46.5557479907775</v>
+        <v>46.5596212264505</v>
       </c>
       <c r="O101" t="s">
         <v>26</v>
@@ -18035,7 +18035,7 @@
         <v>242</v>
       </c>
       <c r="N102" t="n">
-        <v>2.14466680647164</v>
+        <v>2.14420429605779</v>
       </c>
       <c r="O102" t="s">
         <v>20</v>
@@ -18086,7 +18086,7 @@
         <v>242</v>
       </c>
       <c r="N103" t="n">
-        <v>1.98262451009629</v>
+        <v>1.32081676762569</v>
       </c>
       <c r="O103" t="s">
         <v>20</v>
@@ -18135,7 +18135,7 @@
         <v>242</v>
       </c>
       <c r="N104" t="n">
-        <v>11.6191894602328</v>
+        <v>11.6202773536615</v>
       </c>
       <c r="O104" t="s">
         <v>20</v>
@@ -18186,7 +18186,7 @@
         <v>242</v>
       </c>
       <c r="N105" t="n">
-        <v>10.3387676701061</v>
+        <v>11.6383482184709</v>
       </c>
       <c r="O105" t="s">
         <v>20</v>
@@ -18235,7 +18235,7 @@
         <v>242</v>
       </c>
       <c r="N106" t="n">
-        <v>9.38646772240299</v>
+        <v>9.38811959642256</v>
       </c>
       <c r="O106" t="s">
         <v>20</v>
@@ -18286,7 +18286,7 @@
         <v>242</v>
       </c>
       <c r="N107" t="n">
-        <v>4.80542773699556</v>
+        <v>8.16961064333156</v>
       </c>
       <c r="O107" t="s">
         <v>20</v>
@@ -18337,7 +18337,7 @@
         <v>242</v>
       </c>
       <c r="N108" t="n">
-        <v>10.1747537747187</v>
+        <v>12.1040470010412</v>
       </c>
       <c r="O108" t="s">
         <v>20</v>
@@ -18386,7 +18386,7 @@
         <v>242</v>
       </c>
       <c r="N109" t="n">
-        <v>31.1211257581424</v>
+        <v>30.6644086042866</v>
       </c>
       <c r="O109" t="s">
         <v>20</v>
@@ -18435,7 +18435,7 @@
         <v>242</v>
       </c>
       <c r="N110" t="n">
-        <v>47.1897965528831</v>
+        <v>46.6256547683002</v>
       </c>
       <c r="O110" t="s">
         <v>26</v>
@@ -18484,7 +18484,7 @@
         <v>242</v>
       </c>
       <c r="N111" t="n">
-        <v>36.1227151646562</v>
+        <v>35.8360658033654</v>
       </c>
       <c r="O111" t="s">
         <v>20</v>
@@ -18533,7 +18533,7 @@
         <v>242</v>
       </c>
       <c r="N112" t="n">
-        <v>42.5421191400731</v>
+        <v>44.7565103451307</v>
       </c>
       <c r="O112" t="s">
         <v>26</v>
@@ -18582,7 +18582,7 @@
         <v>242</v>
       </c>
       <c r="N113" t="n">
-        <v>43.8461235237061</v>
+        <v>42.7624117274131</v>
       </c>
       <c r="O113" t="s">
         <v>26</v>
@@ -18631,7 +18631,7 @@
         <v>242</v>
       </c>
       <c r="N114" t="n">
-        <v>27.3189987855729</v>
+        <v>27.5299886947659</v>
       </c>
       <c r="O114" t="s">
         <v>20</v>
@@ -18680,7 +18680,7 @@
         <v>242</v>
       </c>
       <c r="N115" t="n">
-        <v>21.5284937020595</v>
+        <v>20.6405849047233</v>
       </c>
       <c r="O115" t="s">
         <v>20</v>
@@ -18729,7 +18729,7 @@
         <v>242</v>
       </c>
       <c r="N116" t="n">
-        <v>48.2853416352102</v>
+        <v>47.4585847681724</v>
       </c>
       <c r="O116" t="s">
         <v>26</v>
@@ -18778,7 +18778,7 @@
         <v>242</v>
       </c>
       <c r="N117" t="n">
-        <v>24.6906614267598</v>
+        <v>23.8355136573165</v>
       </c>
       <c r="O117" t="s">
         <v>20</v>
@@ -18827,7 +18827,7 @@
         <v>242</v>
       </c>
       <c r="N118" t="n">
-        <v>36.2570045434227</v>
+        <v>37.7801970738236</v>
       </c>
       <c r="O118" t="s">
         <v>20</v>
@@ -18876,7 +18876,7 @@
         <v>242</v>
       </c>
       <c r="N119" t="n">
-        <v>21.4965155439</v>
+        <v>21.4978404899989</v>
       </c>
       <c r="O119" t="s">
         <v>20</v>
@@ -18925,7 +18925,7 @@
         <v>242</v>
       </c>
       <c r="N120" t="n">
-        <v>46.1964999441301</v>
+        <v>46.2000741490114</v>
       </c>
       <c r="O120" t="s">
         <v>26</v>
@@ -18974,7 +18974,7 @@
         <v>242</v>
       </c>
       <c r="N121" t="n">
-        <v>66.6622743885865</v>
+        <v>66.6661098221637</v>
       </c>
       <c r="O121" t="s">
         <v>42</v>
@@ -19023,7 +19023,7 @@
         <v>242</v>
       </c>
       <c r="N122" t="n">
-        <v>57.0222130349308</v>
+        <v>57.026510365107</v>
       </c>
       <c r="O122" t="s">
         <v>42</v>
@@ -19072,7 +19072,7 @@
         <v>242</v>
       </c>
       <c r="N123" t="n">
-        <v>47.1882343413431</v>
+        <v>48.3906204338871</v>
       </c>
       <c r="O123" t="s">
         <v>26</v>
@@ -19121,7 +19121,7 @@
         <v>242</v>
       </c>
       <c r="N124" t="n">
-        <v>47.8482770760628</v>
+        <v>47.852521720281</v>
       </c>
       <c r="O124" t="s">
         <v>26</v>
@@ -19170,7 +19170,7 @@
         <v>242</v>
       </c>
       <c r="N125" t="n">
-        <v>64.0805893132035</v>
+        <v>64.0849572302475</v>
       </c>
       <c r="O125" t="s">
         <v>42</v>
@@ -19219,7 +19219,7 @@
         <v>242</v>
       </c>
       <c r="N126" t="n">
-        <v>38.425469626862</v>
+        <v>38.429474379491</v>
       </c>
       <c r="O126" t="s">
         <v>20</v>
@@ -19268,7 +19268,7 @@
         <v>242</v>
       </c>
       <c r="N127" t="n">
-        <v>41.3274729396881</v>
+        <v>41.3310423144838</v>
       </c>
       <c r="O127" t="s">
         <v>26</v>
@@ -19317,7 +19317,7 @@
         <v>242</v>
       </c>
       <c r="N128" t="n">
-        <v>44.2985559045416</v>
+        <v>44.3034349249428</v>
       </c>
       <c r="O128" t="s">
         <v>26</v>
@@ -19366,7 +19366,7 @@
         <v>242</v>
       </c>
       <c r="N129" t="n">
-        <v>40.4725794243005</v>
+        <v>40.8727281383874</v>
       </c>
       <c r="O129" t="s">
         <v>26</v>
@@ -19415,7 +19415,7 @@
         <v>242</v>
       </c>
       <c r="N130" t="n">
-        <v>40.3502360309018</v>
+        <v>41.9807099288077</v>
       </c>
       <c r="O130" t="s">
         <v>26</v>
@@ -19464,7 +19464,7 @@
         <v>242</v>
       </c>
       <c r="N131" t="n">
-        <v>44.6572184297854</v>
+        <v>44.6615340709059</v>
       </c>
       <c r="O131" t="s">
         <v>26</v>
@@ -19513,7 +19513,7 @@
         <v>242</v>
       </c>
       <c r="N132" t="n">
-        <v>45.3330176218466</v>
+        <v>45.3376123556685</v>
       </c>
       <c r="O132" t="s">
         <v>26</v>
@@ -19562,13 +19562,13 @@
         <v>242</v>
       </c>
       <c r="N133" t="n">
-        <v>49.8333351317402</v>
+        <v>48.9228614521441</v>
       </c>
       <c r="O133" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P133" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q133"/>
     </row>
@@ -19611,7 +19611,7 @@
         <v>242</v>
       </c>
       <c r="N134" t="n">
-        <v>52.2772886396889</v>
+        <v>51.4091444274823</v>
       </c>
       <c r="O134" t="s">
         <v>42</v>
@@ -19660,7 +19660,7 @@
         <v>242</v>
       </c>
       <c r="N135" t="n">
-        <v>49.5920964985622</v>
+        <v>49.597075379376</v>
       </c>
       <c r="O135" t="s">
         <v>42</v>
@@ -19709,7 +19709,7 @@
         <v>242</v>
       </c>
       <c r="N136" t="n">
-        <v>49.8294054830651</v>
+        <v>49.8322908697209</v>
       </c>
       <c r="O136" t="s">
         <v>42</v>
@@ -19758,7 +19758,7 @@
         <v>242</v>
       </c>
       <c r="N137" t="n">
-        <v>42.7972122978928</v>
+        <v>42.8005761488192</v>
       </c>
       <c r="O137" t="s">
         <v>26</v>
@@ -19807,7 +19807,7 @@
         <v>242</v>
       </c>
       <c r="N138" t="n">
-        <v>40.8134536927987</v>
+        <v>42.314685818171</v>
       </c>
       <c r="O138" t="s">
         <v>26</v>
@@ -19856,7 +19856,7 @@
         <v>242</v>
       </c>
       <c r="N139" t="n">
-        <v>42.9428751180818</v>
+        <v>42.4230650178746</v>
       </c>
       <c r="O139" t="s">
         <v>26</v>
@@ -19905,7 +19905,7 @@
         <v>242</v>
       </c>
       <c r="N140" t="n">
-        <v>42.5655223220909</v>
+        <v>44.7006950436784</v>
       </c>
       <c r="O140" t="s">
         <v>26</v>
@@ -19954,7 +19954,7 @@
         <v>242</v>
       </c>
       <c r="N141" t="n">
-        <v>41.7342042409386</v>
+        <v>41.7753303847744</v>
       </c>
       <c r="O141" t="s">
         <v>26</v>
@@ -20005,7 +20005,7 @@
         <v>242</v>
       </c>
       <c r="N142" t="n">
-        <v>38.3068553435736</v>
+        <v>38.311041234604</v>
       </c>
       <c r="O142" t="s">
         <v>20</v>
@@ -20056,7 +20056,7 @@
         <v>242</v>
       </c>
       <c r="N143" t="n">
-        <v>63.4756400968901</v>
+        <v>68.1876518214113</v>
       </c>
       <c r="O143" t="s">
         <v>42</v>
@@ -20107,7 +20107,7 @@
         <v>242</v>
       </c>
       <c r="N144" t="n">
-        <v>44.9715080857073</v>
+        <v>46.0604562850646</v>
       </c>
       <c r="O144" t="s">
         <v>26</v>
@@ -20158,7 +20158,7 @@
         <v>242</v>
       </c>
       <c r="N145" t="n">
-        <v>35.7036831742656</v>
+        <v>35.6278547478465</v>
       </c>
       <c r="O145" t="s">
         <v>20</v>
@@ -20207,7 +20207,7 @@
         <v>242</v>
       </c>
       <c r="N146" t="n">
-        <v>46.0046484336742</v>
+        <v>47.2565507810849</v>
       </c>
       <c r="O146" t="s">
         <v>26</v>
@@ -20258,7 +20258,7 @@
         <v>242</v>
       </c>
       <c r="N147" t="n">
-        <v>51.9132617715786</v>
+        <v>51.9173492799867</v>
       </c>
       <c r="O147" t="s">
         <v>42</v>
@@ -20309,7 +20309,7 @@
         <v>242</v>
       </c>
       <c r="N148" t="n">
-        <v>63.0742143131437</v>
+        <v>63.0776182048867</v>
       </c>
       <c r="O148" t="s">
         <v>42</v>
@@ -20360,7 +20360,7 @@
         <v>242</v>
       </c>
       <c r="N149" t="n">
-        <v>46.9510047562081</v>
+        <v>45.8220839569622</v>
       </c>
       <c r="O149" t="s">
         <v>26</v>
@@ -20411,7 +20411,7 @@
         <v>242</v>
       </c>
       <c r="N150" t="n">
-        <v>59.6198818020546</v>
+        <v>59.6532996938498</v>
       </c>
       <c r="O150" t="s">
         <v>42</v>
@@ -20462,7 +20462,7 @@
         <v>242</v>
       </c>
       <c r="N151" t="n">
-        <v>48.2981999328139</v>
+        <v>46.969130247006</v>
       </c>
       <c r="O151" t="s">
         <v>26</v>
@@ -20513,7 +20513,7 @@
         <v>242</v>
       </c>
       <c r="N152" t="n">
-        <v>42.6542539120847</v>
+        <v>42.9836210661531</v>
       </c>
       <c r="O152" t="s">
         <v>26</v>
@@ -20564,7 +20564,7 @@
         <v>242</v>
       </c>
       <c r="N153" t="n">
-        <v>43.3427236763665</v>
+        <v>41.1157080768444</v>
       </c>
       <c r="O153" t="s">
         <v>26</v>
@@ -20615,7 +20615,7 @@
         <v>242</v>
       </c>
       <c r="N154" t="n">
-        <v>44.0802014732414</v>
+        <v>41.6660057447824</v>
       </c>
       <c r="O154" t="s">
         <v>26</v>
@@ -20666,7 +20666,7 @@
         <v>242</v>
       </c>
       <c r="N155" t="n">
-        <v>48.5484662475755</v>
+        <v>47.6826464123334</v>
       </c>
       <c r="O155" t="s">
         <v>26</v>
@@ -20717,7 +20717,7 @@
         <v>242</v>
       </c>
       <c r="N156" t="n">
-        <v>45.2339532445515</v>
+        <v>44.2227130443011</v>
       </c>
       <c r="O156" t="s">
         <v>26</v>
@@ -20768,13 +20768,13 @@
         <v>242</v>
       </c>
       <c r="N157" t="n">
-        <v>43.1894911623646</v>
+        <v>50.3200075560917</v>
       </c>
       <c r="O157" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P157" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q157"/>
     </row>
@@ -20819,7 +20819,7 @@
         <v>242</v>
       </c>
       <c r="N158" t="n">
-        <v>54.3283280945605</v>
+        <v>54.3331519508221</v>
       </c>
       <c r="O158" t="s">
         <v>42</v>
@@ -20870,7 +20870,7 @@
         <v>242</v>
       </c>
       <c r="N159" t="n">
-        <v>70.1149135277061</v>
+        <v>70.121401370688</v>
       </c>
       <c r="O159" t="s">
         <v>42</v>
@@ -20921,7 +20921,7 @@
         <v>242</v>
       </c>
       <c r="N160" t="n">
-        <v>66.1471478991895</v>
+        <v>63.4361802885292</v>
       </c>
       <c r="O160" t="s">
         <v>42</v>
@@ -20972,7 +20972,7 @@
         <v>242</v>
       </c>
       <c r="N161" t="n">
-        <v>42.4352947696759</v>
+        <v>42.4398982678953</v>
       </c>
       <c r="O161" t="s">
         <v>26</v>
@@ -21023,7 +21023,7 @@
         <v>242</v>
       </c>
       <c r="N162" t="n">
-        <v>68.3605870855828</v>
+        <v>64.1733843858322</v>
       </c>
       <c r="O162" t="s">
         <v>42</v>
@@ -21074,7 +21074,7 @@
         <v>242</v>
       </c>
       <c r="N163" t="n">
-        <v>44.9140114323532</v>
+        <v>47.5424121211345</v>
       </c>
       <c r="O163" t="s">
         <v>26</v>
@@ -21125,7 +21125,7 @@
         <v>242</v>
       </c>
       <c r="N164" t="n">
-        <v>53.3093343490612</v>
+        <v>51.1126212670072</v>
       </c>
       <c r="O164" t="s">
         <v>42</v>
@@ -21176,7 +21176,7 @@
         <v>242</v>
       </c>
       <c r="N165" t="n">
-        <v>51.6833585712822</v>
+        <v>49.4444629115014</v>
       </c>
       <c r="O165" t="s">
         <v>42</v>
@@ -21227,7 +21227,7 @@
         <v>242</v>
       </c>
       <c r="N166" t="n">
-        <v>50.4274547413038</v>
+        <v>50.4339111615517</v>
       </c>
       <c r="O166" t="s">
         <v>42</v>
@@ -21278,7 +21278,7 @@
         <v>242</v>
       </c>
       <c r="N167" t="n">
-        <v>68.4830632118997</v>
+        <v>67.6395071626007</v>
       </c>
       <c r="O167" t="s">
         <v>42</v>
@@ -21329,7 +21329,7 @@
         <v>242</v>
       </c>
       <c r="N168" t="n">
-        <v>47.473094180015</v>
+        <v>47.4786861844209</v>
       </c>
       <c r="O168" t="s">
         <v>26</v>
@@ -21378,7 +21378,7 @@
         <v>242</v>
       </c>
       <c r="N169" t="n">
-        <v>43.9115161761981</v>
+        <v>43.9143318015873</v>
       </c>
       <c r="O169" t="s">
         <v>26</v>
@@ -21427,7 +21427,7 @@
         <v>242</v>
       </c>
       <c r="N170" t="n">
-        <v>43.8035949993957</v>
+        <v>43.807472742447</v>
       </c>
       <c r="O170" t="s">
         <v>26</v>
@@ -21476,7 +21476,7 @@
         <v>242</v>
       </c>
       <c r="N171" t="n">
-        <v>60.0973152227697</v>
+        <v>60.102476593241</v>
       </c>
       <c r="O171" t="s">
         <v>42</v>
@@ -21525,7 +21525,7 @@
         <v>242</v>
       </c>
       <c r="N172" t="n">
-        <v>44.5089404393813</v>
+        <v>44.5129157272546</v>
       </c>
       <c r="O172" t="s">
         <v>26</v>
@@ -21576,7 +21576,7 @@
         <v>242</v>
       </c>
       <c r="N173" t="n">
-        <v>45.8726229655959</v>
+        <v>45.1214524227251</v>
       </c>
       <c r="O173" t="s">
         <v>26</v>
@@ -21674,7 +21674,7 @@
         <v>242</v>
       </c>
       <c r="N175" t="n">
-        <v>80.5555032440556</v>
+        <v>79.1787504698617</v>
       </c>
       <c r="O175" t="s">
         <v>38</v>
@@ -21725,7 +21725,7 @@
         <v>242</v>
       </c>
       <c r="N176" t="n">
-        <v>69.95</v>
+        <v>69.9587992</v>
       </c>
       <c r="O176" t="s">
         <v>42</v>
@@ -21776,7 +21776,7 @@
         <v>242</v>
       </c>
       <c r="N177" t="n">
-        <v>31.37</v>
+        <v>31.379525007</v>
       </c>
       <c r="O177" t="s">
         <v>20</v>
@@ -21827,7 +21827,7 @@
         <v>242</v>
       </c>
       <c r="N178" t="n">
-        <v>65.6001183025116</v>
+        <v>64.0567320807063</v>
       </c>
       <c r="O178" t="s">
         <v>42</v>
@@ -21878,7 +21878,7 @@
         <v>242</v>
       </c>
       <c r="N179" t="n">
-        <v>100.914152888188</v>
+        <v>103.575012595292</v>
       </c>
       <c r="O179" t="s">
         <v>38</v>
@@ -21929,7 +21929,7 @@
         <v>242</v>
       </c>
       <c r="N180" t="n">
-        <v>100.846655654698</v>
+        <v>103.376414891309</v>
       </c>
       <c r="O180" t="s">
         <v>38</v>
@@ -21980,7 +21980,7 @@
         <v>242</v>
       </c>
       <c r="N181" t="n">
-        <v>92.4425500632061</v>
+        <v>90.7419499720894</v>
       </c>
       <c r="O181" t="s">
         <v>38</v>
@@ -22031,7 +22031,7 @@
         <v>242</v>
       </c>
       <c r="N182" t="n">
-        <v>62.9939853131011</v>
+        <v>60.5341403489081</v>
       </c>
       <c r="O182" t="s">
         <v>42</v>
@@ -22082,7 +22082,7 @@
         <v>242</v>
       </c>
       <c r="N183" t="n">
-        <v>80.2993623979004</v>
+        <v>82.9432288876675</v>
       </c>
       <c r="O183" t="s">
         <v>38</v>
@@ -22131,7 +22131,7 @@
         <v>242</v>
       </c>
       <c r="N184" t="n">
-        <v>62.9996282426913</v>
+        <v>59.773849666236</v>
       </c>
       <c r="O184" t="s">
         <v>42</v>
@@ -22182,7 +22182,7 @@
         <v>242</v>
       </c>
       <c r="N185" t="n">
-        <v>46.2481291843476</v>
+        <v>41.7268992562071</v>
       </c>
       <c r="O185" t="s">
         <v>26</v>
@@ -22233,7 +22233,7 @@
         <v>242</v>
       </c>
       <c r="N186" t="n">
-        <v>47.348539207356</v>
+        <v>43.764771987482</v>
       </c>
       <c r="O186" t="s">
         <v>26</v>
@@ -22284,7 +22284,7 @@
         <v>242</v>
       </c>
       <c r="N187" t="n">
-        <v>67.1334226495279</v>
+        <v>67.1375967349711</v>
       </c>
       <c r="O187" t="s">
         <v>42</v>
@@ -22333,7 +22333,7 @@
         <v>242</v>
       </c>
       <c r="N188" t="n">
-        <v>14.5376272087859</v>
+        <v>15.0973837903592</v>
       </c>
       <c r="O188" t="s">
         <v>20</v>
@@ -22382,7 +22382,7 @@
         <v>242</v>
       </c>
       <c r="N189" t="n">
-        <v>12.5680670664863</v>
+        <v>12.5698046426121</v>
       </c>
       <c r="O189" t="s">
         <v>20</v>
@@ -22431,13 +22431,13 @@
         <v>242</v>
       </c>
       <c r="N190" t="n">
-        <v>40.8019214988018</v>
+        <v>39.3743639877656</v>
       </c>
       <c r="O190" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q190"/>
     </row>
@@ -22480,7 +22480,7 @@
         <v>242</v>
       </c>
       <c r="N191" t="n">
-        <v>29.1883826253006</v>
+        <v>28.701506477696</v>
       </c>
       <c r="O191" t="s">
         <v>20</v>
@@ -22529,7 +22529,7 @@
         <v>242</v>
       </c>
       <c r="N192" t="n">
-        <v>42.8291806733234</v>
+        <v>41.7027444687709</v>
       </c>
       <c r="O192" t="s">
         <v>26</v>
@@ -22578,7 +22578,7 @@
         <v>242</v>
       </c>
       <c r="N193" t="n">
-        <v>69.95</v>
+        <v>69.9587992</v>
       </c>
       <c r="O193" t="s">
         <v>42</v>
@@ -22629,7 +22629,7 @@
         <v>242</v>
       </c>
       <c r="N194" t="n">
-        <v>77.6361392954012</v>
+        <v>77.6408201529544</v>
       </c>
       <c r="O194" t="s">
         <v>38</v>
@@ -22680,7 +22680,7 @@
         <v>242</v>
       </c>
       <c r="N195" t="n">
-        <v>32.8584426583852</v>
+        <v>33.1764519722665</v>
       </c>
       <c r="O195" t="s">
         <v>20</v>
@@ -22731,7 +22731,7 @@
         <v>242</v>
       </c>
       <c r="N196" t="n">
-        <v>62.8240924171001</v>
+        <v>64.9895164357706</v>
       </c>
       <c r="O196" t="s">
         <v>42</v>
@@ -22876,7 +22876,7 @@
         <v>242</v>
       </c>
       <c r="N199" t="n">
-        <v>77.367859953028</v>
+        <v>77.3725439867089</v>
       </c>
       <c r="O199" t="s">
         <v>38</v>
@@ -22927,7 +22927,7 @@
         <v>242</v>
       </c>
       <c r="N200" t="n">
-        <v>69.95</v>
+        <v>69.9587992</v>
       </c>
       <c r="O200" t="s">
         <v>42</v>
@@ -23025,7 +23025,7 @@
         <v>242</v>
       </c>
       <c r="N202" t="n">
-        <v>49.5749956358063</v>
+        <v>49.5791316120116</v>
       </c>
       <c r="O202" t="s">
         <v>42</v>
@@ -23076,7 +23076,7 @@
         <v>242</v>
       </c>
       <c r="N203" t="n">
-        <v>73.0302715390466</v>
+        <v>73.0362981218374</v>
       </c>
       <c r="O203" t="s">
         <v>42</v>
@@ -23127,7 +23127,7 @@
         <v>242</v>
       </c>
       <c r="N204" t="n">
-        <v>56.484274471388</v>
+        <v>55.1331427182267</v>
       </c>
       <c r="O204" t="s">
         <v>42</v>
@@ -25084,13 +25084,13 @@
         <v>245</v>
       </c>
       <c r="N38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O38" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q38" t="s">
         <v>246</v>
@@ -27246,13 +27246,13 @@
         <v>245</v>
       </c>
       <c r="N80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O80" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="s">
         <v>246</v>
@@ -30291,13 +30291,13 @@
         <v>245</v>
       </c>
       <c r="N139" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O139" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q139" t="s">
         <v>246</v>
@@ -30656,13 +30656,13 @@
         <v>245</v>
       </c>
       <c r="N146" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O146" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P146" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q146" t="s">
         <v>246</v>
@@ -34184,7 +34184,7 @@
         <v>247</v>
       </c>
       <c r="N9" t="n">
-        <v>0.189321402691411</v>
+        <v>0.191475136188428</v>
       </c>
       <c r="O9" t="s">
         <v>26</v>
@@ -34286,7 +34286,7 @@
         <v>247</v>
       </c>
       <c r="N11" t="n">
-        <v>0.178379829095246</v>
+        <v>0.180533562592263</v>
       </c>
       <c r="O11" t="s">
         <v>26</v>
@@ -34390,7 +34390,7 @@
         <v>247</v>
       </c>
       <c r="N13" t="n">
-        <v>0.198906514411919</v>
+        <v>0.201060247908936</v>
       </c>
       <c r="O13" t="s">
         <v>26</v>
@@ -34441,7 +34441,7 @@
         <v>247</v>
       </c>
       <c r="N14" t="n">
-        <v>0.253842949341174</v>
+        <v>0.255996682838191</v>
       </c>
       <c r="O14" t="s">
         <v>26</v>
@@ -34596,7 +34596,7 @@
         <v>247</v>
       </c>
       <c r="N17" t="n">
-        <v>0.259277493457965</v>
+        <v>0.268846598457712</v>
       </c>
       <c r="O17" t="s">
         <v>26</v>
@@ -34647,7 +34647,7 @@
         <v>247</v>
       </c>
       <c r="N18" t="n">
-        <v>0.22485494504881</v>
+        <v>0.222701211551793</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -34698,7 +34698,7 @@
         <v>247</v>
       </c>
       <c r="N19" t="n">
-        <v>0.145856769427758</v>
+        <v>0.1556254892178</v>
       </c>
       <c r="O19" t="s">
         <v>42</v>
@@ -34800,7 +34800,7 @@
         <v>247</v>
       </c>
       <c r="N21" t="n">
-        <v>0.759605072469519</v>
+        <v>0.767083414916195</v>
       </c>
       <c r="O21" t="s">
         <v>20</v>
@@ -34851,7 +34851,7 @@
         <v>247</v>
       </c>
       <c r="N22" t="n">
-        <v>0.771634163538059</v>
+        <v>0.781203268537805</v>
       </c>
       <c r="O22" t="s">
         <v>20</v>
@@ -35157,13 +35157,13 @@
         <v>247</v>
       </c>
       <c r="N28" t="n">
-        <v>0.155302054444533</v>
+        <v>0.164997101332174</v>
       </c>
       <c r="O28" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q28" t="s">
         <v>246</v>
@@ -35514,7 +35514,7 @@
         <v>247</v>
       </c>
       <c r="N35" t="n">
-        <v>0.196074034540926</v>
+        <v>0.198227768037943</v>
       </c>
       <c r="O35" t="s">
         <v>26</v>
@@ -35565,7 +35565,7 @@
         <v>247</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0712752423970888</v>
+        <v>0.0691215089000718</v>
       </c>
       <c r="O36" t="s">
         <v>38</v>
@@ -35718,7 +35718,7 @@
         <v>247</v>
       </c>
       <c r="N39" t="n">
-        <v>0.187011088779152</v>
+        <v>0.184857355282135</v>
       </c>
       <c r="O39" t="s">
         <v>26</v>
@@ -35922,7 +35922,7 @@
         <v>247</v>
       </c>
       <c r="N43" t="n">
-        <v>0.366734095729723</v>
+        <v>0.376271715257496</v>
       </c>
       <c r="O43" t="s">
         <v>20</v>
@@ -36240,7 +36240,7 @@
         <v>247</v>
       </c>
       <c r="N49" t="n">
-        <v>0.241347881307264</v>
+        <v>0.260580547722678</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
@@ -36293,7 +36293,7 @@
         <v>247</v>
       </c>
       <c r="N50" t="n">
-        <v>0.160277512900468</v>
+        <v>0.179415722899961</v>
       </c>
       <c r="O50" t="s">
         <v>26</v>
@@ -36397,7 +36397,7 @@
         <v>247</v>
       </c>
       <c r="N52" t="n">
-        <v>0.430880281817545</v>
+        <v>0.438495268110569</v>
       </c>
       <c r="O52" t="s">
         <v>20</v>
@@ -36448,7 +36448,7 @@
         <v>247</v>
       </c>
       <c r="N53" t="n">
-        <v>0.423380536643283</v>
+        <v>0.43294964164303</v>
       </c>
       <c r="O53" t="s">
         <v>20</v>
@@ -36501,7 +36501,7 @@
         <v>247</v>
       </c>
       <c r="N54" t="n">
-        <v>0.33026081993043</v>
+        <v>0.33830590087263</v>
       </c>
       <c r="O54" t="s">
         <v>20</v>
@@ -36605,7 +36605,7 @@
         <v>247</v>
       </c>
       <c r="N56" t="n">
-        <v>0.0690936126810361</v>
+        <v>0.0786312322088091</v>
       </c>
       <c r="O56" t="s">
         <v>38</v>
@@ -36656,7 +36656,7 @@
         <v>247</v>
       </c>
       <c r="N57" t="n">
-        <v>0.168308278191142</v>
+        <v>0.190626520859961</v>
       </c>
       <c r="O57" t="s">
         <v>26</v>
@@ -36758,7 +36758,7 @@
         <v>247</v>
       </c>
       <c r="N59" t="n">
-        <v>0.396805551224153</v>
+        <v>0.416573470663116</v>
       </c>
       <c r="O59" t="s">
         <v>20</v>
@@ -36962,7 +36962,7 @@
         <v>247</v>
       </c>
       <c r="N63" t="n">
-        <v>0.0724219154935461</v>
+        <v>0.070268181996529</v>
       </c>
       <c r="O63" t="s">
         <v>38</v>
@@ -37013,7 +37013,7 @@
         <v>247</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0427476056192509</v>
+        <v>0.0405938721222338</v>
       </c>
       <c r="O64" t="s">
         <v>38</v>
@@ -37064,7 +37064,7 @@
         <v>247</v>
       </c>
       <c r="N65" t="n">
-        <v>0.286334683939384</v>
+        <v>0.284180950442367</v>
       </c>
       <c r="O65" t="s">
         <v>20</v>
@@ -37217,7 +37217,7 @@
         <v>247</v>
       </c>
       <c r="N68" t="n">
-        <v>0.0697522451384839</v>
+        <v>0.0740597121325181</v>
       </c>
       <c r="O68" t="s">
         <v>38</v>
@@ -37421,7 +37421,7 @@
         <v>247</v>
       </c>
       <c r="N72" t="n">
-        <v>0.387777720632359</v>
+        <v>0.39747276752</v>
       </c>
       <c r="O72" t="s">
         <v>20</v>
@@ -37523,7 +37523,7 @@
         <v>247</v>
       </c>
       <c r="N74" t="n">
-        <v>0.643747857559407</v>
+        <v>0.653568846334942</v>
       </c>
       <c r="O74" t="s">
         <v>20</v>
@@ -37625,7 +37625,7 @@
         <v>247</v>
       </c>
       <c r="N76" t="n">
-        <v>0.459484038967159</v>
+        <v>0.4691790858548</v>
       </c>
       <c r="O76" t="s">
         <v>20</v>
@@ -37829,7 +37829,7 @@
         <v>247</v>
       </c>
       <c r="N80" t="n">
-        <v>0.16150722981051</v>
+        <v>0.180960294529738</v>
       </c>
       <c r="O80" t="s">
         <v>26</v>
@@ -38033,7 +38033,7 @@
         <v>247</v>
       </c>
       <c r="N84" t="n">
-        <v>0.12796159934441</v>
+        <v>0.137562189816131</v>
       </c>
       <c r="O84" t="s">
         <v>42</v>
@@ -38190,7 +38190,7 @@
         <v>247</v>
       </c>
       <c r="N87" t="n">
-        <v>0.0726194425324379</v>
+        <v>0.0821885475321845</v>
       </c>
       <c r="O87" t="s">
         <v>38</v>
@@ -38243,7 +38243,7 @@
         <v>247</v>
       </c>
       <c r="N88" t="n">
-        <v>0.205642469943682</v>
+        <v>0.224938107303042</v>
       </c>
       <c r="O88" t="s">
         <v>26</v>
@@ -38296,7 +38296,7 @@
         <v>247</v>
       </c>
       <c r="N89" t="n">
-        <v>0.103433899047543</v>
+        <v>0.113191916879131</v>
       </c>
       <c r="O89" t="s">
         <v>42</v>
@@ -38400,7 +38400,7 @@
         <v>247</v>
       </c>
       <c r="N91" t="n">
-        <v>0.169397150998561</v>
+        <v>0.171550884495578</v>
       </c>
       <c r="O91" t="s">
         <v>26</v>
@@ -38506,7 +38506,7 @@
         <v>247</v>
       </c>
       <c r="N93" t="n">
-        <v>0.300427036016602</v>
+        <v>0.309964655544375</v>
       </c>
       <c r="O93" t="s">
         <v>20</v>
@@ -38559,7 +38559,7 @@
         <v>247</v>
       </c>
       <c r="N94" t="n">
-        <v>0.166855984985389</v>
+        <v>0.188084957537952</v>
       </c>
       <c r="O94" t="s">
         <v>26</v>
@@ -38612,7 +38612,7 @@
         <v>247</v>
       </c>
       <c r="N95" t="n">
-        <v>0.210820139484092</v>
+        <v>0.230115776843453</v>
       </c>
       <c r="O95" t="s">
         <v>26</v>
@@ -38665,7 +38665,7 @@
         <v>247</v>
       </c>
       <c r="N96" t="n">
-        <v>0.234557393536879</v>
+        <v>0.244283925896493</v>
       </c>
       <c r="O96" t="s">
         <v>26</v>
@@ -38716,7 +38716,7 @@
         <v>247</v>
       </c>
       <c r="N97" t="n">
-        <v>0.281096535433485</v>
+        <v>0.292819373930249</v>
       </c>
       <c r="O97" t="s">
         <v>20</v>
@@ -38767,7 +38767,7 @@
         <v>247</v>
       </c>
       <c r="N98" t="n">
-        <v>0.120135254463613</v>
+        <v>0.12228898796063</v>
       </c>
       <c r="O98" t="s">
         <v>42</v>
@@ -38820,7 +38820,7 @@
         <v>247</v>
       </c>
       <c r="N99" t="n">
-        <v>0.168480957760984</v>
+        <v>0.180172310785774</v>
       </c>
       <c r="O99" t="s">
         <v>26</v>
@@ -39187,7 +39187,7 @@
         <v>247</v>
       </c>
       <c r="N106" t="n">
-        <v>0.219774235157993</v>
+        <v>0.22192796865501</v>
       </c>
       <c r="O106" t="s">
         <v>26</v>
@@ -39344,7 +39344,7 @@
         <v>247</v>
       </c>
       <c r="N109" t="n">
-        <v>0.134678893267576</v>
+        <v>0.144216512795349</v>
       </c>
       <c r="O109" t="s">
         <v>42</v>
@@ -39446,7 +39446,7 @@
         <v>247</v>
       </c>
       <c r="N111" t="n">
-        <v>0.494017711023271</v>
+        <v>0.503712757910912</v>
       </c>
       <c r="O111" t="s">
         <v>20</v>
@@ -39497,7 +39497,7 @@
         <v>247</v>
       </c>
       <c r="N112" t="n">
-        <v>0.487011326660829</v>
+        <v>0.496580431660575</v>
       </c>
       <c r="O112" t="s">
         <v>20</v>
@@ -39650,7 +39650,7 @@
         <v>247</v>
       </c>
       <c r="N115" t="n">
-        <v>0.527882205570981</v>
+        <v>0.537419825098754</v>
       </c>
       <c r="O115" t="s">
         <v>20</v>
@@ -39701,7 +39701,7 @@
         <v>247</v>
       </c>
       <c r="N116" t="n">
-        <v>0.115521367102578</v>
+        <v>0.125090472102325</v>
       </c>
       <c r="O116" t="s">
         <v>42</v>
@@ -39803,7 +39803,7 @@
         <v>247</v>
       </c>
       <c r="N118" t="n">
-        <v>0.487997175368161</v>
+        <v>0.497818164143696</v>
       </c>
       <c r="O118" t="s">
         <v>20</v>
@@ -39905,7 +39905,7 @@
         <v>247</v>
       </c>
       <c r="N120" t="n">
-        <v>0.449491822586785</v>
+        <v>0.459060927586531</v>
       </c>
       <c r="O120" t="s">
         <v>20</v>
@@ -40415,7 +40415,7 @@
         <v>247</v>
       </c>
       <c r="N130" t="n">
-        <v>0.122854010946783</v>
+        <v>0.120700277449766</v>
       </c>
       <c r="O130" t="s">
         <v>42</v>
@@ -40925,7 +40925,7 @@
         <v>247</v>
       </c>
       <c r="N140" t="n">
-        <v>0.361533486617351</v>
+        <v>0.371071106145124</v>
       </c>
       <c r="O140" t="s">
         <v>20</v>
@@ -41082,7 +41082,7 @@
         <v>247</v>
       </c>
       <c r="N143" t="n">
-        <v>0.292783367877424</v>
+        <v>0.290629634380407</v>
       </c>
       <c r="O143" t="s">
         <v>20</v>
@@ -41135,13 +41135,13 @@
         <v>247</v>
       </c>
       <c r="N144" t="n">
-        <v>0.263080445909677</v>
+        <v>0.270779186660168</v>
       </c>
       <c r="O144" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q144" t="s">
         <v>246</v>
@@ -41188,7 +41188,7 @@
         <v>247</v>
       </c>
       <c r="N145" t="n">
-        <v>0.479358486470311</v>
+        <v>0.488896105998084</v>
       </c>
       <c r="O145" t="s">
         <v>20</v>
@@ -41239,7 +41239,7 @@
         <v>247</v>
       </c>
       <c r="N146" t="n">
-        <v>0.0531135567313678</v>
+        <v>0.0509598232343507</v>
       </c>
       <c r="O146" t="s">
         <v>38</v>
@@ -41557,7 +41557,7 @@
         <v>247</v>
       </c>
       <c r="N152" t="n">
-        <v>0.20301455242334</v>
+        <v>0.21261514289506</v>
       </c>
       <c r="O152" t="s">
         <v>26</v>
@@ -41663,7 +41663,7 @@
         <v>247</v>
       </c>
       <c r="N154" t="n">
-        <v>0.254177629082527</v>
+        <v>0.263746734082273</v>
       </c>
       <c r="O154" t="s">
         <v>26</v>
@@ -41716,13 +41716,13 @@
         <v>247</v>
       </c>
       <c r="N155" t="n">
-        <v>0.157734541137433</v>
+        <v>0.167335131609153</v>
       </c>
       <c r="O155" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="P155" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q155" t="s">
         <v>246</v>
@@ -42246,7 +42246,7 @@
         <v>247</v>
       </c>
       <c r="N165" t="n">
-        <v>0.43319261674325</v>
+        <v>0.442761721742997</v>
       </c>
       <c r="O165" t="s">
         <v>20</v>
@@ -42352,7 +42352,7 @@
         <v>247</v>
       </c>
       <c r="N167" t="n">
-        <v>0.39029885569023</v>
+        <v>0.399930931633923</v>
       </c>
       <c r="O167" t="s">
         <v>20</v>
@@ -42927,7 +42927,7 @@
         <v>247</v>
       </c>
       <c r="N178" t="n">
-        <v>0.136619161311979</v>
+        <v>0.134465427814962</v>
       </c>
       <c r="O178" t="s">
         <v>42</v>
@@ -43192,7 +43192,7 @@
         <v>247</v>
       </c>
       <c r="N183" t="n">
-        <v>0.0730837646485635</v>
+        <v>0.0829047534240982</v>
       </c>
       <c r="O183" t="s">
         <v>38</v>
@@ -43243,7 +43243,7 @@
         <v>247</v>
       </c>
       <c r="N184" t="n">
-        <v>0.0226195294797795</v>
+        <v>0.0322830908954467</v>
       </c>
       <c r="O184" t="s">
         <v>38</v>
@@ -43296,7 +43296,7 @@
         <v>247</v>
       </c>
       <c r="N185" t="n">
-        <v>0.196949864271371</v>
+        <v>0.194796130774354</v>
       </c>
       <c r="O185" t="s">
         <v>26</v>
@@ -43349,13 +43349,13 @@
         <v>247</v>
       </c>
       <c r="N186" t="n">
-        <v>0.260698192464484</v>
+        <v>0.279962344351872</v>
       </c>
       <c r="O186" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q186" t="s">
         <v>246</v>
@@ -43402,7 +43402,7 @@
         <v>247</v>
       </c>
       <c r="N187" t="n">
-        <v>0.0329514326659267</v>
+        <v>0.0352625935228114</v>
       </c>
       <c r="O187" t="s">
         <v>38</v>
@@ -43504,7 +43504,7 @@
         <v>247</v>
       </c>
       <c r="N189" t="n">
-        <v>0.164921554686205</v>
+        <v>0.167075288183222</v>
       </c>
       <c r="O189" t="s">
         <v>26</v>
@@ -43555,7 +43555,7 @@
         <v>247</v>
       </c>
       <c r="N190" t="n">
-        <v>0.273619846142505</v>
+        <v>0.283314893030146</v>
       </c>
       <c r="O190" t="s">
         <v>20</v>
@@ -43657,7 +43657,7 @@
         <v>247</v>
       </c>
       <c r="N192" t="n">
-        <v>0.764539944366864</v>
+        <v>0.774077563894637</v>
       </c>
       <c r="O192" t="s">
         <v>20</v>
@@ -43761,7 +43761,7 @@
         <v>247</v>
       </c>
       <c r="N194" t="n">
-        <v>0.241933469829401</v>
+        <v>0.251534060301121</v>
       </c>
       <c r="O194" t="s">
         <v>26</v>
@@ -43814,7 +43814,7 @@
         <v>247</v>
       </c>
       <c r="N195" t="n">
-        <v>0.162603715092841</v>
+        <v>0.181962323396149</v>
       </c>
       <c r="O195" t="s">
         <v>26</v>
@@ -43867,7 +43867,7 @@
         <v>247</v>
       </c>
       <c r="N196" t="n">
-        <v>0.314848107062628</v>
+        <v>0.312694373565611</v>
       </c>
       <c r="O196" t="s">
         <v>20</v>
@@ -44026,7 +44026,7 @@
         <v>247</v>
       </c>
       <c r="N199" t="n">
-        <v>0.127915860268404</v>
+        <v>0.137453479796177</v>
       </c>
       <c r="O199" t="s">
         <v>42</v>
@@ -56017,10 +56017,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E26" t="s">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -56029,7 +56029,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
@@ -56616,7 +56616,7 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H36" t="n">
         <v>2</v>
@@ -59154,7 +59154,7 @@
         <v>2</v>
       </c>
       <c r="G78" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H78" t="n">
         <v>2</v>
@@ -62386,7 +62386,7 @@
         <v>42</v>
       </c>
       <c r="F131" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
         <v>2</v>
@@ -62743,7 +62743,7 @@
         <v>2</v>
       </c>
       <c r="G137" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H137" t="n">
         <v>2</v>
@@ -63053,7 +63053,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I142" t="n">
         <v>3</v>
@@ -63180,7 +63180,7 @@
         <v>2</v>
       </c>
       <c r="G144" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H144" t="n">
         <v>4</v>
@@ -63762,7 +63762,7 @@
         <v>2</v>
       </c>
       <c r="H153" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -63880,13 +63880,13 @@
         <v>1</v>
       </c>
       <c r="D155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E155" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G155" t="n">
         <v>2</v>
@@ -65745,7 +65745,7 @@
         <v>2</v>
       </c>
       <c r="H184" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I184" t="n">
         <v>3</v>
@@ -65987,7 +65987,7 @@
         <v>26</v>
       </c>
       <c r="F188" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G188" t="n">
         <v>2</v>

--- a/SQO dry run/djg test SQO BLOE output summary.xlsx
+++ b/SQO dry run/djg test SQO BLOE output summary.xlsx
@@ -71,7 +71,7 @@
     <t xml:space="preserve">salinity</t>
   </si>
   <si>
-    <t xml:space="preserve">areaweight_all_sites</t>
+    <t xml:space="preserve">areaweightallsites</t>
   </si>
   <si>
     <t xml:space="preserve">notes</t>
@@ -1421,7 +1421,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -1537,7 +1537,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -1710,7 +1710,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -1942,7 +1942,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -1999,7 +1999,7 @@
         <v>39</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -2170,7 +2170,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -3253,7 +3253,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -3892,7 +3892,7 @@
         <v>74</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -3951,7 +3951,7 @@
         <v>75</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -4299,7 +4299,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -4470,7 +4470,7 @@
         <v>84</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -4584,7 +4584,7 @@
         <v>86</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -4641,7 +4641,7 @@
         <v>87</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -4698,7 +4698,7 @@
         <v>88</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -4755,7 +4755,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -4812,7 +4812,7 @@
         <v>90</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -4869,7 +4869,7 @@
         <v>91</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -4926,7 +4926,7 @@
         <v>92</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -4983,7 +4983,7 @@
         <v>93</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -5040,7 +5040,7 @@
         <v>94</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -5097,7 +5097,7 @@
         <v>95</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -5154,7 +5154,7 @@
         <v>96</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -5724,7 +5724,7 @@
         <v>106</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -5781,7 +5781,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -5838,7 +5838,7 @@
         <v>108</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -5895,7 +5895,7 @@
         <v>109</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -6070,7 +6070,7 @@
         <v>113</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -6188,7 +6188,7 @@
         <v>115</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -6304,7 +6304,7 @@
         <v>117</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -6363,7 +6363,7 @@
         <v>118</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -6422,7 +6422,7 @@
         <v>119</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -6540,7 +6540,7 @@
         <v>121</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -6713,7 +6713,7 @@
         <v>124</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -6772,7 +6772,7 @@
         <v>125</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -6890,7 +6890,7 @@
         <v>127</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -6949,7 +6949,7 @@
         <v>128</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -7065,7 +7065,7 @@
         <v>130</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -7181,7 +7181,7 @@
         <v>132</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -8040,7 +8040,7 @@
         <v>147</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -8211,7 +8211,7 @@
         <v>150</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -8268,7 +8268,7 @@
         <v>151</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -8325,7 +8325,7 @@
         <v>152</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -8382,7 +8382,7 @@
         <v>153</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -8553,7 +8553,7 @@
         <v>156</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -8610,7 +8610,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -8781,7 +8781,7 @@
         <v>160</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -9180,7 +9180,7 @@
         <v>167</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -9239,7 +9239,7 @@
         <v>169</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -9357,7 +9357,7 @@
         <v>171</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -9827,7 +9827,7 @@
         <v>179</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -10181,7 +10181,7 @@
         <v>185</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -10240,7 +10240,7 @@
         <v>186</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -10299,7 +10299,7 @@
         <v>187</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -10358,7 +10358,7 @@
         <v>188</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -10417,7 +10417,7 @@
         <v>189</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -10476,7 +10476,7 @@
         <v>190</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -10535,7 +10535,7 @@
         <v>191</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -11292,7 +11292,7 @@
         <v>207</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -11351,7 +11351,7 @@
         <v>208</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -11646,7 +11646,7 @@
         <v>213</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -11821,7 +11821,7 @@
         <v>215</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -11994,7 +11994,7 @@
         <v>218</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -12108,7 +12108,7 @@
         <v>220</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -12281,7 +12281,7 @@
         <v>223</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -12340,7 +12340,7 @@
         <v>224</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -12513,7 +12513,7 @@
         <v>227</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -12865,7 +12865,7 @@
         <v>233</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -13059,7 +13059,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="I2" t="s">
         <v>234</v>
@@ -13308,7 +13308,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -13408,7 +13408,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -13557,7 +13557,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -13757,7 +13757,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -13806,7 +13806,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -13953,7 +13953,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -14884,7 +14884,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -15435,7 +15435,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I50" t="s">
         <v>66</v>
@@ -15486,7 +15486,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I51" t="s">
         <v>66</v>
@@ -15786,7 +15786,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I57" t="s">
         <v>66</v>
@@ -15933,7 +15933,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I60" t="s">
         <v>66</v>
@@ -16031,7 +16031,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I62" t="s">
         <v>66</v>
@@ -16080,7 +16080,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I63" t="s">
         <v>66</v>
@@ -16129,7 +16129,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I64" t="s">
         <v>66</v>
@@ -16178,7 +16178,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I65" t="s">
         <v>66</v>
@@ -16227,7 +16227,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I66" t="s">
         <v>66</v>
@@ -16276,7 +16276,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I67" t="s">
         <v>66</v>
@@ -16325,7 +16325,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I68" t="s">
         <v>66</v>
@@ -16374,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I69" t="s">
         <v>66</v>
@@ -16423,7 +16423,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I70" t="s">
         <v>66</v>
@@ -16472,7 +16472,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I71" t="s">
         <v>66</v>
@@ -16521,7 +16521,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I72" t="s">
         <v>66</v>
@@ -17011,7 +17011,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I82" t="s">
         <v>66</v>
@@ -17060,7 +17060,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I83" t="s">
         <v>66</v>
@@ -17109,7 +17109,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I84" t="s">
         <v>66</v>
@@ -17158,7 +17158,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I85" t="s">
         <v>66</v>
@@ -17309,7 +17309,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I88" t="s">
         <v>111</v>
@@ -17411,7 +17411,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I90" t="s">
         <v>111</v>
@@ -17511,7 +17511,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I92" t="s">
         <v>111</v>
@@ -17562,7 +17562,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I93" t="s">
         <v>111</v>
@@ -17613,7 +17613,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I94" t="s">
         <v>111</v>
@@ -17715,7 +17715,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I96" t="s">
         <v>111</v>
@@ -17864,7 +17864,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I99" t="s">
         <v>111</v>
@@ -17915,7 +17915,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I100" t="s">
         <v>111</v>
@@ -18017,7 +18017,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I102" t="s">
         <v>111</v>
@@ -18068,7 +18068,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I103" t="s">
         <v>111</v>
@@ -18168,7 +18168,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I105" t="s">
         <v>111</v>
@@ -18268,7 +18268,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I107" t="s">
         <v>111</v>
@@ -19007,7 +19007,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I122" t="s">
         <v>111</v>
@@ -19154,7 +19154,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I125" t="s">
         <v>111</v>
@@ -19203,7 +19203,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I126" t="s">
         <v>111</v>
@@ -19252,7 +19252,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I127" t="s">
         <v>111</v>
@@ -19301,7 +19301,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I128" t="s">
         <v>111</v>
@@ -19448,7 +19448,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I131" t="s">
         <v>111</v>
@@ -19497,7 +19497,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I132" t="s">
         <v>111</v>
@@ -19644,7 +19644,7 @@
         <v>1</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I135" t="s">
         <v>111</v>
@@ -19987,7 +19987,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I142" t="s">
         <v>168</v>
@@ -20038,7 +20038,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I143" t="s">
         <v>168</v>
@@ -20140,7 +20140,7 @@
         <v>1</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I145" t="s">
         <v>168</v>
@@ -20546,7 +20546,7 @@
         <v>1</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I153" t="s">
         <v>168</v>
@@ -20852,7 +20852,7 @@
         <v>1</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I159" t="s">
         <v>168</v>
@@ -20903,7 +20903,7 @@
         <v>1</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I160" t="s">
         <v>168</v>
@@ -20954,7 +20954,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I161" t="s">
         <v>168</v>
@@ -21005,7 +21005,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I162" t="s">
         <v>168</v>
@@ -21056,7 +21056,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I163" t="s">
         <v>168</v>
@@ -21107,7 +21107,7 @@
         <v>1</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I164" t="s">
         <v>168</v>
@@ -21158,7 +21158,7 @@
         <v>1</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I165" t="s">
         <v>168</v>
@@ -21809,7 +21809,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I178" t="s">
         <v>201</v>
@@ -21860,7 +21860,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="I179" t="s">
         <v>201</v>
@@ -22115,7 +22115,7 @@
         <v>1</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I184" t="s">
         <v>201</v>
@@ -22266,7 +22266,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I187" t="s">
         <v>201</v>
@@ -22415,7 +22415,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I190" t="s">
         <v>22</v>
@@ -22513,7 +22513,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I192" t="s">
         <v>22</v>
@@ -22662,7 +22662,7 @@
         <v>1</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I195" t="s">
         <v>168</v>
@@ -22713,7 +22713,7 @@
         <v>1</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I196" t="s">
         <v>168</v>
@@ -22858,7 +22858,7 @@
         <v>1</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I199" t="s">
         <v>201</v>
@@ -23222,7 +23222,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="I2" t="s">
         <v>234</v>
@@ -23479,7 +23479,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -23583,7 +23583,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -23738,7 +23738,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -23946,7 +23946,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -23997,7 +23997,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -24150,7 +24150,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -25119,7 +25119,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -25692,7 +25692,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I50" t="s">
         <v>66</v>
@@ -25745,7 +25745,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I51" t="s">
         <v>66</v>
@@ -26057,7 +26057,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I57" t="s">
         <v>66</v>
@@ -26210,7 +26210,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I60" t="s">
         <v>66</v>
@@ -26312,7 +26312,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I62" t="s">
         <v>66</v>
@@ -26363,7 +26363,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I63" t="s">
         <v>66</v>
@@ -26414,7 +26414,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I64" t="s">
         <v>66</v>
@@ -26465,7 +26465,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I65" t="s">
         <v>66</v>
@@ -26516,7 +26516,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I66" t="s">
         <v>66</v>
@@ -26567,7 +26567,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I67" t="s">
         <v>66</v>
@@ -26618,7 +26618,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I68" t="s">
         <v>66</v>
@@ -26669,7 +26669,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I69" t="s">
         <v>66</v>
@@ -26720,7 +26720,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I70" t="s">
         <v>66</v>
@@ -26771,7 +26771,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I71" t="s">
         <v>66</v>
@@ -26822,7 +26822,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I72" t="s">
         <v>66</v>
@@ -27332,7 +27332,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I82" t="s">
         <v>66</v>
@@ -27383,7 +27383,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I83" t="s">
         <v>66</v>
@@ -27434,7 +27434,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I84" t="s">
         <v>66</v>
@@ -27485,7 +27485,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I85" t="s">
         <v>66</v>
@@ -27642,7 +27642,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I88" t="s">
         <v>111</v>
@@ -27748,7 +27748,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I90" t="s">
         <v>111</v>
@@ -27852,7 +27852,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I92" t="s">
         <v>111</v>
@@ -27905,7 +27905,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I93" t="s">
         <v>111</v>
@@ -27958,7 +27958,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I94" t="s">
         <v>111</v>
@@ -28064,7 +28064,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I96" t="s">
         <v>111</v>
@@ -28219,7 +28219,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I99" t="s">
         <v>111</v>
@@ -28272,7 +28272,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I100" t="s">
         <v>111</v>
@@ -28378,7 +28378,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I102" t="s">
         <v>111</v>
@@ -28431,7 +28431,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I103" t="s">
         <v>111</v>
@@ -28535,7 +28535,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I105" t="s">
         <v>111</v>
@@ -28639,7 +28639,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I107" t="s">
         <v>111</v>
@@ -29408,7 +29408,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I122" t="s">
         <v>111</v>
@@ -29561,7 +29561,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I125" t="s">
         <v>111</v>
@@ -29612,7 +29612,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I126" t="s">
         <v>111</v>
@@ -29663,7 +29663,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I127" t="s">
         <v>111</v>
@@ -29714,7 +29714,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I128" t="s">
         <v>111</v>
@@ -29867,7 +29867,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I131" t="s">
         <v>111</v>
@@ -29918,7 +29918,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I132" t="s">
         <v>111</v>
@@ -30071,7 +30071,7 @@
         <v>1</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I135" t="s">
         <v>111</v>
@@ -30428,7 +30428,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I142" t="s">
         <v>168</v>
@@ -30481,7 +30481,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I143" t="s">
         <v>168</v>
@@ -30587,7 +30587,7 @@
         <v>1</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I145" t="s">
         <v>168</v>
@@ -31009,7 +31009,7 @@
         <v>1</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I153" t="s">
         <v>168</v>
@@ -31327,7 +31327,7 @@
         <v>1</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I159" t="s">
         <v>168</v>
@@ -31380,7 +31380,7 @@
         <v>1</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I160" t="s">
         <v>168</v>
@@ -31433,7 +31433,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I161" t="s">
         <v>168</v>
@@ -31486,7 +31486,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I162" t="s">
         <v>168</v>
@@ -31539,7 +31539,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I163" t="s">
         <v>168</v>
@@ -31592,7 +31592,7 @@
         <v>1</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I164" t="s">
         <v>168</v>
@@ -31645,7 +31645,7 @@
         <v>1</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I165" t="s">
         <v>168</v>
@@ -32326,7 +32326,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I178" t="s">
         <v>201</v>
@@ -32379,7 +32379,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="I179" t="s">
         <v>201</v>
@@ -32644,7 +32644,7 @@
         <v>1</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I184" t="s">
         <v>201</v>
@@ -32801,7 +32801,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I187" t="s">
         <v>201</v>
@@ -32956,7 +32956,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I190" t="s">
         <v>22</v>
@@ -33058,7 +33058,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I192" t="s">
         <v>22</v>
@@ -33213,7 +33213,7 @@
         <v>1</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I195" t="s">
         <v>168</v>
@@ -33266,7 +33266,7 @@
         <v>1</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I196" t="s">
         <v>168</v>
@@ -33425,7 +33425,7 @@
         <v>1</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I199" t="s">
         <v>201</v>
@@ -33805,7 +33805,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="I2" t="s">
         <v>234</v>
@@ -34062,7 +34062,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -34166,7 +34166,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -34321,7 +34321,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -34529,7 +34529,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -34580,7 +34580,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -34733,7 +34733,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -35702,7 +35702,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -36275,7 +36275,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I50" t="s">
         <v>66</v>
@@ -36328,7 +36328,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I51" t="s">
         <v>66</v>
@@ -36640,7 +36640,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I57" t="s">
         <v>66</v>
@@ -36793,7 +36793,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I60" t="s">
         <v>66</v>
@@ -36895,7 +36895,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I62" t="s">
         <v>66</v>
@@ -36946,7 +36946,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I63" t="s">
         <v>66</v>
@@ -36997,7 +36997,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I64" t="s">
         <v>66</v>
@@ -37048,7 +37048,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I65" t="s">
         <v>66</v>
@@ -37099,7 +37099,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I66" t="s">
         <v>66</v>
@@ -37150,7 +37150,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I67" t="s">
         <v>66</v>
@@ -37201,7 +37201,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I68" t="s">
         <v>66</v>
@@ -37252,7 +37252,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I69" t="s">
         <v>66</v>
@@ -37303,7 +37303,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I70" t="s">
         <v>66</v>
@@ -37354,7 +37354,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I71" t="s">
         <v>66</v>
@@ -37405,7 +37405,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I72" t="s">
         <v>66</v>
@@ -37915,7 +37915,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I82" t="s">
         <v>66</v>
@@ -37966,7 +37966,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I83" t="s">
         <v>66</v>
@@ -38017,7 +38017,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I84" t="s">
         <v>66</v>
@@ -38068,7 +38068,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I85" t="s">
         <v>66</v>
@@ -38225,7 +38225,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I88" t="s">
         <v>111</v>
@@ -38331,7 +38331,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I90" t="s">
         <v>111</v>
@@ -38435,7 +38435,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I92" t="s">
         <v>111</v>
@@ -38488,7 +38488,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I93" t="s">
         <v>111</v>
@@ -38541,7 +38541,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I94" t="s">
         <v>111</v>
@@ -38647,7 +38647,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I96" t="s">
         <v>111</v>
@@ -38802,7 +38802,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I99" t="s">
         <v>111</v>
@@ -38855,7 +38855,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I100" t="s">
         <v>111</v>
@@ -38961,7 +38961,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I102" t="s">
         <v>111</v>
@@ -39014,7 +39014,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I103" t="s">
         <v>111</v>
@@ -39118,7 +39118,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I105" t="s">
         <v>111</v>
@@ -39222,7 +39222,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I107" t="s">
         <v>111</v>
@@ -39991,7 +39991,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I122" t="s">
         <v>111</v>
@@ -40144,7 +40144,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I125" t="s">
         <v>111</v>
@@ -40195,7 +40195,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I126" t="s">
         <v>111</v>
@@ -40246,7 +40246,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I127" t="s">
         <v>111</v>
@@ -40297,7 +40297,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I128" t="s">
         <v>111</v>
@@ -40450,7 +40450,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I131" t="s">
         <v>111</v>
@@ -40501,7 +40501,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I132" t="s">
         <v>111</v>
@@ -40654,7 +40654,7 @@
         <v>1</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I135" t="s">
         <v>111</v>
@@ -41011,7 +41011,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I142" t="s">
         <v>168</v>
@@ -41064,7 +41064,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I143" t="s">
         <v>168</v>
@@ -41170,7 +41170,7 @@
         <v>1</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I145" t="s">
         <v>168</v>
@@ -41592,7 +41592,7 @@
         <v>1</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I153" t="s">
         <v>168</v>
@@ -41910,7 +41910,7 @@
         <v>1</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I159" t="s">
         <v>168</v>
@@ -41963,7 +41963,7 @@
         <v>1</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I160" t="s">
         <v>168</v>
@@ -42016,7 +42016,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I161" t="s">
         <v>168</v>
@@ -42069,7 +42069,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I162" t="s">
         <v>168</v>
@@ -42122,7 +42122,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I163" t="s">
         <v>168</v>
@@ -42175,7 +42175,7 @@
         <v>1</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I164" t="s">
         <v>168</v>
@@ -42228,7 +42228,7 @@
         <v>1</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I165" t="s">
         <v>168</v>
@@ -42909,7 +42909,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I178" t="s">
         <v>201</v>
@@ -42962,7 +42962,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="I179" t="s">
         <v>201</v>
@@ -43227,7 +43227,7 @@
         <v>1</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I184" t="s">
         <v>201</v>
@@ -43384,7 +43384,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I187" t="s">
         <v>201</v>
@@ -43539,7 +43539,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I190" t="s">
         <v>22</v>
@@ -43641,7 +43641,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I192" t="s">
         <v>22</v>
@@ -43796,7 +43796,7 @@
         <v>1</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I195" t="s">
         <v>168</v>
@@ -43849,7 +43849,7 @@
         <v>1</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I196" t="s">
         <v>168</v>
@@ -44008,7 +44008,7 @@
         <v>1</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I199" t="s">
         <v>201</v>
@@ -44388,7 +44388,7 @@
         <v>1</v>
       </c>
       <c r="H2" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="I2" t="s">
         <v>234</v>
@@ -44637,7 +44637,7 @@
         <v>1</v>
       </c>
       <c r="H7" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I7" t="s">
         <v>22</v>
@@ -44737,7 +44737,7 @@
         <v>1</v>
       </c>
       <c r="H9" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I9" t="s">
         <v>22</v>
@@ -44886,7 +44886,7 @@
         <v>1</v>
       </c>
       <c r="H12" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I12" t="s">
         <v>22</v>
@@ -45086,7 +45086,7 @@
         <v>1</v>
       </c>
       <c r="H16" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I16" t="s">
         <v>22</v>
@@ -45135,7 +45135,7 @@
         <v>1</v>
       </c>
       <c r="H17" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I17" t="s">
         <v>22</v>
@@ -45282,7 +45282,7 @@
         <v>1</v>
       </c>
       <c r="H20" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I20" t="s">
         <v>22</v>
@@ -46213,7 +46213,7 @@
         <v>1</v>
       </c>
       <c r="H39" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I39" t="s">
         <v>22</v>
@@ -46764,7 +46764,7 @@
         <v>1</v>
       </c>
       <c r="H50" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I50" t="s">
         <v>66</v>
@@ -46815,7 +46815,7 @@
         <v>1</v>
       </c>
       <c r="H51" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I51" t="s">
         <v>66</v>
@@ -47115,7 +47115,7 @@
         <v>1</v>
       </c>
       <c r="H57" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I57" t="s">
         <v>66</v>
@@ -47262,7 +47262,7 @@
         <v>1</v>
       </c>
       <c r="H60" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I60" t="s">
         <v>66</v>
@@ -47360,7 +47360,7 @@
         <v>1</v>
       </c>
       <c r="H62" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I62" t="s">
         <v>66</v>
@@ -47409,7 +47409,7 @@
         <v>1</v>
       </c>
       <c r="H63" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I63" t="s">
         <v>66</v>
@@ -47458,7 +47458,7 @@
         <v>1</v>
       </c>
       <c r="H64" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I64" t="s">
         <v>66</v>
@@ -47507,7 +47507,7 @@
         <v>1</v>
       </c>
       <c r="H65" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="I65" t="s">
         <v>66</v>
@@ -47556,7 +47556,7 @@
         <v>1</v>
       </c>
       <c r="H66" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I66" t="s">
         <v>66</v>
@@ -47605,7 +47605,7 @@
         <v>1</v>
       </c>
       <c r="H67" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I67" t="s">
         <v>66</v>
@@ -47654,7 +47654,7 @@
         <v>1</v>
       </c>
       <c r="H68" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I68" t="s">
         <v>66</v>
@@ -47703,7 +47703,7 @@
         <v>1</v>
       </c>
       <c r="H69" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="I69" t="s">
         <v>66</v>
@@ -47752,7 +47752,7 @@
         <v>1</v>
       </c>
       <c r="H70" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I70" t="s">
         <v>66</v>
@@ -47801,7 +47801,7 @@
         <v>1</v>
       </c>
       <c r="H71" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I71" t="s">
         <v>66</v>
@@ -47850,7 +47850,7 @@
         <v>1</v>
       </c>
       <c r="H72" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I72" t="s">
         <v>66</v>
@@ -48340,7 +48340,7 @@
         <v>1</v>
       </c>
       <c r="H82" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I82" t="s">
         <v>66</v>
@@ -48389,7 +48389,7 @@
         <v>1</v>
       </c>
       <c r="H83" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I83" t="s">
         <v>66</v>
@@ -48438,7 +48438,7 @@
         <v>1</v>
       </c>
       <c r="H84" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I84" t="s">
         <v>66</v>
@@ -48487,7 +48487,7 @@
         <v>1</v>
       </c>
       <c r="H85" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="I85" t="s">
         <v>66</v>
@@ -48638,7 +48638,7 @@
         <v>1</v>
       </c>
       <c r="H88" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I88" t="s">
         <v>111</v>
@@ -48740,7 +48740,7 @@
         <v>1</v>
       </c>
       <c r="H90" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I90" t="s">
         <v>111</v>
@@ -48840,7 +48840,7 @@
         <v>1</v>
       </c>
       <c r="H92" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I92" t="s">
         <v>111</v>
@@ -48891,7 +48891,7 @@
         <v>1</v>
       </c>
       <c r="H93" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I93" t="s">
         <v>111</v>
@@ -48942,7 +48942,7 @@
         <v>1</v>
       </c>
       <c r="H94" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I94" t="s">
         <v>111</v>
@@ -49044,7 +49044,7 @@
         <v>1</v>
       </c>
       <c r="H96" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I96" t="s">
         <v>111</v>
@@ -49193,7 +49193,7 @@
         <v>1</v>
       </c>
       <c r="H99" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I99" t="s">
         <v>111</v>
@@ -49244,7 +49244,7 @@
         <v>1</v>
       </c>
       <c r="H100" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I100" t="s">
         <v>111</v>
@@ -49346,7 +49346,7 @@
         <v>1</v>
       </c>
       <c r="H102" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I102" t="s">
         <v>111</v>
@@ -49397,7 +49397,7 @@
         <v>1</v>
       </c>
       <c r="H103" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I103" t="s">
         <v>111</v>
@@ -49497,7 +49497,7 @@
         <v>1</v>
       </c>
       <c r="H105" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="I105" t="s">
         <v>111</v>
@@ -49597,7 +49597,7 @@
         <v>1</v>
       </c>
       <c r="H107" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I107" t="s">
         <v>111</v>
@@ -50336,7 +50336,7 @@
         <v>1</v>
       </c>
       <c r="H122" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I122" t="s">
         <v>111</v>
@@ -50483,7 +50483,7 @@
         <v>1</v>
       </c>
       <c r="H125" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I125" t="s">
         <v>111</v>
@@ -50532,7 +50532,7 @@
         <v>1</v>
       </c>
       <c r="H126" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I126" t="s">
         <v>111</v>
@@ -50581,7 +50581,7 @@
         <v>1</v>
       </c>
       <c r="H127" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I127" t="s">
         <v>111</v>
@@ -50630,7 +50630,7 @@
         <v>1</v>
       </c>
       <c r="H128" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I128" t="s">
         <v>111</v>
@@ -50777,7 +50777,7 @@
         <v>1</v>
       </c>
       <c r="H131" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I131" t="s">
         <v>111</v>
@@ -50826,7 +50826,7 @@
         <v>1</v>
       </c>
       <c r="H132" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I132" t="s">
         <v>111</v>
@@ -50973,7 +50973,7 @@
         <v>1</v>
       </c>
       <c r="H135" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I135" t="s">
         <v>111</v>
@@ -51316,7 +51316,7 @@
         <v>1</v>
       </c>
       <c r="H142" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I142" t="s">
         <v>168</v>
@@ -51367,7 +51367,7 @@
         <v>1</v>
       </c>
       <c r="H143" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I143" t="s">
         <v>168</v>
@@ -51469,7 +51469,7 @@
         <v>1</v>
       </c>
       <c r="H145" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I145" t="s">
         <v>168</v>
@@ -51875,7 +51875,7 @@
         <v>1</v>
       </c>
       <c r="H153" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I153" t="s">
         <v>168</v>
@@ -52181,7 +52181,7 @@
         <v>1</v>
       </c>
       <c r="H159" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I159" t="s">
         <v>168</v>
@@ -52232,7 +52232,7 @@
         <v>1</v>
       </c>
       <c r="H160" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I160" t="s">
         <v>168</v>
@@ -52283,7 +52283,7 @@
         <v>1</v>
       </c>
       <c r="H161" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="I161" t="s">
         <v>168</v>
@@ -52334,7 +52334,7 @@
         <v>1</v>
       </c>
       <c r="H162" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I162" t="s">
         <v>168</v>
@@ -52385,7 +52385,7 @@
         <v>1</v>
       </c>
       <c r="H163" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I163" t="s">
         <v>168</v>
@@ -52436,7 +52436,7 @@
         <v>1</v>
       </c>
       <c r="H164" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I164" t="s">
         <v>168</v>
@@ -52487,7 +52487,7 @@
         <v>1</v>
       </c>
       <c r="H165" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I165" t="s">
         <v>168</v>
@@ -53144,7 +53144,7 @@
         <v>1</v>
       </c>
       <c r="H178" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="I178" t="s">
         <v>201</v>
@@ -53195,7 +53195,7 @@
         <v>1</v>
       </c>
       <c r="H179" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="I179" t="s">
         <v>201</v>
@@ -53450,7 +53450,7 @@
         <v>1</v>
       </c>
       <c r="H184" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="I184" t="s">
         <v>201</v>
@@ -53601,7 +53601,7 @@
         <v>1</v>
       </c>
       <c r="H187" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I187" t="s">
         <v>201</v>
@@ -53750,7 +53750,7 @@
         <v>1</v>
       </c>
       <c r="H190" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="I190" t="s">
         <v>22</v>
@@ -53848,7 +53848,7 @@
         <v>1</v>
       </c>
       <c r="H192" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="I192" t="s">
         <v>22</v>
@@ -53999,7 +53999,7 @@
         <v>1</v>
       </c>
       <c r="H195" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I195" t="s">
         <v>168</v>
@@ -54050,7 +54050,7 @@
         <v>1</v>
       </c>
       <c r="H196" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="I196" t="s">
         <v>168</v>
@@ -54207,7 +54207,7 @@
         <v>1</v>
       </c>
       <c r="H199" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="I199" t="s">
         <v>201</v>
@@ -54748,7 +54748,7 @@
         <v>27</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C5" t="n">
         <v>1</v>
@@ -54872,7 +54872,7 @@
         <v>30</v>
       </c>
       <c r="B7" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C7" t="n">
         <v>1</v>
@@ -55055,7 +55055,7 @@
         <v>33</v>
       </c>
       <c r="B10" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C10" t="n">
         <v>1</v>
@@ -55303,7 +55303,7 @@
         <v>37</v>
       </c>
       <c r="B14" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C14" t="n">
         <v>1</v>
@@ -55362,7 +55362,7 @@
         <v>39</v>
       </c>
       <c r="B15" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C15" t="n">
         <v>1</v>
@@ -55539,7 +55539,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C18" t="n">
         <v>1</v>
@@ -56660,7 +56660,7 @@
         <v>62</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C37" t="n">
         <v>1</v>
@@ -57345,7 +57345,7 @@
         <v>74</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C48" t="n">
         <v>1</v>
@@ -57410,7 +57410,7 @@
         <v>75</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C49" t="n">
         <v>1</v>
@@ -57782,7 +57782,7 @@
         <v>81</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C55" t="n">
         <v>1</v>
@@ -57959,7 +57959,7 @@
         <v>84</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C58" t="n">
         <v>1</v>
@@ -58077,7 +58077,7 @@
         <v>86</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C60" t="n">
         <v>1</v>
@@ -58136,7 +58136,7 @@
         <v>87</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C61" t="n">
         <v>1</v>
@@ -58195,7 +58195,7 @@
         <v>88</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C62" t="n">
         <v>1</v>
@@ -58254,7 +58254,7 @@
         <v>89</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="C63" t="n">
         <v>1</v>
@@ -58313,7 +58313,7 @@
         <v>90</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C64" t="n">
         <v>1</v>
@@ -58372,7 +58372,7 @@
         <v>91</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C65" t="n">
         <v>1</v>
@@ -58431,7 +58431,7 @@
         <v>92</v>
       </c>
       <c r="B66" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C66" t="n">
         <v>1</v>
@@ -58490,7 +58490,7 @@
         <v>93</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="C67" t="n">
         <v>1</v>
@@ -58549,7 +58549,7 @@
         <v>94</v>
       </c>
       <c r="B68" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C68" t="n">
         <v>1</v>
@@ -58608,7 +58608,7 @@
         <v>95</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C69" t="n">
         <v>1</v>
@@ -58667,7 +58667,7 @@
         <v>96</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C70" t="n">
         <v>1</v>
@@ -59257,7 +59257,7 @@
         <v>106</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C80" t="n">
         <v>1</v>
@@ -59316,7 +59316,7 @@
         <v>107</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C81" t="n">
         <v>1</v>
@@ -59375,7 +59375,7 @@
         <v>108</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C82" t="n">
         <v>1</v>
@@ -59434,7 +59434,7 @@
         <v>109</v>
       </c>
       <c r="B83" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="C83" t="n">
         <v>1</v>
@@ -59623,7 +59623,7 @@
         <v>113</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C86" t="n">
         <v>1</v>
@@ -59753,7 +59753,7 @@
         <v>115</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C88" t="n">
         <v>1</v>
@@ -59877,7 +59877,7 @@
         <v>117</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C90" t="n">
         <v>1</v>
@@ -59942,7 +59942,7 @@
         <v>118</v>
       </c>
       <c r="B91" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C91" t="n">
         <v>1</v>
@@ -60007,7 +60007,7 @@
         <v>119</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C92" t="n">
         <v>1</v>
@@ -60137,7 +60137,7 @@
         <v>121</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C94" t="n">
         <v>1</v>
@@ -60320,7 +60320,7 @@
         <v>124</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C97" t="n">
         <v>1</v>
@@ -60385,7 +60385,7 @@
         <v>125</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C98" t="n">
         <v>1</v>
@@ -60515,7 +60515,7 @@
         <v>127</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C100" t="n">
         <v>1</v>
@@ -60580,7 +60580,7 @@
         <v>128</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C101" t="n">
         <v>1</v>
@@ -60704,7 +60704,7 @@
         <v>130</v>
       </c>
       <c r="B103" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="C103" t="n">
         <v>1</v>
@@ -60828,7 +60828,7 @@
         <v>132</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C105" t="n">
         <v>1</v>
@@ -61725,7 +61725,7 @@
         <v>147</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C120" t="n">
         <v>1</v>
@@ -61902,7 +61902,7 @@
         <v>150</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C123" t="n">
         <v>1</v>
@@ -61961,7 +61961,7 @@
         <v>151</v>
       </c>
       <c r="B124" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C124" t="n">
         <v>1</v>
@@ -62020,7 +62020,7 @@
         <v>152</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C125" t="n">
         <v>1</v>
@@ -62079,7 +62079,7 @@
         <v>153</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C126" t="n">
         <v>1</v>
@@ -62256,7 +62256,7 @@
         <v>156</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C129" t="n">
         <v>1</v>
@@ -62315,7 +62315,7 @@
         <v>157</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C130" t="n">
         <v>1</v>
@@ -62492,7 +62492,7 @@
         <v>160</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C133" t="n">
         <v>1</v>
@@ -62905,7 +62905,7 @@
         <v>167</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C140" t="n">
         <v>1</v>
@@ -62970,7 +62970,7 @@
         <v>169</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C141" t="n">
         <v>1</v>
@@ -63100,7 +63100,7 @@
         <v>171</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C143" t="n">
         <v>1</v>
@@ -63614,7 +63614,7 @@
         <v>179</v>
       </c>
       <c r="B151" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C151" t="n">
         <v>1</v>
@@ -64004,7 +64004,7 @@
         <v>185</v>
       </c>
       <c r="B157" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C157" t="n">
         <v>1</v>
@@ -64069,7 +64069,7 @@
         <v>186</v>
       </c>
       <c r="B158" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C158" t="n">
         <v>1</v>
@@ -64134,7 +64134,7 @@
         <v>187</v>
       </c>
       <c r="B159" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="C159" t="n">
         <v>1</v>
@@ -64199,7 +64199,7 @@
         <v>188</v>
       </c>
       <c r="B160" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C160" t="n">
         <v>1</v>
@@ -64264,7 +64264,7 @@
         <v>189</v>
       </c>
       <c r="B161" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C161" t="n">
         <v>1</v>
@@ -64329,7 +64329,7 @@
         <v>190</v>
       </c>
       <c r="B162" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C162" t="n">
         <v>1</v>
@@ -64394,7 +64394,7 @@
         <v>191</v>
       </c>
       <c r="B163" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C163" t="n">
         <v>1</v>
@@ -65213,7 +65213,7 @@
         <v>207</v>
       </c>
       <c r="B176" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="C176" t="n">
         <v>1</v>
@@ -65278,7 +65278,7 @@
         <v>208</v>
       </c>
       <c r="B177" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="C177" t="n">
         <v>1</v>
@@ -65603,7 +65603,7 @@
         <v>213</v>
       </c>
       <c r="B182" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="C182" t="n">
         <v>1</v>
@@ -65792,7 +65792,7 @@
         <v>215</v>
       </c>
       <c r="B185" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C185" t="n">
         <v>1</v>
@@ -65975,7 +65975,7 @@
         <v>218</v>
       </c>
       <c r="B188" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="C188" t="n">
         <v>1</v>
@@ -66093,7 +66093,7 @@
         <v>220</v>
       </c>
       <c r="B190" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="C190" t="n">
         <v>1</v>
@@ -66276,7 +66276,7 @@
         <v>223</v>
       </c>
       <c r="B193" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C193" t="n">
         <v>1</v>
@@ -66341,7 +66341,7 @@
         <v>224</v>
       </c>
       <c r="B194" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="C194" t="n">
         <v>1</v>
@@ -66532,7 +66532,7 @@
         <v>227</v>
       </c>
       <c r="B197" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="C197" t="n">
         <v>1</v>
@@ -66920,7 +66920,7 @@
         <v>233</v>
       </c>
       <c r="B203" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="C203" t="n">
         <v>1</v>
@@ -67566,7 +67566,7 @@
         <v>1</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D8" t="s">
         <v>265</v>
@@ -67638,7 +67638,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D9" t="s">
         <v>265</v>
@@ -67710,7 +67710,7 @@
         <v>1</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D10" t="s">
         <v>265</v>
@@ -68214,7 +68214,7 @@
         <v>1</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="D17" t="s">
         <v>265</v>
@@ -68286,7 +68286,7 @@
         <v>1</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D18" t="s">
         <v>265</v>
@@ -68574,7 +68574,7 @@
         <v>1</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="D22" t="s">
         <v>265</v>
@@ -68718,7 +68718,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D24" t="s">
         <v>265</v>
@@ -68790,7 +68790,7 @@
         <v>1</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="D25" t="s">
         <v>265</v>
@@ -68862,7 +68862,7 @@
         <v>1</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D26" t="s">
         <v>265</v>
@@ -68934,7 +68934,7 @@
         <v>1</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="D27" t="s">
         <v>265</v>
@@ -69078,7 +69078,7 @@
         <v>1</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="D29" t="s">
         <v>265</v>
@@ -69150,7 +69150,7 @@
         <v>1</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D30" t="s">
         <v>265</v>
@@ -69222,7 +69222,7 @@
         <v>1</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="D31" t="s">
         <v>265</v>
@@ -69366,7 +69366,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D33" t="s">
         <v>265</v>
@@ -69438,7 +69438,7 @@
         <v>1</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D34" t="s">
         <v>265</v>
@@ -69510,7 +69510,7 @@
         <v>1</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>43324</v>
+        <v>43442</v>
       </c>
       <c r="D35" t="s">
         <v>265</v>
@@ -69582,7 +69582,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D36" t="s">
         <v>265</v>
@@ -69654,7 +69654,7 @@
         <v>1</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="D37" t="s">
         <v>265</v>
@@ -69726,7 +69726,7 @@
         <v>1</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D38" t="s">
         <v>265</v>
@@ -69870,7 +69870,7 @@
         <v>1</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D40" t="s">
         <v>265</v>
@@ -70374,7 +70374,7 @@
         <v>1</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="D47" t="s">
         <v>265</v>
@@ -70806,7 +70806,7 @@
         <v>1</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="D53" t="s">
         <v>265</v>
@@ -70878,7 +70878,7 @@
         <v>1</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="D54" t="s">
         <v>265</v>
@@ -70950,7 +70950,7 @@
         <v>1</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="D55" t="s">
         <v>265</v>
@@ -71022,7 +71022,7 @@
         <v>1</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="D56" t="s">
         <v>265</v>
@@ -71094,7 +71094,7 @@
         <v>1</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="D57" t="s">
         <v>265</v>
@@ -71166,7 +71166,7 @@
         <v>1</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="D58" t="s">
         <v>265</v>
@@ -71238,7 +71238,7 @@
         <v>1</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="D59" t="s">
         <v>265</v>
@@ -71598,7 +71598,7 @@
         <v>1</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>43322</v>
+        <v>43381</v>
       </c>
       <c r="D64" t="s">
         <v>265</v>
@@ -71670,7 +71670,7 @@
         <v>1</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>43353</v>
+        <v>43382</v>
       </c>
       <c r="D65" t="s">
         <v>265</v>
@@ -72174,7 +72174,7 @@
         <v>1</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="D72" t="s">
         <v>265</v>
@@ -72246,7 +72246,7 @@
         <v>1</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>43321</v>
+        <v>43351</v>
       </c>
       <c r="D73" t="s">
         <v>265</v>
@@ -72318,7 +72318,7 @@
         <v>1</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="D74" t="s">
         <v>265</v>
@@ -72750,7 +72750,7 @@
         <v>1</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>43348</v>
+        <v>43229</v>
       </c>
       <c r="D80" t="s">
         <v>265</v>
@@ -73678,7 +73678,7 @@
         <v>1</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D94" t="s">
         <v>265</v>
@@ -73740,7 +73740,7 @@
         <v>1</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D95" t="s">
         <v>265</v>
@@ -73926,7 +73926,7 @@
         <v>1</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D98" t="s">
         <v>265</v>
@@ -75104,7 +75104,7 @@
         <v>1</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="D117" t="s">
         <v>265</v>
@@ -75600,7 +75600,7 @@
         <v>1</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="D125" t="s">
         <v>265</v>
@@ -75786,7 +75786,7 @@
         <v>1</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>43354</v>
+        <v>43413</v>
       </c>
       <c r="D128" t="s">
         <v>265</v>
@@ -75910,7 +75910,7 @@
         <v>1</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="D130" t="s">
         <v>265</v>
@@ -75972,7 +75972,7 @@
         <v>1</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="D131" t="s">
         <v>265</v>
@@ -76034,7 +76034,7 @@
         <v>1</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="D132" t="s">
         <v>265</v>
@@ -76096,7 +76096,7 @@
         <v>1</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>43291</v>
+        <v>43380</v>
       </c>
       <c r="D133" t="s">
         <v>265</v>
@@ -76158,7 +76158,7 @@
         <v>1</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="D134" t="s">
         <v>265</v>
@@ -76220,7 +76220,7 @@
         <v>1</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="D135" t="s">
         <v>265</v>
@@ -76282,7 +76282,7 @@
         <v>1</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="D136" t="s">
         <v>265</v>
@@ -76344,7 +76344,7 @@
         <v>1</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>43292</v>
+        <v>43411</v>
       </c>
       <c r="D137" t="s">
         <v>265</v>
@@ -76406,7 +76406,7 @@
         <v>1</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D138" t="s">
         <v>265</v>
@@ -76468,7 +76468,7 @@
         <v>1</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D139" t="s">
         <v>265</v>
@@ -76530,7 +76530,7 @@
         <v>1</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D140" t="s">
         <v>265</v>
@@ -77150,7 +77150,7 @@
         <v>1</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="D150" t="s">
         <v>265</v>
@@ -77212,7 +77212,7 @@
         <v>1</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="D151" t="s">
         <v>265</v>
@@ -77274,7 +77274,7 @@
         <v>1</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="D152" t="s">
         <v>265</v>
@@ -77336,7 +77336,7 @@
         <v>1</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>43313</v>
+        <v>43108</v>
       </c>
       <c r="D153" t="s">
         <v>265</v>
@@ -78514,7 +78514,7 @@
         <v>1</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D172" t="s">
         <v>265</v>
@@ -78700,7 +78700,7 @@
         <v>1</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D175" t="s">
         <v>265</v>
@@ -78762,7 +78762,7 @@
         <v>1</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D176" t="s">
         <v>265</v>
@@ -78824,7 +78824,7 @@
         <v>1</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D177" t="s">
         <v>265</v>
@@ -78886,7 +78886,7 @@
         <v>1</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D178" t="s">
         <v>265</v>
@@ -79072,7 +79072,7 @@
         <v>1</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D181" t="s">
         <v>265</v>
@@ -79134,7 +79134,7 @@
         <v>1</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D182" t="s">
         <v>265</v>
@@ -79320,7 +79320,7 @@
         <v>1</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D185" t="s">
         <v>265</v>
@@ -80064,7 +80064,7 @@
         <v>1</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>43355</v>
+        <v>43443</v>
       </c>
       <c r="D197" t="s">
         <v>265</v>
@@ -80250,7 +80250,7 @@
         <v>1</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>43293</v>
+        <v>43441</v>
       </c>
       <c r="D200" t="s">
         <v>265</v>
@@ -80374,7 +80374,7 @@
         <v>1</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>43319</v>
+        <v>43289</v>
       </c>
       <c r="D202" t="s">
         <v>265</v>
@@ -80498,7 +80498,7 @@
         <v>1</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>27581</v>
+        <v>27552</v>
       </c>
       <c r="D204" t="s">
         <v>265</v>

--- a/SQO dry run/djg test SQO BLOE output summary.xlsx
+++ b/SQO dry run/djg test SQO BLOE output summary.xlsx
@@ -13,12 +13,13 @@
     <sheet name="rivpacs" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="sqo_bloe_w_mambi" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="mambi" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="potential_mismatches" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="278" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="479">
   <si>
     <t xml:space="preserve">stationid</t>
   </si>
@@ -853,6 +854,609 @@
   <si>
     <t xml:space="preserve">No salnity data - cannot calculate M-AMBI</t>
   </si>
+  <si>
+    <t xml:space="preserve">not_on_LU_list</t>
+  </si>
+  <si>
+    <t xml:space="preserve">did_you_mean</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampelisca cristata microdentata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ericthonius sp SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Garnotia naticarum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majoidea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virgularia californica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callianax baetica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paradialychone paramollis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilargis sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pilargis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caryocorbula luteola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pinnixa franciscana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amphioplus sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumbrineris sp E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lumbrineris sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hippolyte clarki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mysida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Myidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mysidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neverita recluziana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neverita reclusiana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninoe tridentata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tellina sp B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tellina sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Virgulariidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Drilonereis sp LA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phascolion sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sigambra sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amage anops</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amphisamytha bioculata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cymatioa electilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listriella sp SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heterophoxus cf ellisi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netastoma rostratum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caprella simia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plesiocystiscus politulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pisione sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prionospio heterobranchia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syllis (spellingsyllis) nipponica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Romaleon branneri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Zeuxo normani Cmplx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Columbellidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dendraster terminalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hornellia occidentalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acanthoptilum sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polygireulima rutila</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Platymera gaudichaudii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rhepoxynius lucubrans</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Eohaustorius barnardi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Molpadia arenicola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hartmanodes sp SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solen sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microspio sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leitoscoloplos sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leitoscoloplos sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyathura munda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutiderma rotundum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chiridota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caulleriella sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hesionella mccullochae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paradialychone harrisae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parexogone molesta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panopeidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caesia fossatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Xanthidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trophoniella harrisae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmothoe fragilis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epigamia-Myrianida Cmplx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actiniaria sp 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Halosydna sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Metridium sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lottia depicta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flabelligeridae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rutidermatidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spirorbidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spirorbinae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nutricola cymata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediomastus sp 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediomastus sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirkegaardia serratiseta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmothoe sp LA1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Harmothoe sp 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haminoea sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nutricola sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petricola sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Modiolatus neglectus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serpula columbiana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Brada pilosa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Erileptus spinosus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stomatopoda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corymorphidae sp SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aricidea sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sicyoniidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kirkegaardia sp 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deltamysis holmquistae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actiniaria sp DC2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podocopa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Podocopida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kurtiella pedroana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phyllochaetopterus prolifica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Strongylocentrotus sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teinostoma sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bemlos concavus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Callipallene pacifica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polydora heterochaeta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nymphon pixellae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chaetozone hartmanae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paradoneis spinifera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmoneus sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesocrangon munitella</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naineris sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pachycerianthus fimbriatus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Euchone hancocki</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampelisciphotis podophthalma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naticidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paradoneis sp SD1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phyllophoridae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neogyptis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanystylum intermedium</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Thraciidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcteobia cf anticostiensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paradoneis lyra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Magelona sp B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Polyodontes sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vitrinella berryi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anopla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Glycera oxycephala</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leodice americana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calliostoma annulatum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Heterophoxus sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Latulambrus occidentalis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancistrosyllis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maera jerrica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calyptraeidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ampelisca cristata cristata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gammaropsis shoemakeri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crepidula fornicata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apolochus picadurus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leopecten diegensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cranopsis multistriata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Deflexilodes sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hesperonoe adventor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Here excavata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Crangonidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enopla</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scolanthus triangulus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argua sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aruga sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Caprella penantis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calocarides spinulicauda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syllis alternata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syllis hyalina</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ammothella spinifera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Byblis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Syllis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hydroides dirampha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palola paloloides</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vermiliopsis infundibulum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Volvarina taeniolata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Semelidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Styelidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phtisicinae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amphipholis pugetana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Farfantepenaeus californiensis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Melanoides tuberculata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ocinebrina circumtexta</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colomastix sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alia sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Donax californicus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyramidellidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paracerceis sp A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paracerceis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Astyris sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lasaea adansoni</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pyramidella adamsi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pseudatherospio fauchaldi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dorvillea sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amphilochidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chironomini</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Psocidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hemiptera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staphylinidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leptoconops sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penaeoidea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chionista fluctifraga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanaididae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tanaidae</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acanthomysis californica</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photis sp C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Photis sp</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ancistrosyllis hamata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cephalaspidea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haplosyllis spongicola Cmplx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nudibranchia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Salmacina tribranchiata</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Naineris quadricuspida</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ianiropsis analoga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coleoptera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Physa sp</t>
+  </si>
 </sst>
 </file>
 
@@ -2632,10 +3236,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -2644,7 +3248,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
@@ -4136,7 +4740,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -5331,13 +5935,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -5571,7 +6175,7 @@
         <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>3</v>
@@ -9316,7 +9920,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I142" t="n">
         <v>3</v>
@@ -9963,7 +10567,7 @@
         <v>2</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -13822,7 +14426,7 @@
         <v>242</v>
       </c>
       <c r="N17" t="n">
-        <v>33.9697703600652</v>
+        <v>33.5895538336782</v>
       </c>
       <c r="O17" t="s">
         <v>20</v>
@@ -13871,7 +14475,7 @@
         <v>242</v>
       </c>
       <c r="N18" t="n">
-        <v>42.4469265154747</v>
+        <v>42.1666592075788</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -13920,7 +14524,7 @@
         <v>242</v>
       </c>
       <c r="N19" t="n">
-        <v>26.7370411270221</v>
+        <v>25.5023096161838</v>
       </c>
       <c r="O19" t="s">
         <v>20</v>
@@ -14018,7 +14622,7 @@
         <v>242</v>
       </c>
       <c r="N21" t="n">
-        <v>32.2459417423192</v>
+        <v>32.0513491485474</v>
       </c>
       <c r="O21" t="s">
         <v>20</v>
@@ -14361,7 +14965,7 @@
         <v>242</v>
       </c>
       <c r="N28" t="n">
-        <v>21.5154834181272</v>
+        <v>20.7449030042881</v>
       </c>
       <c r="O28" t="s">
         <v>20</v>
@@ -14753,7 +15357,7 @@
         <v>242</v>
       </c>
       <c r="N36" t="n">
-        <v>57.4863757949222</v>
+        <v>55.8193672483401</v>
       </c>
       <c r="O36" t="s">
         <v>42</v>
@@ -14802,7 +15406,7 @@
         <v>242</v>
       </c>
       <c r="N37" t="n">
-        <v>43.7748376827739</v>
+        <v>43.4772409388251</v>
       </c>
       <c r="O37" t="s">
         <v>26</v>
@@ -14900,7 +15504,7 @@
         <v>242</v>
       </c>
       <c r="N39" t="n">
-        <v>46.2484492144239</v>
+        <v>45.4203998847961</v>
       </c>
       <c r="O39" t="s">
         <v>26</v>
@@ -15096,7 +15700,7 @@
         <v>242</v>
       </c>
       <c r="N43" t="n">
-        <v>32.7738773952884</v>
+        <v>31.9268400322133</v>
       </c>
       <c r="O43" t="s">
         <v>20</v>
@@ -15402,7 +16006,7 @@
         <v>242</v>
       </c>
       <c r="N49" t="n">
-        <v>44.0394315292482</v>
+        <v>43.5912415766671</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
@@ -15453,7 +16057,7 @@
         <v>242</v>
       </c>
       <c r="N50" t="n">
-        <v>54.593701476202</v>
+        <v>54.6204517521314</v>
       </c>
       <c r="O50" t="s">
         <v>42</v>
@@ -15553,7 +16157,7 @@
         <v>242</v>
       </c>
       <c r="N52" t="n">
-        <v>38.5797223342776</v>
+        <v>38.077337750763</v>
       </c>
       <c r="O52" t="s">
         <v>20</v>
@@ -15653,13 +16257,13 @@
         <v>242</v>
       </c>
       <c r="N54" t="n">
-        <v>41.1151784188755</v>
+        <v>39.7240197376182</v>
       </c>
       <c r="O54" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P54" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q54"/>
     </row>
@@ -15802,7 +16406,7 @@
         <v>242</v>
       </c>
       <c r="N57" t="n">
-        <v>44.2645082796971</v>
+        <v>43.9525013015552</v>
       </c>
       <c r="O57" t="s">
         <v>26</v>
@@ -16047,7 +16651,7 @@
         <v>242</v>
       </c>
       <c r="N62" t="n">
-        <v>46.8718604742481</v>
+        <v>46.432675099521</v>
       </c>
       <c r="O62" t="s">
         <v>26</v>
@@ -16096,7 +16700,7 @@
         <v>242</v>
       </c>
       <c r="N63" t="n">
-        <v>57.8461293200658</v>
+        <v>56.0213317188235</v>
       </c>
       <c r="O63" t="s">
         <v>42</v>
@@ -16145,7 +16749,7 @@
         <v>242</v>
       </c>
       <c r="N64" t="n">
-        <v>62.6880989195223</v>
+        <v>59.9658581379792</v>
       </c>
       <c r="O64" t="s">
         <v>42</v>
@@ -16194,7 +16798,7 @@
         <v>242</v>
       </c>
       <c r="N65" t="n">
-        <v>37.8755232951499</v>
+        <v>37.4187203998449</v>
       </c>
       <c r="O65" t="s">
         <v>20</v>
@@ -16488,7 +17092,7 @@
         <v>242</v>
       </c>
       <c r="N71" t="n">
-        <v>34.2825329082141</v>
+        <v>33.7982636365621</v>
       </c>
       <c r="O71" t="s">
         <v>20</v>
@@ -16537,7 +17141,7 @@
         <v>242</v>
       </c>
       <c r="N72" t="n">
-        <v>31.2955291311754</v>
+        <v>30.3589465861107</v>
       </c>
       <c r="O72" t="s">
         <v>20</v>
@@ -16684,13 +17288,13 @@
         <v>242</v>
       </c>
       <c r="N75" t="n">
-        <v>40.3290087302363</v>
+        <v>39.7513161173131</v>
       </c>
       <c r="O75" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="P75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q75"/>
     </row>
@@ -16831,7 +17435,7 @@
         <v>242</v>
       </c>
       <c r="N78" t="n">
-        <v>53.5737911776543</v>
+        <v>53.54750235917</v>
       </c>
       <c r="O78" t="s">
         <v>42</v>
@@ -16880,7 +17484,7 @@
         <v>242</v>
       </c>
       <c r="N79" t="n">
-        <v>53.0463318602157</v>
+        <v>52.9669856903712</v>
       </c>
       <c r="O79" t="s">
         <v>42</v>
@@ -17076,7 +17680,7 @@
         <v>242</v>
       </c>
       <c r="N83" t="n">
-        <v>56.2859324071618</v>
+        <v>56.3770858486722</v>
       </c>
       <c r="O83" t="s">
         <v>42</v>
@@ -17125,7 +17729,7 @@
         <v>242</v>
       </c>
       <c r="N84" t="n">
-        <v>52.5511471646297</v>
+        <v>52.3774861341432</v>
       </c>
       <c r="O84" t="s">
         <v>42</v>
@@ -17378,7 +17982,7 @@
         <v>242</v>
       </c>
       <c r="N89" t="n">
-        <v>31.3979309943615</v>
+        <v>30.809416631158</v>
       </c>
       <c r="O89" t="s">
         <v>20</v>
@@ -17580,7 +18184,7 @@
         <v>242</v>
       </c>
       <c r="N93" t="n">
-        <v>4.78397879213011</v>
+        <v>4.02634237830541</v>
       </c>
       <c r="O93" t="s">
         <v>20</v>
@@ -17682,7 +18286,7 @@
         <v>242</v>
       </c>
       <c r="N95" t="n">
-        <v>17.5891857612011</v>
+        <v>16.8387514547085</v>
       </c>
       <c r="O95" t="s">
         <v>20</v>
@@ -18680,7 +19284,7 @@
         <v>242</v>
       </c>
       <c r="N115" t="n">
-        <v>20.6405849047233</v>
+        <v>20.2154360107962</v>
       </c>
       <c r="O115" t="s">
         <v>20</v>
@@ -19415,7 +20019,7 @@
         <v>242</v>
       </c>
       <c r="N130" t="n">
-        <v>41.9807099288077</v>
+        <v>41.4980276447431</v>
       </c>
       <c r="O130" t="s">
         <v>26</v>
@@ -19513,7 +20117,7 @@
         <v>242</v>
       </c>
       <c r="N132" t="n">
-        <v>45.3376123556685</v>
+        <v>44.9067281549152</v>
       </c>
       <c r="O132" t="s">
         <v>26</v>
@@ -19856,7 +20460,7 @@
         <v>242</v>
       </c>
       <c r="N139" t="n">
-        <v>42.4230650178746</v>
+        <v>42.1626199947267</v>
       </c>
       <c r="O139" t="s">
         <v>26</v>
@@ -20056,7 +20660,7 @@
         <v>242</v>
       </c>
       <c r="N143" t="n">
-        <v>68.1876518214113</v>
+        <v>63.4799679110741</v>
       </c>
       <c r="O143" t="s">
         <v>42</v>
@@ -20107,7 +20711,7 @@
         <v>242</v>
       </c>
       <c r="N144" t="n">
-        <v>46.0604562850646</v>
+        <v>45.6671774335875</v>
       </c>
       <c r="O144" t="s">
         <v>26</v>
@@ -20207,7 +20811,7 @@
         <v>242</v>
       </c>
       <c r="N146" t="n">
-        <v>47.2565507810849</v>
+        <v>46.0093050796232</v>
       </c>
       <c r="O146" t="s">
         <v>26</v>
@@ -20513,7 +21117,7 @@
         <v>242</v>
       </c>
       <c r="N152" t="n">
-        <v>42.9836210661531</v>
+        <v>42.4194933680008</v>
       </c>
       <c r="O152" t="s">
         <v>26</v>
@@ -20615,7 +21219,7 @@
         <v>242</v>
       </c>
       <c r="N154" t="n">
-        <v>41.6660057447824</v>
+        <v>41.4317883481121</v>
       </c>
       <c r="O154" t="s">
         <v>26</v>
@@ -20666,7 +21270,7 @@
         <v>242</v>
       </c>
       <c r="N155" t="n">
-        <v>47.6826464123334</v>
+        <v>47.2921470686118</v>
       </c>
       <c r="O155" t="s">
         <v>26</v>
@@ -20717,7 +21321,7 @@
         <v>242</v>
       </c>
       <c r="N156" t="n">
-        <v>44.2227130443011</v>
+        <v>43.8045730296478</v>
       </c>
       <c r="O156" t="s">
         <v>26</v>
@@ -21074,7 +21678,7 @@
         <v>242</v>
       </c>
       <c r="N163" t="n">
-        <v>47.5424121211345</v>
+        <v>46.8395688000563</v>
       </c>
       <c r="O163" t="s">
         <v>26</v>
@@ -21125,7 +21729,7 @@
         <v>242</v>
       </c>
       <c r="N164" t="n">
-        <v>51.1126212670072</v>
+        <v>50.9404575075729</v>
       </c>
       <c r="O164" t="s">
         <v>42</v>
@@ -21176,7 +21780,7 @@
         <v>242</v>
       </c>
       <c r="N165" t="n">
-        <v>49.4444629115014</v>
+        <v>49.2880989199958</v>
       </c>
       <c r="O165" t="s">
         <v>42</v>
@@ -21525,7 +22129,7 @@
         <v>242</v>
       </c>
       <c r="N172" t="n">
-        <v>44.5129157272546</v>
+        <v>44.2789509659073</v>
       </c>
       <c r="O172" t="s">
         <v>26</v>
@@ -21827,7 +22431,7 @@
         <v>242</v>
       </c>
       <c r="N178" t="n">
-        <v>64.0567320807063</v>
+        <v>63.155869695152</v>
       </c>
       <c r="O178" t="s">
         <v>42</v>
@@ -22182,7 +22786,7 @@
         <v>242</v>
       </c>
       <c r="N185" t="n">
-        <v>41.7268992562071</v>
+        <v>41.4057492247746</v>
       </c>
       <c r="O185" t="s">
         <v>26</v>
@@ -22233,7 +22837,7 @@
         <v>242</v>
       </c>
       <c r="N186" t="n">
-        <v>43.764771987482</v>
+        <v>43.6196078308323</v>
       </c>
       <c r="O186" t="s">
         <v>26</v>
@@ -22529,7 +23133,7 @@
         <v>242</v>
       </c>
       <c r="N192" t="n">
-        <v>41.7027444687709</v>
+        <v>41.405714948948</v>
       </c>
       <c r="O192" t="s">
         <v>26</v>
@@ -22680,7 +23284,7 @@
         <v>242</v>
       </c>
       <c r="N195" t="n">
-        <v>33.1764519722665</v>
+        <v>31.0606820011508</v>
       </c>
       <c r="O195" t="s">
         <v>20</v>
@@ -22731,7 +23335,7 @@
         <v>242</v>
       </c>
       <c r="N196" t="n">
-        <v>64.9895164357706</v>
+        <v>62.8276173246879</v>
       </c>
       <c r="O196" t="s">
         <v>42</v>
@@ -34596,7 +35200,7 @@
         <v>247</v>
       </c>
       <c r="N17" t="n">
-        <v>0.268846598457712</v>
+        <v>0.259308978929939</v>
       </c>
       <c r="O17" t="s">
         <v>26</v>
@@ -34647,7 +35251,7 @@
         <v>247</v>
       </c>
       <c r="N18" t="n">
-        <v>0.222701211551793</v>
+        <v>0.22485494504881</v>
       </c>
       <c r="O18" t="s">
         <v>26</v>
@@ -34698,7 +35302,7 @@
         <v>247</v>
       </c>
       <c r="N19" t="n">
-        <v>0.1556254892178</v>
+        <v>0.146056384218053</v>
       </c>
       <c r="O19" t="s">
         <v>42</v>
@@ -34800,7 +35404,7 @@
         <v>247</v>
       </c>
       <c r="N21" t="n">
-        <v>0.767083414916195</v>
+        <v>0.769237148413212</v>
       </c>
       <c r="O21" t="s">
         <v>20</v>
@@ -35157,13 +35761,13 @@
         <v>247</v>
       </c>
       <c r="N28" t="n">
-        <v>0.164997101332174</v>
+        <v>0.155459481804401</v>
       </c>
       <c r="O28" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="s">
         <v>246</v>
@@ -35565,7 +36169,7 @@
         <v>247</v>
       </c>
       <c r="N36" t="n">
-        <v>0.0691215089000718</v>
+        <v>0.0712752423970888</v>
       </c>
       <c r="O36" t="s">
         <v>38</v>
@@ -35616,7 +36220,7 @@
         <v>247</v>
       </c>
       <c r="N37" t="n">
-        <v>0.0886070768034991</v>
+        <v>0.079069457275726</v>
       </c>
       <c r="O37" t="s">
         <v>38</v>
@@ -35718,7 +36322,7 @@
         <v>247</v>
       </c>
       <c r="N39" t="n">
-        <v>0.184857355282135</v>
+        <v>0.17712712905967</v>
       </c>
       <c r="O39" t="s">
         <v>26</v>
@@ -35769,7 +36373,7 @@
         <v>247</v>
       </c>
       <c r="N40" t="n">
-        <v>0.215128700957437</v>
+        <v>0.21297496746042</v>
       </c>
       <c r="O40" t="s">
         <v>26</v>
@@ -35922,7 +36526,7 @@
         <v>247</v>
       </c>
       <c r="N43" t="n">
-        <v>0.376271715257496</v>
+        <v>0.366545182897882</v>
       </c>
       <c r="O43" t="s">
         <v>20</v>
@@ -36240,7 +36844,7 @@
         <v>247</v>
       </c>
       <c r="N49" t="n">
-        <v>0.260580547722678</v>
+        <v>0.249468654596229</v>
       </c>
       <c r="O49" t="s">
         <v>26</v>
@@ -36293,7 +36897,7 @@
         <v>247</v>
       </c>
       <c r="N50" t="n">
-        <v>0.179415722899961</v>
+        <v>0.162101191794728</v>
       </c>
       <c r="O50" t="s">
         <v>26</v>
@@ -36501,7 +37105,7 @@
         <v>247</v>
       </c>
       <c r="N54" t="n">
-        <v>0.33830590087263</v>
+        <v>0.328371691612019</v>
       </c>
       <c r="O54" t="s">
         <v>20</v>
@@ -36656,7 +37260,7 @@
         <v>247</v>
       </c>
       <c r="N57" t="n">
-        <v>0.190626520859961</v>
+        <v>0.180679590196532</v>
       </c>
       <c r="O57" t="s">
         <v>26</v>
@@ -36911,7 +37515,7 @@
         <v>247</v>
       </c>
       <c r="N62" t="n">
-        <v>0.105296939090127</v>
+        <v>0.0951296101228833</v>
       </c>
       <c r="O62" t="s">
         <v>42</v>
@@ -36962,7 +37566,7 @@
         <v>247</v>
       </c>
       <c r="N63" t="n">
-        <v>0.070268181996529</v>
+        <v>0.0724219154935461</v>
       </c>
       <c r="O63" t="s">
         <v>38</v>
@@ -37013,7 +37617,7 @@
         <v>247</v>
       </c>
       <c r="N64" t="n">
-        <v>0.0405938721222338</v>
+        <v>0.0427476056192509</v>
       </c>
       <c r="O64" t="s">
         <v>38</v>
@@ -37064,7 +37668,7 @@
         <v>247</v>
       </c>
       <c r="N65" t="n">
-        <v>0.284180950442367</v>
+        <v>0.286334683939384</v>
       </c>
       <c r="O65" t="s">
         <v>20</v>
@@ -37370,7 +37974,7 @@
         <v>247</v>
       </c>
       <c r="N71" t="n">
-        <v>0.218780811411917</v>
+        <v>0.208991308108356</v>
       </c>
       <c r="O71" t="s">
         <v>26</v>
@@ -37421,7 +38025,7 @@
         <v>247</v>
       </c>
       <c r="N72" t="n">
-        <v>0.39747276752</v>
+        <v>0.385668194010133</v>
       </c>
       <c r="O72" t="s">
         <v>20</v>
@@ -37574,7 +38178,7 @@
         <v>247</v>
       </c>
       <c r="N75" t="n">
-        <v>0.524923362195977</v>
+        <v>0.513905925485448</v>
       </c>
       <c r="O75" t="s">
         <v>20</v>
@@ -37727,7 +38331,7 @@
         <v>247</v>
       </c>
       <c r="N78" t="n">
-        <v>0.149307052633191</v>
+        <v>0.139674976689497</v>
       </c>
       <c r="O78" t="s">
         <v>42</v>
@@ -37778,13 +38382,13 @@
         <v>247</v>
       </c>
       <c r="N79" t="n">
-        <v>0.169662494081197</v>
+        <v>0.158739513786589</v>
       </c>
       <c r="O79" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P79" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q79" t="s">
         <v>246</v>
@@ -37982,7 +38586,7 @@
         <v>247</v>
       </c>
       <c r="N83" t="n">
-        <v>0.137260599508845</v>
+        <v>0.127502581677258</v>
       </c>
       <c r="O83" t="s">
         <v>42</v>
@@ -38033,7 +38637,7 @@
         <v>247</v>
       </c>
       <c r="N84" t="n">
-        <v>0.137562189816131</v>
+        <v>0.126576238577575</v>
       </c>
       <c r="O84" t="s">
         <v>42</v>
@@ -38296,7 +38900,7 @@
         <v>247</v>
       </c>
       <c r="N89" t="n">
-        <v>0.113191916879131</v>
+        <v>0.103654297351358</v>
       </c>
       <c r="O89" t="s">
         <v>42</v>
@@ -38506,7 +39110,7 @@
         <v>247</v>
       </c>
       <c r="N93" t="n">
-        <v>0.309964655544375</v>
+        <v>0.300427036016602</v>
       </c>
       <c r="O93" t="s">
         <v>20</v>
@@ -38612,7 +39216,7 @@
         <v>247</v>
       </c>
       <c r="N95" t="n">
-        <v>0.230115776843453</v>
+        <v>0.220546671843706</v>
       </c>
       <c r="O95" t="s">
         <v>26</v>
@@ -39650,7 +40254,7 @@
         <v>247</v>
       </c>
       <c r="N115" t="n">
-        <v>0.537419825098754</v>
+        <v>0.527882205570981</v>
       </c>
       <c r="O115" t="s">
         <v>20</v>
@@ -40415,7 +41019,7 @@
         <v>247</v>
       </c>
       <c r="N130" t="n">
-        <v>0.120700277449766</v>
+        <v>0.122854010946783</v>
       </c>
       <c r="O130" t="s">
         <v>42</v>
@@ -40517,7 +41121,7 @@
         <v>247</v>
       </c>
       <c r="N132" t="n">
-        <v>0.325187077044333</v>
+        <v>0.315429059212746</v>
       </c>
       <c r="O132" t="s">
         <v>20</v>
@@ -40874,7 +41478,7 @@
         <v>247</v>
       </c>
       <c r="N139" t="n">
-        <v>0.26065424001775</v>
+        <v>0.251022164074056</v>
       </c>
       <c r="O139" t="s">
         <v>26</v>
@@ -41082,7 +41686,7 @@
         <v>247</v>
       </c>
       <c r="N143" t="n">
-        <v>0.290629634380407</v>
+        <v>0.292783367877424</v>
       </c>
       <c r="O143" t="s">
         <v>20</v>
@@ -41135,13 +41739,13 @@
         <v>247</v>
       </c>
       <c r="N144" t="n">
-        <v>0.270779186660168</v>
+        <v>0.263206387797571</v>
       </c>
       <c r="O144" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q144" t="s">
         <v>246</v>
@@ -41239,7 +41843,7 @@
         <v>247</v>
       </c>
       <c r="N146" t="n">
-        <v>0.0509598232343507</v>
+        <v>0.0531135567313678</v>
       </c>
       <c r="O146" t="s">
         <v>38</v>
@@ -41557,7 +42161,7 @@
         <v>247</v>
       </c>
       <c r="N152" t="n">
-        <v>0.21261514289506</v>
+        <v>0.200936511273087</v>
       </c>
       <c r="O152" t="s">
         <v>26</v>
@@ -41663,7 +42267,7 @@
         <v>247</v>
       </c>
       <c r="N154" t="n">
-        <v>0.263746734082273</v>
+        <v>0.254020201722659</v>
       </c>
       <c r="O154" t="s">
         <v>26</v>
@@ -41716,13 +42320,13 @@
         <v>247</v>
       </c>
       <c r="N155" t="n">
-        <v>0.167335131609153</v>
+        <v>0.157136317169936</v>
       </c>
       <c r="O155" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="P155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q155" t="s">
         <v>246</v>
@@ -41769,7 +42373,7 @@
         <v>247</v>
       </c>
       <c r="N156" t="n">
-        <v>0.141097025230054</v>
+        <v>0.131339007398466</v>
       </c>
       <c r="O156" t="s">
         <v>42</v>
@@ -42140,7 +42744,7 @@
         <v>247</v>
       </c>
       <c r="N163" t="n">
-        <v>0.15910476374825</v>
+        <v>0.148402181757456</v>
       </c>
       <c r="O163" t="s">
         <v>42</v>
@@ -42193,7 +42797,7 @@
         <v>247</v>
       </c>
       <c r="N164" t="n">
-        <v>0.114401969821768</v>
+        <v>0.104675437462154</v>
       </c>
       <c r="O164" t="s">
         <v>42</v>
@@ -42246,7 +42850,7 @@
         <v>247</v>
       </c>
       <c r="N165" t="n">
-        <v>0.442761721742997</v>
+        <v>0.43309816032733</v>
       </c>
       <c r="O165" t="s">
         <v>20</v>
@@ -42609,7 +43213,7 @@
         <v>247</v>
       </c>
       <c r="N172" t="n">
-        <v>0.147779650823862</v>
+        <v>0.138242031296089</v>
       </c>
       <c r="O172" t="s">
         <v>42</v>
@@ -42927,7 +43531,7 @@
         <v>247</v>
       </c>
       <c r="N178" t="n">
-        <v>0.134465427814962</v>
+        <v>0.127081541784206</v>
       </c>
       <c r="O178" t="s">
         <v>42</v>
@@ -43296,7 +43900,7 @@
         <v>247</v>
       </c>
       <c r="N185" t="n">
-        <v>0.194796130774354</v>
+        <v>0.196949864271371</v>
       </c>
       <c r="O185" t="s">
         <v>26</v>
@@ -43349,7 +43953,7 @@
         <v>247</v>
       </c>
       <c r="N186" t="n">
-        <v>0.279962344351872</v>
+        <v>0.270393239352125</v>
       </c>
       <c r="O186" t="s">
         <v>20</v>
@@ -43555,7 +44159,7 @@
         <v>247</v>
       </c>
       <c r="N190" t="n">
-        <v>0.283314893030146</v>
+        <v>0.281161159533129</v>
       </c>
       <c r="O190" t="s">
         <v>20</v>
@@ -43657,7 +44261,7 @@
         <v>247</v>
       </c>
       <c r="N192" t="n">
-        <v>0.774077563894637</v>
+        <v>0.764288060591076</v>
       </c>
       <c r="O192" t="s">
         <v>20</v>
@@ -43814,7 +44418,7 @@
         <v>247</v>
       </c>
       <c r="N195" t="n">
-        <v>0.181962323396149</v>
+        <v>0.166851775329063</v>
       </c>
       <c r="O195" t="s">
         <v>26</v>
@@ -43867,7 +44471,7 @@
         <v>247</v>
       </c>
       <c r="N196" t="n">
-        <v>0.312694373565611</v>
+        <v>0.314848107062628</v>
       </c>
       <c r="O196" t="s">
         <v>20</v>
@@ -56017,10 +56621,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c r="F26" t="n">
         <v>1</v>
@@ -56029,7 +56633,7 @@
         <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
@@ -57605,7 +58209,7 @@
         <v>26</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G52" t="n">
         <v>2</v>
@@ -58850,13 +59454,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G73" t="n">
         <v>1</v>
@@ -59098,7 +59702,7 @@
         <v>2</v>
       </c>
       <c r="H77" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I77" t="n">
         <v>3</v>
@@ -63053,7 +63657,7 @@
         <v>2</v>
       </c>
       <c r="H142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I142" t="n">
         <v>3</v>
@@ -63762,7 +64366,7 @@
         <v>2</v>
       </c>
       <c r="H153" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I153" t="n">
         <v>1</v>
@@ -80564,4 +81168,8015 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" t="s">
+        <v>278</v>
+      </c>
+      <c r="D1" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>281</v>
+      </c>
+      <c r="D3"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D5" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>285</v>
+      </c>
+      <c r="D6"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>280</v>
+      </c>
+      <c r="D7"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>24</v>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="s">
+        <v>286</v>
+      </c>
+      <c r="D8"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>287</v>
+      </c>
+      <c r="D9"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" t="n">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>288</v>
+      </c>
+      <c r="D10" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>285</v>
+      </c>
+      <c r="D11"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>25</v>
+      </c>
+      <c r="B12" t="n">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>25</v>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="s">
+        <v>291</v>
+      </c>
+      <c r="D13"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" t="n">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>285</v>
+      </c>
+      <c r="D14"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>292</v>
+      </c>
+      <c r="D15"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>27</v>
+      </c>
+      <c r="B16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>293</v>
+      </c>
+      <c r="D16" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>29</v>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>280</v>
+      </c>
+      <c r="D17"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="s">
+        <v>295</v>
+      </c>
+      <c r="D18"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="s">
+        <v>296</v>
+      </c>
+      <c r="D19" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="s">
+        <v>296</v>
+      </c>
+      <c r="D20" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="s">
+        <v>299</v>
+      </c>
+      <c r="D21" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>29</v>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>288</v>
+      </c>
+      <c r="D22" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>291</v>
+      </c>
+      <c r="D23"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>301</v>
+      </c>
+      <c r="D25"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>30</v>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>302</v>
+      </c>
+      <c r="D26" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>304</v>
+      </c>
+      <c r="D27"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>31</v>
+      </c>
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>285</v>
+      </c>
+      <c r="D29"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>32</v>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>32</v>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="s">
+        <v>280</v>
+      </c>
+      <c r="D31"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>33</v>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="s">
+        <v>302</v>
+      </c>
+      <c r="D32" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>33</v>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="s">
+        <v>304</v>
+      </c>
+      <c r="D33"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="s">
+        <v>301</v>
+      </c>
+      <c r="D34"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" t="s">
+        <v>280</v>
+      </c>
+      <c r="D35"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>33</v>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="s">
+        <v>291</v>
+      </c>
+      <c r="D36"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>34</v>
+      </c>
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="s">
+        <v>291</v>
+      </c>
+      <c r="D37"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>34</v>
+      </c>
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="s">
+        <v>280</v>
+      </c>
+      <c r="D38"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>34</v>
+      </c>
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="s">
+        <v>305</v>
+      </c>
+      <c r="D39"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>34</v>
+      </c>
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="s">
+        <v>299</v>
+      </c>
+      <c r="D40" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>34</v>
+      </c>
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="s">
+        <v>301</v>
+      </c>
+      <c r="D41"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="s">
+        <v>306</v>
+      </c>
+      <c r="D42"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>34</v>
+      </c>
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="s">
+        <v>307</v>
+      </c>
+      <c r="D43"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="s">
+        <v>307</v>
+      </c>
+      <c r="D44"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="s">
+        <v>35</v>
+      </c>
+      <c r="B45" t="n">
+        <v>1</v>
+      </c>
+      <c r="C45" t="s">
+        <v>308</v>
+      </c>
+      <c r="D45"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="s">
+        <v>35</v>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="s">
+        <v>280</v>
+      </c>
+      <c r="D46"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="s">
+        <v>35</v>
+      </c>
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="s">
+        <v>309</v>
+      </c>
+      <c r="D47"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="s">
+        <v>310</v>
+      </c>
+      <c r="D48"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="s">
+        <v>35</v>
+      </c>
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="s">
+        <v>311</v>
+      </c>
+      <c r="D49"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="s">
+        <v>312</v>
+      </c>
+      <c r="D50"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51" t="n">
+        <v>1</v>
+      </c>
+      <c r="C51" t="s">
+        <v>283</v>
+      </c>
+      <c r="D51" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s">
+        <v>36</v>
+      </c>
+      <c r="B52" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" t="s">
+        <v>302</v>
+      </c>
+      <c r="D52" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="s">
+        <v>313</v>
+      </c>
+      <c r="D53"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="s">
+        <v>39</v>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="s">
+        <v>314</v>
+      </c>
+      <c r="D54"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="s">
+        <v>39</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>315</v>
+      </c>
+      <c r="D55"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="s">
+        <v>39</v>
+      </c>
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="s">
+        <v>312</v>
+      </c>
+      <c r="D56"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="s">
+        <v>39</v>
+      </c>
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="s">
+        <v>316</v>
+      </c>
+      <c r="D57"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="s">
+        <v>39</v>
+      </c>
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>317</v>
+      </c>
+      <c r="D58"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="s">
+        <v>39</v>
+      </c>
+      <c r="B59" t="n">
+        <v>1</v>
+      </c>
+      <c r="C59" t="s">
+        <v>318</v>
+      </c>
+      <c r="D59"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="s">
+        <v>39</v>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="s">
+        <v>319</v>
+      </c>
+      <c r="D60"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="s">
+        <v>320</v>
+      </c>
+      <c r="D61"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="s">
+        <v>40</v>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
+        <v>317</v>
+      </c>
+      <c r="D62"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>40</v>
+      </c>
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
+        <v>318</v>
+      </c>
+      <c r="D63"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>40</v>
+      </c>
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="s">
+        <v>321</v>
+      </c>
+      <c r="D64"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="s">
+        <v>41</v>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="s">
+        <v>322</v>
+      </c>
+      <c r="D65"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="s">
+        <v>41</v>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="s">
+        <v>323</v>
+      </c>
+      <c r="D66"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="s">
+        <v>41</v>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="s">
+        <v>324</v>
+      </c>
+      <c r="D67"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="s">
+        <v>41</v>
+      </c>
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="s">
+        <v>325</v>
+      </c>
+      <c r="D68"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="s">
+        <v>41</v>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="s">
+        <v>320</v>
+      </c>
+      <c r="D69"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="s">
+        <v>41</v>
+      </c>
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="s">
+        <v>326</v>
+      </c>
+      <c r="D70"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="s">
+        <v>41</v>
+      </c>
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>317</v>
+      </c>
+      <c r="D71"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="s">
+        <v>43</v>
+      </c>
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
+        <v>327</v>
+      </c>
+      <c r="D72"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="s">
+        <v>43</v>
+      </c>
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="s">
+        <v>328</v>
+      </c>
+      <c r="D73"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="s">
+        <v>43</v>
+      </c>
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="s">
+        <v>329</v>
+      </c>
+      <c r="D74"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="s">
+        <v>317</v>
+      </c>
+      <c r="D75"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="s">
+        <v>44</v>
+      </c>
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="s">
+        <v>330</v>
+      </c>
+      <c r="D76"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
+        <v>44</v>
+      </c>
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="s">
+        <v>318</v>
+      </c>
+      <c r="D77"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
+        <v>44</v>
+      </c>
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="s">
+        <v>331</v>
+      </c>
+      <c r="D78"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
+        <v>45</v>
+      </c>
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="s">
+        <v>293</v>
+      </c>
+      <c r="D79" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="s">
+        <v>45</v>
+      </c>
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>318</v>
+      </c>
+      <c r="D80"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>45</v>
+      </c>
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="s">
+        <v>324</v>
+      </c>
+      <c r="D81"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s">
+        <v>45</v>
+      </c>
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="s">
+        <v>283</v>
+      </c>
+      <c r="D82" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>45</v>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="s">
+        <v>332</v>
+      </c>
+      <c r="D83"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
+        <v>45</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>304</v>
+      </c>
+      <c r="D84"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
+        <v>46</v>
+      </c>
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="s">
+        <v>293</v>
+      </c>
+      <c r="D85" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
+        <v>46</v>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="s">
+        <v>330</v>
+      </c>
+      <c r="D86"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
+        <v>46</v>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="s">
+        <v>304</v>
+      </c>
+      <c r="D87"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="s">
+        <v>333</v>
+      </c>
+      <c r="D88" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="s">
+        <v>312</v>
+      </c>
+      <c r="D89"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
+        <v>50</v>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="s">
+        <v>312</v>
+      </c>
+      <c r="D90"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
+        <v>50</v>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="s">
+        <v>332</v>
+      </c>
+      <c r="D91"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="s">
+        <v>50</v>
+      </c>
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="s">
+        <v>317</v>
+      </c>
+      <c r="D92"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="s">
+        <v>51</v>
+      </c>
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="s">
+        <v>323</v>
+      </c>
+      <c r="D93"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="s">
+        <v>51</v>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="s">
+        <v>287</v>
+      </c>
+      <c r="D94"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>51</v>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="s">
+        <v>335</v>
+      </c>
+      <c r="D95"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="s">
+        <v>51</v>
+      </c>
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="s">
+        <v>336</v>
+      </c>
+      <c r="D96"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="s">
+        <v>51</v>
+      </c>
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="s">
+        <v>293</v>
+      </c>
+      <c r="D97" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="s">
+        <v>51</v>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="s">
+        <v>337</v>
+      </c>
+      <c r="D98"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="s">
+        <v>51</v>
+      </c>
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="s">
+        <v>338</v>
+      </c>
+      <c r="D99"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="s">
+        <v>51</v>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="s">
+        <v>290</v>
+      </c>
+      <c r="D100"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="s">
+        <v>51</v>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>339</v>
+      </c>
+      <c r="D101"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="s">
+        <v>51</v>
+      </c>
+      <c r="B102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="s">
+        <v>283</v>
+      </c>
+      <c r="D102" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="s">
+        <v>51</v>
+      </c>
+      <c r="B103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="s">
+        <v>340</v>
+      </c>
+      <c r="D103"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="s">
+        <v>51</v>
+      </c>
+      <c r="B104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="s">
+        <v>341</v>
+      </c>
+      <c r="D104"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="s">
+        <v>51</v>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="s">
+        <v>320</v>
+      </c>
+      <c r="D105"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="s">
+        <v>52</v>
+      </c>
+      <c r="B106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="s">
+        <v>317</v>
+      </c>
+      <c r="D106"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="s">
+        <v>52</v>
+      </c>
+      <c r="B107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="s">
+        <v>293</v>
+      </c>
+      <c r="D107" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s">
+        <v>52</v>
+      </c>
+      <c r="B108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="s">
+        <v>312</v>
+      </c>
+      <c r="D108"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="s">
+        <v>52</v>
+      </c>
+      <c r="B109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="s">
+        <v>342</v>
+      </c>
+      <c r="D109"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="s">
+        <v>52</v>
+      </c>
+      <c r="B110" t="n">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>330</v>
+      </c>
+      <c r="D110"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="s">
+        <v>53</v>
+      </c>
+      <c r="B111" t="n">
+        <v>1</v>
+      </c>
+      <c r="C111" t="s">
+        <v>332</v>
+      </c>
+      <c r="D111"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="s">
+        <v>53</v>
+      </c>
+      <c r="B112" t="n">
+        <v>1</v>
+      </c>
+      <c r="C112" t="s">
+        <v>317</v>
+      </c>
+      <c r="D112"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="s">
+        <v>53</v>
+      </c>
+      <c r="B113" t="n">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>343</v>
+      </c>
+      <c r="D113"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="s">
+        <v>53</v>
+      </c>
+      <c r="B114" t="n">
+        <v>1</v>
+      </c>
+      <c r="C114" t="s">
+        <v>283</v>
+      </c>
+      <c r="D114" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="s">
+        <v>54</v>
+      </c>
+      <c r="B115" t="n">
+        <v>1</v>
+      </c>
+      <c r="C115" t="s">
+        <v>317</v>
+      </c>
+      <c r="D115"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="s">
+        <v>54</v>
+      </c>
+      <c r="B116" t="n">
+        <v>1</v>
+      </c>
+      <c r="C116" t="s">
+        <v>342</v>
+      </c>
+      <c r="D116"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="s">
+        <v>54</v>
+      </c>
+      <c r="B117" t="n">
+        <v>1</v>
+      </c>
+      <c r="C117" t="s">
+        <v>344</v>
+      </c>
+      <c r="D117"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="s">
+        <v>54</v>
+      </c>
+      <c r="B118" t="n">
+        <v>1</v>
+      </c>
+      <c r="C118" t="s">
+        <v>345</v>
+      </c>
+      <c r="D118"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="s">
+        <v>55</v>
+      </c>
+      <c r="B119" t="n">
+        <v>1</v>
+      </c>
+      <c r="C119" t="s">
+        <v>317</v>
+      </c>
+      <c r="D119"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="s">
+        <v>55</v>
+      </c>
+      <c r="B120" t="n">
+        <v>1</v>
+      </c>
+      <c r="C120" t="s">
+        <v>342</v>
+      </c>
+      <c r="D120"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="s">
+        <v>55</v>
+      </c>
+      <c r="B121" t="n">
+        <v>1</v>
+      </c>
+      <c r="C121" t="s">
+        <v>343</v>
+      </c>
+      <c r="D121"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="s">
+        <v>56</v>
+      </c>
+      <c r="B122" t="n">
+        <v>1</v>
+      </c>
+      <c r="C122" t="s">
+        <v>317</v>
+      </c>
+      <c r="D122"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="s">
+        <v>56</v>
+      </c>
+      <c r="B123" t="n">
+        <v>1</v>
+      </c>
+      <c r="C123" t="s">
+        <v>342</v>
+      </c>
+      <c r="D123"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="s">
+        <v>56</v>
+      </c>
+      <c r="B124" t="n">
+        <v>1</v>
+      </c>
+      <c r="C124" t="s">
+        <v>346</v>
+      </c>
+      <c r="D124"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="s">
+        <v>57</v>
+      </c>
+      <c r="B125" t="n">
+        <v>1</v>
+      </c>
+      <c r="C125" t="s">
+        <v>317</v>
+      </c>
+      <c r="D125"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="s">
+        <v>57</v>
+      </c>
+      <c r="B126" t="n">
+        <v>1</v>
+      </c>
+      <c r="C126" t="s">
+        <v>345</v>
+      </c>
+      <c r="D126"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="s">
+        <v>57</v>
+      </c>
+      <c r="B127" t="n">
+        <v>1</v>
+      </c>
+      <c r="C127" t="s">
+        <v>347</v>
+      </c>
+      <c r="D127"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="s">
+        <v>57</v>
+      </c>
+      <c r="B128" t="n">
+        <v>1</v>
+      </c>
+      <c r="C128" t="s">
+        <v>346</v>
+      </c>
+      <c r="D128"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="s">
+        <v>57</v>
+      </c>
+      <c r="B129" t="n">
+        <v>1</v>
+      </c>
+      <c r="C129" t="s">
+        <v>342</v>
+      </c>
+      <c r="D129"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="s">
+        <v>57</v>
+      </c>
+      <c r="B130" t="n">
+        <v>1</v>
+      </c>
+      <c r="C130" t="s">
+        <v>287</v>
+      </c>
+      <c r="D130"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="s">
+        <v>58</v>
+      </c>
+      <c r="B131" t="n">
+        <v>1</v>
+      </c>
+      <c r="C131" t="s">
+        <v>317</v>
+      </c>
+      <c r="D131"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="s">
+        <v>58</v>
+      </c>
+      <c r="B132" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" t="s">
+        <v>330</v>
+      </c>
+      <c r="D132"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="s">
+        <v>58</v>
+      </c>
+      <c r="B133" t="n">
+        <v>1</v>
+      </c>
+      <c r="C133" t="s">
+        <v>332</v>
+      </c>
+      <c r="D133"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="s">
+        <v>58</v>
+      </c>
+      <c r="B134" t="n">
+        <v>1</v>
+      </c>
+      <c r="C134" t="s">
+        <v>342</v>
+      </c>
+      <c r="D134"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="s">
+        <v>58</v>
+      </c>
+      <c r="B135" t="n">
+        <v>1</v>
+      </c>
+      <c r="C135" t="s">
+        <v>331</v>
+      </c>
+      <c r="D135"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="s">
+        <v>59</v>
+      </c>
+      <c r="B136" t="n">
+        <v>1</v>
+      </c>
+      <c r="C136" t="s">
+        <v>348</v>
+      </c>
+      <c r="D136"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="s">
+        <v>60</v>
+      </c>
+      <c r="B137" t="n">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>346</v>
+      </c>
+      <c r="D137"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="s">
+        <v>60</v>
+      </c>
+      <c r="B138" t="n">
+        <v>1</v>
+      </c>
+      <c r="C138" t="s">
+        <v>347</v>
+      </c>
+      <c r="D138"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="s">
+        <v>60</v>
+      </c>
+      <c r="B139" t="n">
+        <v>1</v>
+      </c>
+      <c r="C139" t="s">
+        <v>349</v>
+      </c>
+      <c r="D139"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>60</v>
+      </c>
+      <c r="B140" t="n">
+        <v>1</v>
+      </c>
+      <c r="C140" t="s">
+        <v>317</v>
+      </c>
+      <c r="D140"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>60</v>
+      </c>
+      <c r="B141" t="n">
+        <v>1</v>
+      </c>
+      <c r="C141" t="s">
+        <v>320</v>
+      </c>
+      <c r="D141"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="s">
+        <v>61</v>
+      </c>
+      <c r="B142" t="n">
+        <v>1</v>
+      </c>
+      <c r="C142" t="s">
+        <v>350</v>
+      </c>
+      <c r="D142"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="s">
+        <v>61</v>
+      </c>
+      <c r="B143" t="n">
+        <v>1</v>
+      </c>
+      <c r="C143" t="s">
+        <v>351</v>
+      </c>
+      <c r="D143"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="s">
+        <v>61</v>
+      </c>
+      <c r="B144" t="n">
+        <v>1</v>
+      </c>
+      <c r="C144" t="s">
+        <v>317</v>
+      </c>
+      <c r="D144"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="s">
+        <v>61</v>
+      </c>
+      <c r="B145" t="n">
+        <v>1</v>
+      </c>
+      <c r="C145" t="s">
+        <v>342</v>
+      </c>
+      <c r="D145"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="s">
+        <v>62</v>
+      </c>
+      <c r="B146" t="n">
+        <v>1</v>
+      </c>
+      <c r="C146" t="s">
+        <v>320</v>
+      </c>
+      <c r="D146"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="s">
+        <v>62</v>
+      </c>
+      <c r="B147" t="n">
+        <v>1</v>
+      </c>
+      <c r="C147" t="s">
+        <v>317</v>
+      </c>
+      <c r="D147"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="s">
+        <v>62</v>
+      </c>
+      <c r="B148" t="n">
+        <v>1</v>
+      </c>
+      <c r="C148" t="s">
+        <v>348</v>
+      </c>
+      <c r="D148"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="s">
+        <v>62</v>
+      </c>
+      <c r="B149" t="n">
+        <v>1</v>
+      </c>
+      <c r="C149" t="s">
+        <v>352</v>
+      </c>
+      <c r="D149"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="s">
+        <v>62</v>
+      </c>
+      <c r="B150" t="n">
+        <v>1</v>
+      </c>
+      <c r="C150" t="s">
+        <v>342</v>
+      </c>
+      <c r="D150"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="s">
+        <v>62</v>
+      </c>
+      <c r="B151" t="n">
+        <v>1</v>
+      </c>
+      <c r="C151" t="s">
+        <v>353</v>
+      </c>
+      <c r="D151"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>63</v>
+      </c>
+      <c r="B152" t="n">
+        <v>1</v>
+      </c>
+      <c r="C152" t="s">
+        <v>350</v>
+      </c>
+      <c r="D152"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>63</v>
+      </c>
+      <c r="B153" t="n">
+        <v>1</v>
+      </c>
+      <c r="C153" t="s">
+        <v>354</v>
+      </c>
+      <c r="D153" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>65</v>
+      </c>
+      <c r="B154" t="n">
+        <v>1</v>
+      </c>
+      <c r="C154" t="s">
+        <v>317</v>
+      </c>
+      <c r="D154"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>65</v>
+      </c>
+      <c r="B155" t="n">
+        <v>1</v>
+      </c>
+      <c r="C155" t="s">
+        <v>356</v>
+      </c>
+      <c r="D155"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>67</v>
+      </c>
+      <c r="B156" t="n">
+        <v>1</v>
+      </c>
+      <c r="C156" t="s">
+        <v>320</v>
+      </c>
+      <c r="D156"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>67</v>
+      </c>
+      <c r="B157" t="n">
+        <v>1</v>
+      </c>
+      <c r="C157" t="s">
+        <v>357</v>
+      </c>
+      <c r="D157" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>67</v>
+      </c>
+      <c r="B158" t="n">
+        <v>1</v>
+      </c>
+      <c r="C158" t="s">
+        <v>359</v>
+      </c>
+      <c r="D158"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>67</v>
+      </c>
+      <c r="B159" t="n">
+        <v>1</v>
+      </c>
+      <c r="C159" t="s">
+        <v>360</v>
+      </c>
+      <c r="D159" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>67</v>
+      </c>
+      <c r="B160" t="n">
+        <v>1</v>
+      </c>
+      <c r="C160" t="s">
+        <v>318</v>
+      </c>
+      <c r="D160"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>67</v>
+      </c>
+      <c r="B161" t="n">
+        <v>1</v>
+      </c>
+      <c r="C161" t="s">
+        <v>362</v>
+      </c>
+      <c r="D161"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>67</v>
+      </c>
+      <c r="B162" t="n">
+        <v>1</v>
+      </c>
+      <c r="C162" t="s">
+        <v>363</v>
+      </c>
+      <c r="D162" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>73</v>
+      </c>
+      <c r="B163" t="n">
+        <v>1</v>
+      </c>
+      <c r="C163" t="s">
+        <v>320</v>
+      </c>
+      <c r="D163"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>73</v>
+      </c>
+      <c r="B164" t="n">
+        <v>1</v>
+      </c>
+      <c r="C164" t="s">
+        <v>314</v>
+      </c>
+      <c r="D164"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>73</v>
+      </c>
+      <c r="B165" t="n">
+        <v>1</v>
+      </c>
+      <c r="C165" t="s">
+        <v>317</v>
+      </c>
+      <c r="D165"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>73</v>
+      </c>
+      <c r="B166" t="n">
+        <v>1</v>
+      </c>
+      <c r="C166" t="s">
+        <v>365</v>
+      </c>
+      <c r="D166"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="s">
+        <v>74</v>
+      </c>
+      <c r="B167" t="n">
+        <v>1</v>
+      </c>
+      <c r="C167" t="s">
+        <v>320</v>
+      </c>
+      <c r="D167"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="s">
+        <v>74</v>
+      </c>
+      <c r="B168" t="n">
+        <v>1</v>
+      </c>
+      <c r="C168" t="s">
+        <v>314</v>
+      </c>
+      <c r="D168"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="s">
+        <v>74</v>
+      </c>
+      <c r="B169" t="n">
+        <v>1</v>
+      </c>
+      <c r="C169" t="s">
+        <v>359</v>
+      </c>
+      <c r="D169"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="s">
+        <v>74</v>
+      </c>
+      <c r="B170" t="n">
+        <v>1</v>
+      </c>
+      <c r="C170" t="s">
+        <v>312</v>
+      </c>
+      <c r="D170"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="s">
+        <v>74</v>
+      </c>
+      <c r="B171" t="n">
+        <v>1</v>
+      </c>
+      <c r="C171" t="s">
+        <v>318</v>
+      </c>
+      <c r="D171"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="s">
+        <v>74</v>
+      </c>
+      <c r="B172" t="n">
+        <v>1</v>
+      </c>
+      <c r="C172" t="s">
+        <v>366</v>
+      </c>
+      <c r="D172"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="s">
+        <v>75</v>
+      </c>
+      <c r="B173" t="n">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>367</v>
+      </c>
+      <c r="D173"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="s">
+        <v>75</v>
+      </c>
+      <c r="B174" t="n">
+        <v>1</v>
+      </c>
+      <c r="C174" t="s">
+        <v>286</v>
+      </c>
+      <c r="D174"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="s">
+        <v>75</v>
+      </c>
+      <c r="B175" t="n">
+        <v>1</v>
+      </c>
+      <c r="C175" t="s">
+        <v>368</v>
+      </c>
+      <c r="D175"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="s">
+        <v>75</v>
+      </c>
+      <c r="B176" t="n">
+        <v>1</v>
+      </c>
+      <c r="C176" t="s">
+        <v>317</v>
+      </c>
+      <c r="D176"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="s">
+        <v>75</v>
+      </c>
+      <c r="B177" t="n">
+        <v>1</v>
+      </c>
+      <c r="C177" t="s">
+        <v>307</v>
+      </c>
+      <c r="D177"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="s">
+        <v>76</v>
+      </c>
+      <c r="B178" t="n">
+        <v>1</v>
+      </c>
+      <c r="C178" t="s">
+        <v>317</v>
+      </c>
+      <c r="D178"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="s">
+        <v>76</v>
+      </c>
+      <c r="B179" t="n">
+        <v>1</v>
+      </c>
+      <c r="C179" t="s">
+        <v>318</v>
+      </c>
+      <c r="D179"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="s">
+        <v>76</v>
+      </c>
+      <c r="B180" t="n">
+        <v>1</v>
+      </c>
+      <c r="C180" t="s">
+        <v>354</v>
+      </c>
+      <c r="D180" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="s">
+        <v>77</v>
+      </c>
+      <c r="B181" t="n">
+        <v>1</v>
+      </c>
+      <c r="C181" t="s">
+        <v>302</v>
+      </c>
+      <c r="D181" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="s">
+        <v>78</v>
+      </c>
+      <c r="B182" t="n">
+        <v>1</v>
+      </c>
+      <c r="C182" t="s">
+        <v>320</v>
+      </c>
+      <c r="D182"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="s">
+        <v>78</v>
+      </c>
+      <c r="B183" t="n">
+        <v>1</v>
+      </c>
+      <c r="C183" t="s">
+        <v>312</v>
+      </c>
+      <c r="D183"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="s">
+        <v>78</v>
+      </c>
+      <c r="B184" t="n">
+        <v>1</v>
+      </c>
+      <c r="C184" t="s">
+        <v>317</v>
+      </c>
+      <c r="D184"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="s">
+        <v>78</v>
+      </c>
+      <c r="B185" t="n">
+        <v>1</v>
+      </c>
+      <c r="C185" t="s">
+        <v>359</v>
+      </c>
+      <c r="D185"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="s">
+        <v>80</v>
+      </c>
+      <c r="B186" t="n">
+        <v>1</v>
+      </c>
+      <c r="C186" t="s">
+        <v>348</v>
+      </c>
+      <c r="D186"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="s">
+        <v>80</v>
+      </c>
+      <c r="B187" t="n">
+        <v>1</v>
+      </c>
+      <c r="C187" t="s">
+        <v>369</v>
+      </c>
+      <c r="D187"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="s">
+        <v>81</v>
+      </c>
+      <c r="B188" t="n">
+        <v>1</v>
+      </c>
+      <c r="C188" t="s">
+        <v>348</v>
+      </c>
+      <c r="D188"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="s">
+        <v>81</v>
+      </c>
+      <c r="B189" t="n">
+        <v>1</v>
+      </c>
+      <c r="C189" t="s">
+        <v>320</v>
+      </c>
+      <c r="D189"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="s">
+        <v>81</v>
+      </c>
+      <c r="B190" t="n">
+        <v>1</v>
+      </c>
+      <c r="C190" t="s">
+        <v>357</v>
+      </c>
+      <c r="D190" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="s">
+        <v>81</v>
+      </c>
+      <c r="B191" t="n">
+        <v>1</v>
+      </c>
+      <c r="C191" t="s">
+        <v>317</v>
+      </c>
+      <c r="D191"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="s">
+        <v>84</v>
+      </c>
+      <c r="B192" t="n">
+        <v>1</v>
+      </c>
+      <c r="C192" t="s">
+        <v>370</v>
+      </c>
+      <c r="D192"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="s">
+        <v>85</v>
+      </c>
+      <c r="B193" t="n">
+        <v>1</v>
+      </c>
+      <c r="C193" t="s">
+        <v>293</v>
+      </c>
+      <c r="D193" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="s">
+        <v>85</v>
+      </c>
+      <c r="B194" t="n">
+        <v>1</v>
+      </c>
+      <c r="C194" t="s">
+        <v>371</v>
+      </c>
+      <c r="D194"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="s">
+        <v>85</v>
+      </c>
+      <c r="B195" t="n">
+        <v>1</v>
+      </c>
+      <c r="C195" t="s">
+        <v>372</v>
+      </c>
+      <c r="D195"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="s">
+        <v>86</v>
+      </c>
+      <c r="B196" t="n">
+        <v>1</v>
+      </c>
+      <c r="C196" t="s">
+        <v>320</v>
+      </c>
+      <c r="D196"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="s">
+        <v>86</v>
+      </c>
+      <c r="B197" t="n">
+        <v>1</v>
+      </c>
+      <c r="C197" t="s">
+        <v>318</v>
+      </c>
+      <c r="D197"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="s">
+        <v>86</v>
+      </c>
+      <c r="B198" t="n">
+        <v>1</v>
+      </c>
+      <c r="C198" t="s">
+        <v>314</v>
+      </c>
+      <c r="D198"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="s">
+        <v>86</v>
+      </c>
+      <c r="B199" t="n">
+        <v>1</v>
+      </c>
+      <c r="C199" t="s">
+        <v>317</v>
+      </c>
+      <c r="D199"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="s">
+        <v>87</v>
+      </c>
+      <c r="B200" t="n">
+        <v>1</v>
+      </c>
+      <c r="C200" t="s">
+        <v>317</v>
+      </c>
+      <c r="D200"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="s">
+        <v>88</v>
+      </c>
+      <c r="B201" t="n">
+        <v>1</v>
+      </c>
+      <c r="C201" t="s">
+        <v>317</v>
+      </c>
+      <c r="D201"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="s">
+        <v>89</v>
+      </c>
+      <c r="B202" t="n">
+        <v>1</v>
+      </c>
+      <c r="C202" t="s">
+        <v>317</v>
+      </c>
+      <c r="D202"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="s">
+        <v>89</v>
+      </c>
+      <c r="B203" t="n">
+        <v>1</v>
+      </c>
+      <c r="C203" t="s">
+        <v>373</v>
+      </c>
+      <c r="D203"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="s">
+        <v>89</v>
+      </c>
+      <c r="B204" t="n">
+        <v>1</v>
+      </c>
+      <c r="C204" t="s">
+        <v>302</v>
+      </c>
+      <c r="D204" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="s">
+        <v>90</v>
+      </c>
+      <c r="B205" t="n">
+        <v>1</v>
+      </c>
+      <c r="C205" t="s">
+        <v>374</v>
+      </c>
+      <c r="D205"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="s">
+        <v>91</v>
+      </c>
+      <c r="B206" t="n">
+        <v>1</v>
+      </c>
+      <c r="C206" t="s">
+        <v>302</v>
+      </c>
+      <c r="D206" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="s">
+        <v>91</v>
+      </c>
+      <c r="B207" t="n">
+        <v>1</v>
+      </c>
+      <c r="C207" t="s">
+        <v>293</v>
+      </c>
+      <c r="D207" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="s">
+        <v>91</v>
+      </c>
+      <c r="B208" t="n">
+        <v>1</v>
+      </c>
+      <c r="C208" t="s">
+        <v>317</v>
+      </c>
+      <c r="D208"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="s">
+        <v>92</v>
+      </c>
+      <c r="B209" t="n">
+        <v>1</v>
+      </c>
+      <c r="C209" t="s">
+        <v>302</v>
+      </c>
+      <c r="D209" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="s">
+        <v>92</v>
+      </c>
+      <c r="B210" t="n">
+        <v>1</v>
+      </c>
+      <c r="C210" t="s">
+        <v>332</v>
+      </c>
+      <c r="D210"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="s">
+        <v>94</v>
+      </c>
+      <c r="B211" t="n">
+        <v>1</v>
+      </c>
+      <c r="C211" t="s">
+        <v>312</v>
+      </c>
+      <c r="D211"/>
+    </row>
+    <row r="212">
+      <c r="A212" t="s">
+        <v>94</v>
+      </c>
+      <c r="B212" t="n">
+        <v>1</v>
+      </c>
+      <c r="C212" t="s">
+        <v>317</v>
+      </c>
+      <c r="D212"/>
+    </row>
+    <row r="213">
+      <c r="A213" t="s">
+        <v>94</v>
+      </c>
+      <c r="B213" t="n">
+        <v>1</v>
+      </c>
+      <c r="C213" t="s">
+        <v>318</v>
+      </c>
+      <c r="D213"/>
+    </row>
+    <row r="214">
+      <c r="A214" t="s">
+        <v>94</v>
+      </c>
+      <c r="B214" t="n">
+        <v>1</v>
+      </c>
+      <c r="C214" t="s">
+        <v>302</v>
+      </c>
+      <c r="D214" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="s">
+        <v>94</v>
+      </c>
+      <c r="B215" t="n">
+        <v>1</v>
+      </c>
+      <c r="C215" t="s">
+        <v>375</v>
+      </c>
+      <c r="D215"/>
+    </row>
+    <row r="216">
+      <c r="A216" t="s">
+        <v>95</v>
+      </c>
+      <c r="B216" t="n">
+        <v>1</v>
+      </c>
+      <c r="C216" t="s">
+        <v>317</v>
+      </c>
+      <c r="D216"/>
+    </row>
+    <row r="217">
+      <c r="A217" t="s">
+        <v>95</v>
+      </c>
+      <c r="B217" t="n">
+        <v>1</v>
+      </c>
+      <c r="C217" t="s">
+        <v>318</v>
+      </c>
+      <c r="D217"/>
+    </row>
+    <row r="218">
+      <c r="A218" t="s">
+        <v>95</v>
+      </c>
+      <c r="B218" t="n">
+        <v>1</v>
+      </c>
+      <c r="C218" t="s">
+        <v>320</v>
+      </c>
+      <c r="D218"/>
+    </row>
+    <row r="219">
+      <c r="A219" t="s">
+        <v>95</v>
+      </c>
+      <c r="B219" t="n">
+        <v>1</v>
+      </c>
+      <c r="C219" t="s">
+        <v>312</v>
+      </c>
+      <c r="D219"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="s">
+        <v>95</v>
+      </c>
+      <c r="B220" t="n">
+        <v>1</v>
+      </c>
+      <c r="C220" t="s">
+        <v>376</v>
+      </c>
+      <c r="D220" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="s">
+        <v>96</v>
+      </c>
+      <c r="B221" t="n">
+        <v>1</v>
+      </c>
+      <c r="C221" t="s">
+        <v>312</v>
+      </c>
+      <c r="D221"/>
+    </row>
+    <row r="222">
+      <c r="A222" t="s">
+        <v>96</v>
+      </c>
+      <c r="B222" t="n">
+        <v>1</v>
+      </c>
+      <c r="C222" t="s">
+        <v>320</v>
+      </c>
+      <c r="D222"/>
+    </row>
+    <row r="223">
+      <c r="A223" t="s">
+        <v>96</v>
+      </c>
+      <c r="B223" t="n">
+        <v>1</v>
+      </c>
+      <c r="C223" t="s">
+        <v>318</v>
+      </c>
+      <c r="D223"/>
+    </row>
+    <row r="224">
+      <c r="A224" t="s">
+        <v>96</v>
+      </c>
+      <c r="B224" t="n">
+        <v>1</v>
+      </c>
+      <c r="C224" t="s">
+        <v>351</v>
+      </c>
+      <c r="D224"/>
+    </row>
+    <row r="225">
+      <c r="A225" t="s">
+        <v>96</v>
+      </c>
+      <c r="B225" t="n">
+        <v>1</v>
+      </c>
+      <c r="C225" t="s">
+        <v>346</v>
+      </c>
+      <c r="D225"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="s">
+        <v>96</v>
+      </c>
+      <c r="B226" t="n">
+        <v>1</v>
+      </c>
+      <c r="C226" t="s">
+        <v>378</v>
+      </c>
+      <c r="D226"/>
+    </row>
+    <row r="227">
+      <c r="A227" t="s">
+        <v>96</v>
+      </c>
+      <c r="B227" t="n">
+        <v>1</v>
+      </c>
+      <c r="C227" t="s">
+        <v>317</v>
+      </c>
+      <c r="D227"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="s">
+        <v>96</v>
+      </c>
+      <c r="B228" t="n">
+        <v>1</v>
+      </c>
+      <c r="C228" t="s">
+        <v>379</v>
+      </c>
+      <c r="D228"/>
+    </row>
+    <row r="229">
+      <c r="A229" t="s">
+        <v>96</v>
+      </c>
+      <c r="B229" t="n">
+        <v>1</v>
+      </c>
+      <c r="C229" t="s">
+        <v>380</v>
+      </c>
+      <c r="D229"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="s">
+        <v>96</v>
+      </c>
+      <c r="B230" t="n">
+        <v>1</v>
+      </c>
+      <c r="C230" t="s">
+        <v>381</v>
+      </c>
+      <c r="D230"/>
+    </row>
+    <row r="231">
+      <c r="A231" t="s">
+        <v>96</v>
+      </c>
+      <c r="B231" t="n">
+        <v>1</v>
+      </c>
+      <c r="C231" t="s">
+        <v>302</v>
+      </c>
+      <c r="D231" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="s">
+        <v>97</v>
+      </c>
+      <c r="B232" t="n">
+        <v>1</v>
+      </c>
+      <c r="C232" t="s">
+        <v>312</v>
+      </c>
+      <c r="D232"/>
+    </row>
+    <row r="233">
+      <c r="A233" t="s">
+        <v>97</v>
+      </c>
+      <c r="B233" t="n">
+        <v>1</v>
+      </c>
+      <c r="C233" t="s">
+        <v>317</v>
+      </c>
+      <c r="D233"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="s">
+        <v>97</v>
+      </c>
+      <c r="B234" t="n">
+        <v>1</v>
+      </c>
+      <c r="C234" t="s">
+        <v>382</v>
+      </c>
+      <c r="D234"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="s">
+        <v>98</v>
+      </c>
+      <c r="B235" t="n">
+        <v>1</v>
+      </c>
+      <c r="C235" t="s">
+        <v>318</v>
+      </c>
+      <c r="D235"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="s">
+        <v>98</v>
+      </c>
+      <c r="B236" t="n">
+        <v>1</v>
+      </c>
+      <c r="C236" t="s">
+        <v>325</v>
+      </c>
+      <c r="D236"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="s">
+        <v>98</v>
+      </c>
+      <c r="B237" t="n">
+        <v>1</v>
+      </c>
+      <c r="C237" t="s">
+        <v>383</v>
+      </c>
+      <c r="D237"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="s">
+        <v>98</v>
+      </c>
+      <c r="B238" t="n">
+        <v>1</v>
+      </c>
+      <c r="C238" t="s">
+        <v>330</v>
+      </c>
+      <c r="D238"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="s">
+        <v>99</v>
+      </c>
+      <c r="B239" t="n">
+        <v>1</v>
+      </c>
+      <c r="C239" t="s">
+        <v>320</v>
+      </c>
+      <c r="D239"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="s">
+        <v>99</v>
+      </c>
+      <c r="B240" t="n">
+        <v>1</v>
+      </c>
+      <c r="C240" t="s">
+        <v>312</v>
+      </c>
+      <c r="D240"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="s">
+        <v>99</v>
+      </c>
+      <c r="B241" t="n">
+        <v>1</v>
+      </c>
+      <c r="C241" t="s">
+        <v>317</v>
+      </c>
+      <c r="D241"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="s">
+        <v>99</v>
+      </c>
+      <c r="B242" t="n">
+        <v>1</v>
+      </c>
+      <c r="C242" t="s">
+        <v>314</v>
+      </c>
+      <c r="D242"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="s">
+        <v>99</v>
+      </c>
+      <c r="B243" t="n">
+        <v>1</v>
+      </c>
+      <c r="C243" t="s">
+        <v>330</v>
+      </c>
+      <c r="D243"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="s">
+        <v>99</v>
+      </c>
+      <c r="B244" t="n">
+        <v>1</v>
+      </c>
+      <c r="C244" t="s">
+        <v>318</v>
+      </c>
+      <c r="D244"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="s">
+        <v>99</v>
+      </c>
+      <c r="B245" t="n">
+        <v>1</v>
+      </c>
+      <c r="C245" t="s">
+        <v>302</v>
+      </c>
+      <c r="D245" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="s">
+        <v>100</v>
+      </c>
+      <c r="B246" t="n">
+        <v>1</v>
+      </c>
+      <c r="C246" t="s">
+        <v>317</v>
+      </c>
+      <c r="D246"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="s">
+        <v>100</v>
+      </c>
+      <c r="B247" t="n">
+        <v>1</v>
+      </c>
+      <c r="C247" t="s">
+        <v>318</v>
+      </c>
+      <c r="D247"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="s">
+        <v>100</v>
+      </c>
+      <c r="B248" t="n">
+        <v>1</v>
+      </c>
+      <c r="C248" t="s">
+        <v>332</v>
+      </c>
+      <c r="D248"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="s">
+        <v>100</v>
+      </c>
+      <c r="B249" t="n">
+        <v>1</v>
+      </c>
+      <c r="C249" t="s">
+        <v>331</v>
+      </c>
+      <c r="D249"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="s">
+        <v>101</v>
+      </c>
+      <c r="B250" t="n">
+        <v>1</v>
+      </c>
+      <c r="C250" t="s">
+        <v>312</v>
+      </c>
+      <c r="D250"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="s">
+        <v>101</v>
+      </c>
+      <c r="B251" t="n">
+        <v>1</v>
+      </c>
+      <c r="C251" t="s">
+        <v>318</v>
+      </c>
+      <c r="D251"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="s">
+        <v>102</v>
+      </c>
+      <c r="B252" t="n">
+        <v>1</v>
+      </c>
+      <c r="C252" t="s">
+        <v>312</v>
+      </c>
+      <c r="D252"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="s">
+        <v>102</v>
+      </c>
+      <c r="B253" t="n">
+        <v>1</v>
+      </c>
+      <c r="C253" t="s">
+        <v>317</v>
+      </c>
+      <c r="D253"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="s">
+        <v>102</v>
+      </c>
+      <c r="B254" t="n">
+        <v>1</v>
+      </c>
+      <c r="C254" t="s">
+        <v>320</v>
+      </c>
+      <c r="D254"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="s">
+        <v>103</v>
+      </c>
+      <c r="B255" t="n">
+        <v>1</v>
+      </c>
+      <c r="C255" t="s">
+        <v>320</v>
+      </c>
+      <c r="D255"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="s">
+        <v>103</v>
+      </c>
+      <c r="B256" t="n">
+        <v>1</v>
+      </c>
+      <c r="C256" t="s">
+        <v>312</v>
+      </c>
+      <c r="D256"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="s">
+        <v>103</v>
+      </c>
+      <c r="B257" t="n">
+        <v>1</v>
+      </c>
+      <c r="C257" t="s">
+        <v>318</v>
+      </c>
+      <c r="D257"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="s">
+        <v>103</v>
+      </c>
+      <c r="B258" t="n">
+        <v>1</v>
+      </c>
+      <c r="C258" t="s">
+        <v>384</v>
+      </c>
+      <c r="D258"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="s">
+        <v>104</v>
+      </c>
+      <c r="B259" t="n">
+        <v>1</v>
+      </c>
+      <c r="C259" t="s">
+        <v>312</v>
+      </c>
+      <c r="D259"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="s">
+        <v>104</v>
+      </c>
+      <c r="B260" t="n">
+        <v>1</v>
+      </c>
+      <c r="C260" t="s">
+        <v>317</v>
+      </c>
+      <c r="D260"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="s">
+        <v>104</v>
+      </c>
+      <c r="B261" t="n">
+        <v>1</v>
+      </c>
+      <c r="C261" t="s">
+        <v>345</v>
+      </c>
+      <c r="D261"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="s">
+        <v>105</v>
+      </c>
+      <c r="B262" t="n">
+        <v>1</v>
+      </c>
+      <c r="C262" t="s">
+        <v>312</v>
+      </c>
+      <c r="D262"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="s">
+        <v>107</v>
+      </c>
+      <c r="B263" t="n">
+        <v>1</v>
+      </c>
+      <c r="C263" t="s">
+        <v>320</v>
+      </c>
+      <c r="D263"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="s">
+        <v>107</v>
+      </c>
+      <c r="B264" t="n">
+        <v>1</v>
+      </c>
+      <c r="C264" t="s">
+        <v>317</v>
+      </c>
+      <c r="D264"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="s">
+        <v>107</v>
+      </c>
+      <c r="B265" t="n">
+        <v>1</v>
+      </c>
+      <c r="C265" t="s">
+        <v>374</v>
+      </c>
+      <c r="D265"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="s">
+        <v>108</v>
+      </c>
+      <c r="B266" t="n">
+        <v>1</v>
+      </c>
+      <c r="C266" t="s">
+        <v>320</v>
+      </c>
+      <c r="D266"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="s">
+        <v>108</v>
+      </c>
+      <c r="B267" t="n">
+        <v>1</v>
+      </c>
+      <c r="C267" t="s">
+        <v>348</v>
+      </c>
+      <c r="D267"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="s">
+        <v>108</v>
+      </c>
+      <c r="B268" t="n">
+        <v>1</v>
+      </c>
+      <c r="C268" t="s">
+        <v>342</v>
+      </c>
+      <c r="D268"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="s">
+        <v>108</v>
+      </c>
+      <c r="B269" t="n">
+        <v>1</v>
+      </c>
+      <c r="C269" t="s">
+        <v>385</v>
+      </c>
+      <c r="D269"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="s">
+        <v>109</v>
+      </c>
+      <c r="B270" t="n">
+        <v>1</v>
+      </c>
+      <c r="C270" t="s">
+        <v>373</v>
+      </c>
+      <c r="D270"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="s">
+        <v>109</v>
+      </c>
+      <c r="B271" t="n">
+        <v>1</v>
+      </c>
+      <c r="C271" t="s">
+        <v>317</v>
+      </c>
+      <c r="D271"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="s">
+        <v>110</v>
+      </c>
+      <c r="B272" t="n">
+        <v>1</v>
+      </c>
+      <c r="C272" t="s">
+        <v>307</v>
+      </c>
+      <c r="D272"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="s">
+        <v>110</v>
+      </c>
+      <c r="B273" t="n">
+        <v>1</v>
+      </c>
+      <c r="C273" t="s">
+        <v>324</v>
+      </c>
+      <c r="D273"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="s">
+        <v>110</v>
+      </c>
+      <c r="B274" t="n">
+        <v>1</v>
+      </c>
+      <c r="C274" t="s">
+        <v>386</v>
+      </c>
+      <c r="D274"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="s">
+        <v>110</v>
+      </c>
+      <c r="B275" t="n">
+        <v>1</v>
+      </c>
+      <c r="C275" t="s">
+        <v>309</v>
+      </c>
+      <c r="D275"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="s">
+        <v>110</v>
+      </c>
+      <c r="B276" t="n">
+        <v>1</v>
+      </c>
+      <c r="C276" t="s">
+        <v>359</v>
+      </c>
+      <c r="D276"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="s">
+        <v>110</v>
+      </c>
+      <c r="B277" t="n">
+        <v>1</v>
+      </c>
+      <c r="C277" t="s">
+        <v>387</v>
+      </c>
+      <c r="D277"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="s">
+        <v>110</v>
+      </c>
+      <c r="B278" t="n">
+        <v>1</v>
+      </c>
+      <c r="C278" t="s">
+        <v>280</v>
+      </c>
+      <c r="D278"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="s">
+        <v>110</v>
+      </c>
+      <c r="B279" t="n">
+        <v>1</v>
+      </c>
+      <c r="C279" t="s">
+        <v>291</v>
+      </c>
+      <c r="D279"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="s">
+        <v>112</v>
+      </c>
+      <c r="B280" t="n">
+        <v>1</v>
+      </c>
+      <c r="C280" t="s">
+        <v>388</v>
+      </c>
+      <c r="D280"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="s">
+        <v>112</v>
+      </c>
+      <c r="B281" t="n">
+        <v>1</v>
+      </c>
+      <c r="C281" t="s">
+        <v>307</v>
+      </c>
+      <c r="D281"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="s">
+        <v>113</v>
+      </c>
+      <c r="B282" t="n">
+        <v>1</v>
+      </c>
+      <c r="C282" t="s">
+        <v>324</v>
+      </c>
+      <c r="D282"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="s">
+        <v>113</v>
+      </c>
+      <c r="B283" t="n">
+        <v>1</v>
+      </c>
+      <c r="C283" t="s">
+        <v>386</v>
+      </c>
+      <c r="D283"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="s">
+        <v>113</v>
+      </c>
+      <c r="B284" t="n">
+        <v>1</v>
+      </c>
+      <c r="C284" t="s">
+        <v>280</v>
+      </c>
+      <c r="D284"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="s">
+        <v>113</v>
+      </c>
+      <c r="B285" t="n">
+        <v>1</v>
+      </c>
+      <c r="C285" t="s">
+        <v>343</v>
+      </c>
+      <c r="D285"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="s">
+        <v>113</v>
+      </c>
+      <c r="B286" t="n">
+        <v>1</v>
+      </c>
+      <c r="C286" t="s">
+        <v>283</v>
+      </c>
+      <c r="D286" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="s">
+        <v>113</v>
+      </c>
+      <c r="B287" t="n">
+        <v>1</v>
+      </c>
+      <c r="C287" t="s">
+        <v>389</v>
+      </c>
+      <c r="D287"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="s">
+        <v>113</v>
+      </c>
+      <c r="B288" t="n">
+        <v>1</v>
+      </c>
+      <c r="C288" t="s">
+        <v>307</v>
+      </c>
+      <c r="D288"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="s">
+        <v>114</v>
+      </c>
+      <c r="B289" t="n">
+        <v>1</v>
+      </c>
+      <c r="C289" t="s">
+        <v>307</v>
+      </c>
+      <c r="D289"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="s">
+        <v>114</v>
+      </c>
+      <c r="B290" t="n">
+        <v>1</v>
+      </c>
+      <c r="C290" t="s">
+        <v>314</v>
+      </c>
+      <c r="D290"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="s">
+        <v>114</v>
+      </c>
+      <c r="B291" t="n">
+        <v>1</v>
+      </c>
+      <c r="C291" t="s">
+        <v>390</v>
+      </c>
+      <c r="D291"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="s">
+        <v>114</v>
+      </c>
+      <c r="B292" t="n">
+        <v>1</v>
+      </c>
+      <c r="C292" t="s">
+        <v>391</v>
+      </c>
+      <c r="D292"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="s">
+        <v>114</v>
+      </c>
+      <c r="B293" t="n">
+        <v>1</v>
+      </c>
+      <c r="C293" t="s">
+        <v>387</v>
+      </c>
+      <c r="D293"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="s">
+        <v>114</v>
+      </c>
+      <c r="B294" t="n">
+        <v>1</v>
+      </c>
+      <c r="C294" t="s">
+        <v>320</v>
+      </c>
+      <c r="D294"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="s">
+        <v>115</v>
+      </c>
+      <c r="B295" t="n">
+        <v>1</v>
+      </c>
+      <c r="C295" t="s">
+        <v>392</v>
+      </c>
+      <c r="D295"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="s">
+        <v>116</v>
+      </c>
+      <c r="B296" t="n">
+        <v>1</v>
+      </c>
+      <c r="C296" t="s">
+        <v>291</v>
+      </c>
+      <c r="D296"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="s">
+        <v>116</v>
+      </c>
+      <c r="B297" t="n">
+        <v>1</v>
+      </c>
+      <c r="C297" t="s">
+        <v>308</v>
+      </c>
+      <c r="D297"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="s">
+        <v>116</v>
+      </c>
+      <c r="B298" t="n">
+        <v>1</v>
+      </c>
+      <c r="C298" t="s">
+        <v>307</v>
+      </c>
+      <c r="D298"/>
+    </row>
+    <row r="299">
+      <c r="A299" t="s">
+        <v>116</v>
+      </c>
+      <c r="B299" t="n">
+        <v>1</v>
+      </c>
+      <c r="C299" t="s">
+        <v>280</v>
+      </c>
+      <c r="D299"/>
+    </row>
+    <row r="300">
+      <c r="A300" t="s">
+        <v>116</v>
+      </c>
+      <c r="B300" t="n">
+        <v>1</v>
+      </c>
+      <c r="C300" t="s">
+        <v>393</v>
+      </c>
+      <c r="D300"/>
+    </row>
+    <row r="301">
+      <c r="A301" t="s">
+        <v>116</v>
+      </c>
+      <c r="B301" t="n">
+        <v>1</v>
+      </c>
+      <c r="C301" t="s">
+        <v>394</v>
+      </c>
+      <c r="D301"/>
+    </row>
+    <row r="302">
+      <c r="A302" t="s">
+        <v>117</v>
+      </c>
+      <c r="B302" t="n">
+        <v>1</v>
+      </c>
+      <c r="C302" t="s">
+        <v>280</v>
+      </c>
+      <c r="D302"/>
+    </row>
+    <row r="303">
+      <c r="A303" t="s">
+        <v>117</v>
+      </c>
+      <c r="B303" t="n">
+        <v>1</v>
+      </c>
+      <c r="C303" t="s">
+        <v>309</v>
+      </c>
+      <c r="D303"/>
+    </row>
+    <row r="304">
+      <c r="A304" t="s">
+        <v>117</v>
+      </c>
+      <c r="B304" t="n">
+        <v>1</v>
+      </c>
+      <c r="C304" t="s">
+        <v>307</v>
+      </c>
+      <c r="D304"/>
+    </row>
+    <row r="305">
+      <c r="A305" t="s">
+        <v>118</v>
+      </c>
+      <c r="B305" t="n">
+        <v>1</v>
+      </c>
+      <c r="C305" t="s">
+        <v>308</v>
+      </c>
+      <c r="D305"/>
+    </row>
+    <row r="306">
+      <c r="A306" t="s">
+        <v>118</v>
+      </c>
+      <c r="B306" t="n">
+        <v>1</v>
+      </c>
+      <c r="C306" t="s">
+        <v>304</v>
+      </c>
+      <c r="D306"/>
+    </row>
+    <row r="307">
+      <c r="A307" t="s">
+        <v>118</v>
+      </c>
+      <c r="B307" t="n">
+        <v>1</v>
+      </c>
+      <c r="C307" t="s">
+        <v>324</v>
+      </c>
+      <c r="D307"/>
+    </row>
+    <row r="308">
+      <c r="A308" t="s">
+        <v>118</v>
+      </c>
+      <c r="B308" t="n">
+        <v>1</v>
+      </c>
+      <c r="C308" t="s">
+        <v>365</v>
+      </c>
+      <c r="D308"/>
+    </row>
+    <row r="309">
+      <c r="A309" t="s">
+        <v>118</v>
+      </c>
+      <c r="B309" t="n">
+        <v>1</v>
+      </c>
+      <c r="C309" t="s">
+        <v>395</v>
+      </c>
+      <c r="D309"/>
+    </row>
+    <row r="310">
+      <c r="A310" t="s">
+        <v>118</v>
+      </c>
+      <c r="B310" t="n">
+        <v>1</v>
+      </c>
+      <c r="C310" t="s">
+        <v>306</v>
+      </c>
+      <c r="D310"/>
+    </row>
+    <row r="311">
+      <c r="A311" t="s">
+        <v>118</v>
+      </c>
+      <c r="B311" t="n">
+        <v>1</v>
+      </c>
+      <c r="C311" t="s">
+        <v>396</v>
+      </c>
+      <c r="D311"/>
+    </row>
+    <row r="312">
+      <c r="A312" t="s">
+        <v>118</v>
+      </c>
+      <c r="B312" t="n">
+        <v>1</v>
+      </c>
+      <c r="C312" t="s">
+        <v>319</v>
+      </c>
+      <c r="D312"/>
+    </row>
+    <row r="313">
+      <c r="A313" t="s">
+        <v>118</v>
+      </c>
+      <c r="B313" t="n">
+        <v>1</v>
+      </c>
+      <c r="C313" t="s">
+        <v>307</v>
+      </c>
+      <c r="D313"/>
+    </row>
+    <row r="314">
+      <c r="A314" t="s">
+        <v>118</v>
+      </c>
+      <c r="B314" t="n">
+        <v>1</v>
+      </c>
+      <c r="C314" t="s">
+        <v>302</v>
+      </c>
+      <c r="D314" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="s">
+        <v>118</v>
+      </c>
+      <c r="B315" t="n">
+        <v>1</v>
+      </c>
+      <c r="C315" t="s">
+        <v>320</v>
+      </c>
+      <c r="D315"/>
+    </row>
+    <row r="316">
+      <c r="A316" t="s">
+        <v>119</v>
+      </c>
+      <c r="B316" t="n">
+        <v>1</v>
+      </c>
+      <c r="C316" t="s">
+        <v>280</v>
+      </c>
+      <c r="D316"/>
+    </row>
+    <row r="317">
+      <c r="A317" t="s">
+        <v>119</v>
+      </c>
+      <c r="B317" t="n">
+        <v>1</v>
+      </c>
+      <c r="C317" t="s">
+        <v>283</v>
+      </c>
+      <c r="D317" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="s">
+        <v>119</v>
+      </c>
+      <c r="B318" t="n">
+        <v>1</v>
+      </c>
+      <c r="C318" t="s">
+        <v>376</v>
+      </c>
+      <c r="D318" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="s">
+        <v>119</v>
+      </c>
+      <c r="B319" t="n">
+        <v>1</v>
+      </c>
+      <c r="C319" t="s">
+        <v>307</v>
+      </c>
+      <c r="D319"/>
+    </row>
+    <row r="320">
+      <c r="A320" t="s">
+        <v>119</v>
+      </c>
+      <c r="B320" t="n">
+        <v>1</v>
+      </c>
+      <c r="C320" t="s">
+        <v>302</v>
+      </c>
+      <c r="D320" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="s">
+        <v>120</v>
+      </c>
+      <c r="B321" t="n">
+        <v>1</v>
+      </c>
+      <c r="C321" t="s">
+        <v>280</v>
+      </c>
+      <c r="D321"/>
+    </row>
+    <row r="322">
+      <c r="A322" t="s">
+        <v>120</v>
+      </c>
+      <c r="B322" t="n">
+        <v>1</v>
+      </c>
+      <c r="C322" t="s">
+        <v>320</v>
+      </c>
+      <c r="D322"/>
+    </row>
+    <row r="323">
+      <c r="A323" t="s">
+        <v>120</v>
+      </c>
+      <c r="B323" t="n">
+        <v>1</v>
+      </c>
+      <c r="C323" t="s">
+        <v>397</v>
+      </c>
+      <c r="D323"/>
+    </row>
+    <row r="324">
+      <c r="A324" t="s">
+        <v>120</v>
+      </c>
+      <c r="B324" t="n">
+        <v>1</v>
+      </c>
+      <c r="C324" t="s">
+        <v>307</v>
+      </c>
+      <c r="D324"/>
+    </row>
+    <row r="325">
+      <c r="A325" t="s">
+        <v>120</v>
+      </c>
+      <c r="B325" t="n">
+        <v>1</v>
+      </c>
+      <c r="C325" t="s">
+        <v>398</v>
+      </c>
+      <c r="D325"/>
+    </row>
+    <row r="326">
+      <c r="A326" t="s">
+        <v>120</v>
+      </c>
+      <c r="B326" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" t="s">
+        <v>302</v>
+      </c>
+      <c r="D326" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="s">
+        <v>121</v>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" t="s">
+        <v>293</v>
+      </c>
+      <c r="D327" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="s">
+        <v>121</v>
+      </c>
+      <c r="B328" t="n">
+        <v>1</v>
+      </c>
+      <c r="C328" t="s">
+        <v>309</v>
+      </c>
+      <c r="D328"/>
+    </row>
+    <row r="329">
+      <c r="A329" t="s">
+        <v>121</v>
+      </c>
+      <c r="B329" t="n">
+        <v>1</v>
+      </c>
+      <c r="C329" t="s">
+        <v>287</v>
+      </c>
+      <c r="D329"/>
+    </row>
+    <row r="330">
+      <c r="A330" t="s">
+        <v>121</v>
+      </c>
+      <c r="B330" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" t="s">
+        <v>340</v>
+      </c>
+      <c r="D330"/>
+    </row>
+    <row r="331">
+      <c r="A331" t="s">
+        <v>121</v>
+      </c>
+      <c r="B331" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" t="s">
+        <v>285</v>
+      </c>
+      <c r="D331"/>
+    </row>
+    <row r="332">
+      <c r="A332" t="s">
+        <v>122</v>
+      </c>
+      <c r="B332" t="n">
+        <v>1</v>
+      </c>
+      <c r="C332" t="s">
+        <v>308</v>
+      </c>
+      <c r="D332"/>
+    </row>
+    <row r="333">
+      <c r="A333" t="s">
+        <v>122</v>
+      </c>
+      <c r="B333" t="n">
+        <v>1</v>
+      </c>
+      <c r="C333" t="s">
+        <v>399</v>
+      </c>
+      <c r="D333"/>
+    </row>
+    <row r="334">
+      <c r="A334" t="s">
+        <v>122</v>
+      </c>
+      <c r="B334" t="n">
+        <v>1</v>
+      </c>
+      <c r="C334" t="s">
+        <v>309</v>
+      </c>
+      <c r="D334"/>
+    </row>
+    <row r="335">
+      <c r="A335" t="s">
+        <v>122</v>
+      </c>
+      <c r="B335" t="n">
+        <v>1</v>
+      </c>
+      <c r="C335" t="s">
+        <v>400</v>
+      </c>
+      <c r="D335"/>
+    </row>
+    <row r="336">
+      <c r="A336" t="s">
+        <v>122</v>
+      </c>
+      <c r="B336" t="n">
+        <v>1</v>
+      </c>
+      <c r="C336" t="s">
+        <v>401</v>
+      </c>
+      <c r="D336"/>
+    </row>
+    <row r="337">
+      <c r="A337" t="s">
+        <v>122</v>
+      </c>
+      <c r="B337" t="n">
+        <v>1</v>
+      </c>
+      <c r="C337" t="s">
+        <v>395</v>
+      </c>
+      <c r="D337"/>
+    </row>
+    <row r="338">
+      <c r="A338" t="s">
+        <v>122</v>
+      </c>
+      <c r="B338" t="n">
+        <v>1</v>
+      </c>
+      <c r="C338" t="s">
+        <v>307</v>
+      </c>
+      <c r="D338"/>
+    </row>
+    <row r="339">
+      <c r="A339" t="s">
+        <v>123</v>
+      </c>
+      <c r="B339" t="n">
+        <v>1</v>
+      </c>
+      <c r="C339" t="s">
+        <v>291</v>
+      </c>
+      <c r="D339"/>
+    </row>
+    <row r="340">
+      <c r="A340" t="s">
+        <v>123</v>
+      </c>
+      <c r="B340" t="n">
+        <v>1</v>
+      </c>
+      <c r="C340" t="s">
+        <v>280</v>
+      </c>
+      <c r="D340"/>
+    </row>
+    <row r="341">
+      <c r="A341" t="s">
+        <v>123</v>
+      </c>
+      <c r="B341" t="n">
+        <v>1</v>
+      </c>
+      <c r="C341" t="s">
+        <v>290</v>
+      </c>
+      <c r="D341"/>
+    </row>
+    <row r="342">
+      <c r="A342" t="s">
+        <v>123</v>
+      </c>
+      <c r="B342" t="n">
+        <v>1</v>
+      </c>
+      <c r="C342" t="s">
+        <v>310</v>
+      </c>
+      <c r="D342"/>
+    </row>
+    <row r="343">
+      <c r="A343" t="s">
+        <v>123</v>
+      </c>
+      <c r="B343" t="n">
+        <v>1</v>
+      </c>
+      <c r="C343" t="s">
+        <v>402</v>
+      </c>
+      <c r="D343"/>
+    </row>
+    <row r="344">
+      <c r="A344" t="s">
+        <v>123</v>
+      </c>
+      <c r="B344" t="n">
+        <v>1</v>
+      </c>
+      <c r="C344" t="s">
+        <v>301</v>
+      </c>
+      <c r="D344"/>
+    </row>
+    <row r="345">
+      <c r="A345" t="s">
+        <v>123</v>
+      </c>
+      <c r="B345" t="n">
+        <v>1</v>
+      </c>
+      <c r="C345" t="s">
+        <v>403</v>
+      </c>
+      <c r="D345"/>
+    </row>
+    <row r="346">
+      <c r="A346" t="s">
+        <v>123</v>
+      </c>
+      <c r="B346" t="n">
+        <v>1</v>
+      </c>
+      <c r="C346" t="s">
+        <v>307</v>
+      </c>
+      <c r="D346"/>
+    </row>
+    <row r="347">
+      <c r="A347" t="s">
+        <v>124</v>
+      </c>
+      <c r="B347" t="n">
+        <v>1</v>
+      </c>
+      <c r="C347" t="s">
+        <v>280</v>
+      </c>
+      <c r="D347"/>
+    </row>
+    <row r="348">
+      <c r="A348" t="s">
+        <v>124</v>
+      </c>
+      <c r="B348" t="n">
+        <v>1</v>
+      </c>
+      <c r="C348" t="s">
+        <v>285</v>
+      </c>
+      <c r="D348"/>
+    </row>
+    <row r="349">
+      <c r="A349" t="s">
+        <v>124</v>
+      </c>
+      <c r="B349" t="n">
+        <v>1</v>
+      </c>
+      <c r="C349" t="s">
+        <v>397</v>
+      </c>
+      <c r="D349"/>
+    </row>
+    <row r="350">
+      <c r="A350" t="s">
+        <v>124</v>
+      </c>
+      <c r="B350" t="n">
+        <v>1</v>
+      </c>
+      <c r="C350" t="s">
+        <v>301</v>
+      </c>
+      <c r="D350"/>
+    </row>
+    <row r="351">
+      <c r="A351" t="s">
+        <v>124</v>
+      </c>
+      <c r="B351" t="n">
+        <v>1</v>
+      </c>
+      <c r="C351" t="s">
+        <v>291</v>
+      </c>
+      <c r="D351"/>
+    </row>
+    <row r="352">
+      <c r="A352" t="s">
+        <v>124</v>
+      </c>
+      <c r="B352" t="n">
+        <v>1</v>
+      </c>
+      <c r="C352" t="s">
+        <v>307</v>
+      </c>
+      <c r="D352"/>
+    </row>
+    <row r="353">
+      <c r="A353" t="s">
+        <v>124</v>
+      </c>
+      <c r="B353" t="n">
+        <v>1</v>
+      </c>
+      <c r="C353" t="s">
+        <v>302</v>
+      </c>
+      <c r="D353" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="s">
+        <v>125</v>
+      </c>
+      <c r="B354" t="n">
+        <v>1</v>
+      </c>
+      <c r="C354" t="s">
+        <v>376</v>
+      </c>
+      <c r="D354" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="s">
+        <v>127</v>
+      </c>
+      <c r="B355" t="n">
+        <v>1</v>
+      </c>
+      <c r="C355" t="s">
+        <v>280</v>
+      </c>
+      <c r="D355"/>
+    </row>
+    <row r="356">
+      <c r="A356" t="s">
+        <v>127</v>
+      </c>
+      <c r="B356" t="n">
+        <v>1</v>
+      </c>
+      <c r="C356" t="s">
+        <v>302</v>
+      </c>
+      <c r="D356" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="s">
+        <v>127</v>
+      </c>
+      <c r="B357" t="n">
+        <v>1</v>
+      </c>
+      <c r="C357" t="s">
+        <v>404</v>
+      </c>
+      <c r="D357"/>
+    </row>
+    <row r="358">
+      <c r="A358" t="s">
+        <v>128</v>
+      </c>
+      <c r="B358" t="n">
+        <v>1</v>
+      </c>
+      <c r="C358" t="s">
+        <v>302</v>
+      </c>
+      <c r="D358" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="s">
+        <v>128</v>
+      </c>
+      <c r="B359" t="n">
+        <v>1</v>
+      </c>
+      <c r="C359" t="s">
+        <v>280</v>
+      </c>
+      <c r="D359"/>
+    </row>
+    <row r="360">
+      <c r="A360" t="s">
+        <v>128</v>
+      </c>
+      <c r="B360" t="n">
+        <v>1</v>
+      </c>
+      <c r="C360" t="s">
+        <v>405</v>
+      </c>
+      <c r="D360"/>
+    </row>
+    <row r="361">
+      <c r="A361" t="s">
+        <v>128</v>
+      </c>
+      <c r="B361" t="n">
+        <v>1</v>
+      </c>
+      <c r="C361" t="s">
+        <v>406</v>
+      </c>
+      <c r="D361"/>
+    </row>
+    <row r="362">
+      <c r="A362" t="s">
+        <v>128</v>
+      </c>
+      <c r="B362" t="n">
+        <v>1</v>
+      </c>
+      <c r="C362" t="s">
+        <v>407</v>
+      </c>
+      <c r="D362"/>
+    </row>
+    <row r="363">
+      <c r="A363" t="s">
+        <v>128</v>
+      </c>
+      <c r="B363" t="n">
+        <v>1</v>
+      </c>
+      <c r="C363" t="s">
+        <v>285</v>
+      </c>
+      <c r="D363"/>
+    </row>
+    <row r="364">
+      <c r="A364" t="s">
+        <v>129</v>
+      </c>
+      <c r="B364" t="n">
+        <v>1</v>
+      </c>
+      <c r="C364" t="s">
+        <v>280</v>
+      </c>
+      <c r="D364"/>
+    </row>
+    <row r="365">
+      <c r="A365" t="s">
+        <v>129</v>
+      </c>
+      <c r="B365" t="n">
+        <v>1</v>
+      </c>
+      <c r="C365" t="s">
+        <v>291</v>
+      </c>
+      <c r="D365"/>
+    </row>
+    <row r="366">
+      <c r="A366" t="s">
+        <v>129</v>
+      </c>
+      <c r="B366" t="n">
+        <v>1</v>
+      </c>
+      <c r="C366" t="s">
+        <v>285</v>
+      </c>
+      <c r="D366"/>
+    </row>
+    <row r="367">
+      <c r="A367" t="s">
+        <v>130</v>
+      </c>
+      <c r="B367" t="n">
+        <v>1</v>
+      </c>
+      <c r="C367" t="s">
+        <v>301</v>
+      </c>
+      <c r="D367"/>
+    </row>
+    <row r="368">
+      <c r="A368" t="s">
+        <v>130</v>
+      </c>
+      <c r="B368" t="n">
+        <v>1</v>
+      </c>
+      <c r="C368" t="s">
+        <v>280</v>
+      </c>
+      <c r="D368"/>
+    </row>
+    <row r="369">
+      <c r="A369" t="s">
+        <v>130</v>
+      </c>
+      <c r="B369" t="n">
+        <v>1</v>
+      </c>
+      <c r="C369" t="s">
+        <v>283</v>
+      </c>
+      <c r="D369" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="s">
+        <v>131</v>
+      </c>
+      <c r="B370" t="n">
+        <v>1</v>
+      </c>
+      <c r="C370" t="s">
+        <v>280</v>
+      </c>
+      <c r="D370"/>
+    </row>
+    <row r="371">
+      <c r="A371" t="s">
+        <v>131</v>
+      </c>
+      <c r="B371" t="n">
+        <v>1</v>
+      </c>
+      <c r="C371" t="s">
+        <v>291</v>
+      </c>
+      <c r="D371"/>
+    </row>
+    <row r="372">
+      <c r="A372" t="s">
+        <v>131</v>
+      </c>
+      <c r="B372" t="n">
+        <v>1</v>
+      </c>
+      <c r="C372" t="s">
+        <v>307</v>
+      </c>
+      <c r="D372"/>
+    </row>
+    <row r="373">
+      <c r="A373" t="s">
+        <v>131</v>
+      </c>
+      <c r="B373" t="n">
+        <v>1</v>
+      </c>
+      <c r="C373" t="s">
+        <v>287</v>
+      </c>
+      <c r="D373"/>
+    </row>
+    <row r="374">
+      <c r="A374" t="s">
+        <v>132</v>
+      </c>
+      <c r="B374" t="n">
+        <v>1</v>
+      </c>
+      <c r="C374" t="s">
+        <v>302</v>
+      </c>
+      <c r="D374" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="s">
+        <v>132</v>
+      </c>
+      <c r="B375" t="n">
+        <v>1</v>
+      </c>
+      <c r="C375" t="s">
+        <v>301</v>
+      </c>
+      <c r="D375"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="s">
+        <v>132</v>
+      </c>
+      <c r="B376" t="n">
+        <v>1</v>
+      </c>
+      <c r="C376" t="s">
+        <v>288</v>
+      </c>
+      <c r="D376" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="s">
+        <v>133</v>
+      </c>
+      <c r="B377" t="n">
+        <v>1</v>
+      </c>
+      <c r="C377" t="s">
+        <v>302</v>
+      </c>
+      <c r="D377" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="s">
+        <v>133</v>
+      </c>
+      <c r="B378" t="n">
+        <v>1</v>
+      </c>
+      <c r="C378" t="s">
+        <v>408</v>
+      </c>
+      <c r="D378"/>
+    </row>
+    <row r="379">
+      <c r="A379" t="s">
+        <v>133</v>
+      </c>
+      <c r="B379" t="n">
+        <v>1</v>
+      </c>
+      <c r="C379" t="s">
+        <v>409</v>
+      </c>
+      <c r="D379"/>
+    </row>
+    <row r="380">
+      <c r="A380" t="s">
+        <v>133</v>
+      </c>
+      <c r="B380" t="n">
+        <v>1</v>
+      </c>
+      <c r="C380" t="s">
+        <v>410</v>
+      </c>
+      <c r="D380"/>
+    </row>
+    <row r="381">
+      <c r="A381" t="s">
+        <v>133</v>
+      </c>
+      <c r="B381" t="n">
+        <v>1</v>
+      </c>
+      <c r="C381" t="s">
+        <v>317</v>
+      </c>
+      <c r="D381"/>
+    </row>
+    <row r="382">
+      <c r="A382" t="s">
+        <v>134</v>
+      </c>
+      <c r="B382" t="n">
+        <v>1</v>
+      </c>
+      <c r="C382" t="s">
+        <v>317</v>
+      </c>
+      <c r="D382"/>
+    </row>
+    <row r="383">
+      <c r="A383" t="s">
+        <v>134</v>
+      </c>
+      <c r="B383" t="n">
+        <v>1</v>
+      </c>
+      <c r="C383" t="s">
+        <v>411</v>
+      </c>
+      <c r="D383"/>
+    </row>
+    <row r="384">
+      <c r="A384" t="s">
+        <v>134</v>
+      </c>
+      <c r="B384" t="n">
+        <v>1</v>
+      </c>
+      <c r="C384" t="s">
+        <v>330</v>
+      </c>
+      <c r="D384"/>
+    </row>
+    <row r="385">
+      <c r="A385" t="s">
+        <v>134</v>
+      </c>
+      <c r="B385" t="n">
+        <v>1</v>
+      </c>
+      <c r="C385" t="s">
+        <v>412</v>
+      </c>
+      <c r="D385"/>
+    </row>
+    <row r="386">
+      <c r="A386" t="s">
+        <v>134</v>
+      </c>
+      <c r="B386" t="n">
+        <v>1</v>
+      </c>
+      <c r="C386" t="s">
+        <v>332</v>
+      </c>
+      <c r="D386"/>
+    </row>
+    <row r="387">
+      <c r="A387" t="s">
+        <v>135</v>
+      </c>
+      <c r="B387" t="n">
+        <v>1</v>
+      </c>
+      <c r="C387" t="s">
+        <v>312</v>
+      </c>
+      <c r="D387"/>
+    </row>
+    <row r="388">
+      <c r="A388" t="s">
+        <v>135</v>
+      </c>
+      <c r="B388" t="n">
+        <v>1</v>
+      </c>
+      <c r="C388" t="s">
+        <v>332</v>
+      </c>
+      <c r="D388"/>
+    </row>
+    <row r="389">
+      <c r="A389" t="s">
+        <v>135</v>
+      </c>
+      <c r="B389" t="n">
+        <v>1</v>
+      </c>
+      <c r="C389" t="s">
+        <v>302</v>
+      </c>
+      <c r="D389" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="s">
+        <v>135</v>
+      </c>
+      <c r="B390" t="n">
+        <v>1</v>
+      </c>
+      <c r="C390" t="s">
+        <v>293</v>
+      </c>
+      <c r="D390" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="s">
+        <v>135</v>
+      </c>
+      <c r="B391" t="n">
+        <v>1</v>
+      </c>
+      <c r="C391" t="s">
+        <v>317</v>
+      </c>
+      <c r="D391"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="s">
+        <v>136</v>
+      </c>
+      <c r="B392" t="n">
+        <v>1</v>
+      </c>
+      <c r="C392" t="s">
+        <v>312</v>
+      </c>
+      <c r="D392"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="s">
+        <v>136</v>
+      </c>
+      <c r="B393" t="n">
+        <v>1</v>
+      </c>
+      <c r="C393" t="s">
+        <v>330</v>
+      </c>
+      <c r="D393"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="s">
+        <v>136</v>
+      </c>
+      <c r="B394" t="n">
+        <v>1</v>
+      </c>
+      <c r="C394" t="s">
+        <v>317</v>
+      </c>
+      <c r="D394"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="s">
+        <v>136</v>
+      </c>
+      <c r="B395" t="n">
+        <v>1</v>
+      </c>
+      <c r="C395" t="s">
+        <v>318</v>
+      </c>
+      <c r="D395"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="s">
+        <v>137</v>
+      </c>
+      <c r="B396" t="n">
+        <v>1</v>
+      </c>
+      <c r="C396" t="s">
+        <v>317</v>
+      </c>
+      <c r="D396"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="s">
+        <v>137</v>
+      </c>
+      <c r="B397" t="n">
+        <v>1</v>
+      </c>
+      <c r="C397" t="s">
+        <v>312</v>
+      </c>
+      <c r="D397"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="s">
+        <v>137</v>
+      </c>
+      <c r="B398" t="n">
+        <v>1</v>
+      </c>
+      <c r="C398" t="s">
+        <v>293</v>
+      </c>
+      <c r="D398" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="s">
+        <v>137</v>
+      </c>
+      <c r="B399" t="n">
+        <v>1</v>
+      </c>
+      <c r="C399" t="s">
+        <v>314</v>
+      </c>
+      <c r="D399"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="s">
+        <v>137</v>
+      </c>
+      <c r="B400" t="n">
+        <v>1</v>
+      </c>
+      <c r="C400" t="s">
+        <v>330</v>
+      </c>
+      <c r="D400"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="s">
+        <v>137</v>
+      </c>
+      <c r="B401" t="n">
+        <v>1</v>
+      </c>
+      <c r="C401" t="s">
+        <v>342</v>
+      </c>
+      <c r="D401"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="s">
+        <v>138</v>
+      </c>
+      <c r="B402" t="n">
+        <v>1</v>
+      </c>
+      <c r="C402" t="s">
+        <v>413</v>
+      </c>
+      <c r="D402"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="s">
+        <v>139</v>
+      </c>
+      <c r="B403" t="n">
+        <v>1</v>
+      </c>
+      <c r="C403" t="s">
+        <v>280</v>
+      </c>
+      <c r="D403"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="s">
+        <v>139</v>
+      </c>
+      <c r="B404" t="n">
+        <v>1</v>
+      </c>
+      <c r="C404" t="s">
+        <v>332</v>
+      </c>
+      <c r="D404"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="s">
+        <v>139</v>
+      </c>
+      <c r="B405" t="n">
+        <v>1</v>
+      </c>
+      <c r="C405" t="s">
+        <v>317</v>
+      </c>
+      <c r="D405"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="s">
+        <v>139</v>
+      </c>
+      <c r="B406" t="n">
+        <v>1</v>
+      </c>
+      <c r="C406" t="s">
+        <v>283</v>
+      </c>
+      <c r="D406" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="s">
+        <v>139</v>
+      </c>
+      <c r="B407" t="n">
+        <v>1</v>
+      </c>
+      <c r="C407" t="s">
+        <v>318</v>
+      </c>
+      <c r="D407"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="s">
+        <v>139</v>
+      </c>
+      <c r="B408" t="n">
+        <v>1</v>
+      </c>
+      <c r="C408" t="s">
+        <v>291</v>
+      </c>
+      <c r="D408"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="s">
+        <v>139</v>
+      </c>
+      <c r="B409" t="n">
+        <v>1</v>
+      </c>
+      <c r="C409" t="s">
+        <v>302</v>
+      </c>
+      <c r="D409" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="s">
+        <v>140</v>
+      </c>
+      <c r="B410" t="n">
+        <v>1</v>
+      </c>
+      <c r="C410" t="s">
+        <v>333</v>
+      </c>
+      <c r="D410" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="s">
+        <v>140</v>
+      </c>
+      <c r="B411" t="n">
+        <v>1</v>
+      </c>
+      <c r="C411" t="s">
+        <v>317</v>
+      </c>
+      <c r="D411"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="s">
+        <v>140</v>
+      </c>
+      <c r="B412" t="n">
+        <v>1</v>
+      </c>
+      <c r="C412" t="s">
+        <v>414</v>
+      </c>
+      <c r="D412"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="s">
+        <v>140</v>
+      </c>
+      <c r="B413" t="n">
+        <v>1</v>
+      </c>
+      <c r="C413" t="s">
+        <v>324</v>
+      </c>
+      <c r="D413"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="s">
+        <v>140</v>
+      </c>
+      <c r="B414" t="n">
+        <v>1</v>
+      </c>
+      <c r="C414" t="s">
+        <v>415</v>
+      </c>
+      <c r="D414"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="s">
+        <v>140</v>
+      </c>
+      <c r="B415" t="n">
+        <v>1</v>
+      </c>
+      <c r="C415" t="s">
+        <v>416</v>
+      </c>
+      <c r="D415"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="s">
+        <v>140</v>
+      </c>
+      <c r="B416" t="n">
+        <v>1</v>
+      </c>
+      <c r="C416" t="s">
+        <v>417</v>
+      </c>
+      <c r="D416"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="s">
+        <v>140</v>
+      </c>
+      <c r="B417" t="n">
+        <v>1</v>
+      </c>
+      <c r="C417" t="s">
+        <v>321</v>
+      </c>
+      <c r="D417"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="s">
+        <v>140</v>
+      </c>
+      <c r="B418" t="n">
+        <v>1</v>
+      </c>
+      <c r="C418" t="s">
+        <v>368</v>
+      </c>
+      <c r="D418"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="s">
+        <v>140</v>
+      </c>
+      <c r="B419" t="n">
+        <v>1</v>
+      </c>
+      <c r="C419" t="s">
+        <v>418</v>
+      </c>
+      <c r="D419"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="s">
+        <v>140</v>
+      </c>
+      <c r="B420" t="n">
+        <v>1</v>
+      </c>
+      <c r="C420" t="s">
+        <v>283</v>
+      </c>
+      <c r="D420" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="s">
+        <v>140</v>
+      </c>
+      <c r="B421" t="n">
+        <v>1</v>
+      </c>
+      <c r="C421" t="s">
+        <v>413</v>
+      </c>
+      <c r="D421"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="s">
+        <v>140</v>
+      </c>
+      <c r="B422" t="n">
+        <v>1</v>
+      </c>
+      <c r="C422" t="s">
+        <v>419</v>
+      </c>
+      <c r="D422"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="s">
+        <v>140</v>
+      </c>
+      <c r="B423" t="n">
+        <v>1</v>
+      </c>
+      <c r="C423" t="s">
+        <v>420</v>
+      </c>
+      <c r="D423"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="s">
+        <v>140</v>
+      </c>
+      <c r="B424" t="n">
+        <v>1</v>
+      </c>
+      <c r="C424" t="s">
+        <v>318</v>
+      </c>
+      <c r="D424"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="s">
+        <v>140</v>
+      </c>
+      <c r="B425" t="n">
+        <v>1</v>
+      </c>
+      <c r="C425" t="s">
+        <v>389</v>
+      </c>
+      <c r="D425"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="s">
+        <v>140</v>
+      </c>
+      <c r="B426" t="n">
+        <v>1</v>
+      </c>
+      <c r="C426" t="s">
+        <v>365</v>
+      </c>
+      <c r="D426"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="s">
+        <v>140</v>
+      </c>
+      <c r="B427" t="n">
+        <v>1</v>
+      </c>
+      <c r="C427" t="s">
+        <v>319</v>
+      </c>
+      <c r="D427"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="s">
+        <v>140</v>
+      </c>
+      <c r="B428" t="n">
+        <v>1</v>
+      </c>
+      <c r="C428" t="s">
+        <v>320</v>
+      </c>
+      <c r="D428"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="s">
+        <v>141</v>
+      </c>
+      <c r="B429" t="n">
+        <v>1</v>
+      </c>
+      <c r="C429" t="s">
+        <v>317</v>
+      </c>
+      <c r="D429"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="s">
+        <v>141</v>
+      </c>
+      <c r="B430" t="n">
+        <v>1</v>
+      </c>
+      <c r="C430" t="s">
+        <v>293</v>
+      </c>
+      <c r="D430" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="s">
+        <v>141</v>
+      </c>
+      <c r="B431" t="n">
+        <v>1</v>
+      </c>
+      <c r="C431" t="s">
+        <v>312</v>
+      </c>
+      <c r="D431"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="s">
+        <v>142</v>
+      </c>
+      <c r="B432" t="n">
+        <v>1</v>
+      </c>
+      <c r="C432" t="s">
+        <v>333</v>
+      </c>
+      <c r="D432" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="s">
+        <v>142</v>
+      </c>
+      <c r="B433" t="n">
+        <v>1</v>
+      </c>
+      <c r="C433" t="s">
+        <v>414</v>
+      </c>
+      <c r="D433"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="s">
+        <v>142</v>
+      </c>
+      <c r="B434" t="n">
+        <v>1</v>
+      </c>
+      <c r="C434" t="s">
+        <v>318</v>
+      </c>
+      <c r="D434"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="s">
+        <v>143</v>
+      </c>
+      <c r="B435" t="n">
+        <v>1</v>
+      </c>
+      <c r="C435" t="s">
+        <v>312</v>
+      </c>
+      <c r="D435"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="s">
+        <v>143</v>
+      </c>
+      <c r="B436" t="n">
+        <v>1</v>
+      </c>
+      <c r="C436" t="s">
+        <v>330</v>
+      </c>
+      <c r="D436"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="s">
+        <v>144</v>
+      </c>
+      <c r="B437" t="n">
+        <v>1</v>
+      </c>
+      <c r="C437" t="s">
+        <v>333</v>
+      </c>
+      <c r="D437" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="s">
+        <v>144</v>
+      </c>
+      <c r="B438" t="n">
+        <v>1</v>
+      </c>
+      <c r="C438" t="s">
+        <v>317</v>
+      </c>
+      <c r="D438"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="s">
+        <v>144</v>
+      </c>
+      <c r="B439" t="n">
+        <v>1</v>
+      </c>
+      <c r="C439" t="s">
+        <v>414</v>
+      </c>
+      <c r="D439"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="s">
+        <v>144</v>
+      </c>
+      <c r="B440" t="n">
+        <v>1</v>
+      </c>
+      <c r="C440" t="s">
+        <v>421</v>
+      </c>
+      <c r="D440"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="s">
+        <v>144</v>
+      </c>
+      <c r="B441" t="n">
+        <v>1</v>
+      </c>
+      <c r="C441" t="s">
+        <v>422</v>
+      </c>
+      <c r="D441"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="s">
+        <v>144</v>
+      </c>
+      <c r="B442" t="n">
+        <v>1</v>
+      </c>
+      <c r="C442" t="s">
+        <v>331</v>
+      </c>
+      <c r="D442"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="s">
+        <v>144</v>
+      </c>
+      <c r="B443" t="n">
+        <v>1</v>
+      </c>
+      <c r="C443" t="s">
+        <v>321</v>
+      </c>
+      <c r="D443"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="s">
+        <v>144</v>
+      </c>
+      <c r="B444" t="n">
+        <v>1</v>
+      </c>
+      <c r="C444" t="s">
+        <v>423</v>
+      </c>
+      <c r="D444"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="s">
+        <v>144</v>
+      </c>
+      <c r="B445" t="n">
+        <v>1</v>
+      </c>
+      <c r="C445" t="s">
+        <v>424</v>
+      </c>
+      <c r="D445"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="s">
+        <v>144</v>
+      </c>
+      <c r="B446" t="n">
+        <v>1</v>
+      </c>
+      <c r="C446" t="s">
+        <v>368</v>
+      </c>
+      <c r="D446"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="s">
+        <v>145</v>
+      </c>
+      <c r="B447" t="n">
+        <v>1</v>
+      </c>
+      <c r="C447" t="s">
+        <v>317</v>
+      </c>
+      <c r="D447"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="s">
+        <v>145</v>
+      </c>
+      <c r="B448" t="n">
+        <v>1</v>
+      </c>
+      <c r="C448" t="s">
+        <v>312</v>
+      </c>
+      <c r="D448"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="s">
+        <v>145</v>
+      </c>
+      <c r="B449" t="n">
+        <v>1</v>
+      </c>
+      <c r="C449" t="s">
+        <v>293</v>
+      </c>
+      <c r="D449" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="s">
+        <v>146</v>
+      </c>
+      <c r="B450" t="n">
+        <v>1</v>
+      </c>
+      <c r="C450" t="s">
+        <v>312</v>
+      </c>
+      <c r="D450"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="s">
+        <v>147</v>
+      </c>
+      <c r="B451" t="n">
+        <v>1</v>
+      </c>
+      <c r="C451" t="s">
+        <v>317</v>
+      </c>
+      <c r="D451"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="s">
+        <v>147</v>
+      </c>
+      <c r="B452" t="n">
+        <v>1</v>
+      </c>
+      <c r="C452" t="s">
+        <v>333</v>
+      </c>
+      <c r="D452" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="s">
+        <v>147</v>
+      </c>
+      <c r="B453" t="n">
+        <v>1</v>
+      </c>
+      <c r="C453" t="s">
+        <v>425</v>
+      </c>
+      <c r="D453"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="s">
+        <v>148</v>
+      </c>
+      <c r="B454" t="n">
+        <v>1</v>
+      </c>
+      <c r="C454" t="s">
+        <v>409</v>
+      </c>
+      <c r="D454"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="s">
+        <v>149</v>
+      </c>
+      <c r="B455" t="n">
+        <v>1</v>
+      </c>
+      <c r="C455" t="s">
+        <v>312</v>
+      </c>
+      <c r="D455"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="s">
+        <v>150</v>
+      </c>
+      <c r="B456" t="n">
+        <v>1</v>
+      </c>
+      <c r="C456" t="s">
+        <v>317</v>
+      </c>
+      <c r="D456"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="s">
+        <v>150</v>
+      </c>
+      <c r="B457" t="n">
+        <v>1</v>
+      </c>
+      <c r="C457" t="s">
+        <v>342</v>
+      </c>
+      <c r="D457"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="s">
+        <v>152</v>
+      </c>
+      <c r="B458" t="n">
+        <v>1</v>
+      </c>
+      <c r="C458" t="s">
+        <v>333</v>
+      </c>
+      <c r="D458" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="s">
+        <v>152</v>
+      </c>
+      <c r="B459" t="n">
+        <v>1</v>
+      </c>
+      <c r="C459" t="s">
+        <v>317</v>
+      </c>
+      <c r="D459"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="s">
+        <v>152</v>
+      </c>
+      <c r="B460" t="n">
+        <v>1</v>
+      </c>
+      <c r="C460" t="s">
+        <v>368</v>
+      </c>
+      <c r="D460"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="s">
+        <v>152</v>
+      </c>
+      <c r="B461" t="n">
+        <v>1</v>
+      </c>
+      <c r="C461" t="s">
+        <v>312</v>
+      </c>
+      <c r="D461"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="s">
+        <v>152</v>
+      </c>
+      <c r="B462" t="n">
+        <v>1</v>
+      </c>
+      <c r="C462" t="s">
+        <v>426</v>
+      </c>
+      <c r="D462" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="s">
+        <v>152</v>
+      </c>
+      <c r="B463" t="n">
+        <v>1</v>
+      </c>
+      <c r="C463" t="s">
+        <v>416</v>
+      </c>
+      <c r="D463"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="s">
+        <v>152</v>
+      </c>
+      <c r="B464" t="n">
+        <v>1</v>
+      </c>
+      <c r="C464" t="s">
+        <v>318</v>
+      </c>
+      <c r="D464"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="s">
+        <v>153</v>
+      </c>
+      <c r="B465" t="n">
+        <v>1</v>
+      </c>
+      <c r="C465" t="s">
+        <v>333</v>
+      </c>
+      <c r="D465" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="s">
+        <v>153</v>
+      </c>
+      <c r="B466" t="n">
+        <v>1</v>
+      </c>
+      <c r="C466" t="s">
+        <v>317</v>
+      </c>
+      <c r="D466"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="s">
+        <v>154</v>
+      </c>
+      <c r="B467" t="n">
+        <v>1</v>
+      </c>
+      <c r="C467" t="s">
+        <v>317</v>
+      </c>
+      <c r="D467"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="s">
+        <v>154</v>
+      </c>
+      <c r="B468" t="n">
+        <v>1</v>
+      </c>
+      <c r="C468" t="s">
+        <v>330</v>
+      </c>
+      <c r="D468"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="s">
+        <v>154</v>
+      </c>
+      <c r="B469" t="n">
+        <v>1</v>
+      </c>
+      <c r="C469" t="s">
+        <v>342</v>
+      </c>
+      <c r="D469"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="s">
+        <v>154</v>
+      </c>
+      <c r="B470" t="n">
+        <v>1</v>
+      </c>
+      <c r="C470" t="s">
+        <v>293</v>
+      </c>
+      <c r="D470" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="s">
+        <v>154</v>
+      </c>
+      <c r="B471" t="n">
+        <v>1</v>
+      </c>
+      <c r="C471" t="s">
+        <v>302</v>
+      </c>
+      <c r="D471" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="s">
+        <v>154</v>
+      </c>
+      <c r="B472" t="n">
+        <v>1</v>
+      </c>
+      <c r="C472" t="s">
+        <v>428</v>
+      </c>
+      <c r="D472"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="s">
+        <v>154</v>
+      </c>
+      <c r="B473" t="n">
+        <v>1</v>
+      </c>
+      <c r="C473" t="s">
+        <v>332</v>
+      </c>
+      <c r="D473"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="s">
+        <v>154</v>
+      </c>
+      <c r="B474" t="n">
+        <v>1</v>
+      </c>
+      <c r="C474" t="s">
+        <v>385</v>
+      </c>
+      <c r="D474"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="s">
+        <v>155</v>
+      </c>
+      <c r="B475" t="n">
+        <v>1</v>
+      </c>
+      <c r="C475" t="s">
+        <v>317</v>
+      </c>
+      <c r="D475"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="s">
+        <v>155</v>
+      </c>
+      <c r="B476" t="n">
+        <v>1</v>
+      </c>
+      <c r="C476" t="s">
+        <v>293</v>
+      </c>
+      <c r="D476" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="s">
+        <v>155</v>
+      </c>
+      <c r="B477" t="n">
+        <v>1</v>
+      </c>
+      <c r="C477" t="s">
+        <v>312</v>
+      </c>
+      <c r="D477"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="s">
+        <v>156</v>
+      </c>
+      <c r="B478" t="n">
+        <v>1</v>
+      </c>
+      <c r="C478" t="s">
+        <v>333</v>
+      </c>
+      <c r="D478" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="s">
+        <v>156</v>
+      </c>
+      <c r="B479" t="n">
+        <v>1</v>
+      </c>
+      <c r="C479" t="s">
+        <v>317</v>
+      </c>
+      <c r="D479"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="s">
+        <v>156</v>
+      </c>
+      <c r="B480" t="n">
+        <v>1</v>
+      </c>
+      <c r="C480" t="s">
+        <v>312</v>
+      </c>
+      <c r="D480"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="s">
+        <v>156</v>
+      </c>
+      <c r="B481" t="n">
+        <v>1</v>
+      </c>
+      <c r="C481" t="s">
+        <v>429</v>
+      </c>
+      <c r="D481"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="s">
+        <v>156</v>
+      </c>
+      <c r="B482" t="n">
+        <v>1</v>
+      </c>
+      <c r="C482" t="s">
+        <v>430</v>
+      </c>
+      <c r="D482"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="s">
+        <v>156</v>
+      </c>
+      <c r="B483" t="n">
+        <v>1</v>
+      </c>
+      <c r="C483" t="s">
+        <v>431</v>
+      </c>
+      <c r="D483"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="s">
+        <v>156</v>
+      </c>
+      <c r="B484" t="n">
+        <v>1</v>
+      </c>
+      <c r="C484" t="s">
+        <v>432</v>
+      </c>
+      <c r="D484"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="s">
+        <v>156</v>
+      </c>
+      <c r="B485" t="n">
+        <v>1</v>
+      </c>
+      <c r="C485" t="s">
+        <v>426</v>
+      </c>
+      <c r="D485" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="s">
+        <v>156</v>
+      </c>
+      <c r="B486" t="n">
+        <v>1</v>
+      </c>
+      <c r="C486" t="s">
+        <v>433</v>
+      </c>
+      <c r="D486" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="s">
+        <v>156</v>
+      </c>
+      <c r="B487" t="n">
+        <v>1</v>
+      </c>
+      <c r="C487" t="s">
+        <v>420</v>
+      </c>
+      <c r="D487"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="s">
+        <v>156</v>
+      </c>
+      <c r="B488" t="n">
+        <v>1</v>
+      </c>
+      <c r="C488" t="s">
+        <v>368</v>
+      </c>
+      <c r="D488"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="s">
+        <v>156</v>
+      </c>
+      <c r="B489" t="n">
+        <v>1</v>
+      </c>
+      <c r="C489" t="s">
+        <v>435</v>
+      </c>
+      <c r="D489"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="s">
+        <v>156</v>
+      </c>
+      <c r="B490" t="n">
+        <v>1</v>
+      </c>
+      <c r="C490" t="s">
+        <v>436</v>
+      </c>
+      <c r="D490"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="s">
+        <v>156</v>
+      </c>
+      <c r="B491" t="n">
+        <v>1</v>
+      </c>
+      <c r="C491" t="s">
+        <v>342</v>
+      </c>
+      <c r="D491"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="s">
+        <v>156</v>
+      </c>
+      <c r="B492" t="n">
+        <v>1</v>
+      </c>
+      <c r="C492" t="s">
+        <v>437</v>
+      </c>
+      <c r="D492"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="s">
+        <v>156</v>
+      </c>
+      <c r="B493" t="n">
+        <v>1</v>
+      </c>
+      <c r="C493" t="s">
+        <v>438</v>
+      </c>
+      <c r="D493"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="s">
+        <v>157</v>
+      </c>
+      <c r="B494" t="n">
+        <v>1</v>
+      </c>
+      <c r="C494" t="s">
+        <v>333</v>
+      </c>
+      <c r="D494" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="s">
+        <v>157</v>
+      </c>
+      <c r="B495" t="n">
+        <v>1</v>
+      </c>
+      <c r="C495" t="s">
+        <v>320</v>
+      </c>
+      <c r="D495"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="s">
+        <v>157</v>
+      </c>
+      <c r="B496" t="n">
+        <v>1</v>
+      </c>
+      <c r="C496" t="s">
+        <v>312</v>
+      </c>
+      <c r="D496"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="s">
+        <v>157</v>
+      </c>
+      <c r="B497" t="n">
+        <v>1</v>
+      </c>
+      <c r="C497" t="s">
+        <v>317</v>
+      </c>
+      <c r="D497"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="s">
+        <v>157</v>
+      </c>
+      <c r="B498" t="n">
+        <v>1</v>
+      </c>
+      <c r="C498" t="s">
+        <v>439</v>
+      </c>
+      <c r="D498" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="s">
+        <v>157</v>
+      </c>
+      <c r="B499" t="n">
+        <v>1</v>
+      </c>
+      <c r="C499" t="s">
+        <v>368</v>
+      </c>
+      <c r="D499"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="s">
+        <v>157</v>
+      </c>
+      <c r="B500" t="n">
+        <v>1</v>
+      </c>
+      <c r="C500" t="s">
+        <v>385</v>
+      </c>
+      <c r="D500"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="s">
+        <v>157</v>
+      </c>
+      <c r="B501" t="n">
+        <v>1</v>
+      </c>
+      <c r="C501" t="s">
+        <v>342</v>
+      </c>
+      <c r="D501"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="s">
+        <v>157</v>
+      </c>
+      <c r="B502" t="n">
+        <v>1</v>
+      </c>
+      <c r="C502" t="s">
+        <v>441</v>
+      </c>
+      <c r="D502"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="s">
+        <v>158</v>
+      </c>
+      <c r="B503" t="n">
+        <v>1</v>
+      </c>
+      <c r="C503" t="s">
+        <v>317</v>
+      </c>
+      <c r="D503"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="s">
+        <v>158</v>
+      </c>
+      <c r="B504" t="n">
+        <v>1</v>
+      </c>
+      <c r="C504" t="s">
+        <v>312</v>
+      </c>
+      <c r="D504"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="s">
+        <v>159</v>
+      </c>
+      <c r="B505" t="n">
+        <v>1</v>
+      </c>
+      <c r="C505" t="s">
+        <v>312</v>
+      </c>
+      <c r="D505"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="s">
+        <v>160</v>
+      </c>
+      <c r="B506" t="n">
+        <v>1</v>
+      </c>
+      <c r="C506" t="s">
+        <v>333</v>
+      </c>
+      <c r="D506" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="s">
+        <v>160</v>
+      </c>
+      <c r="B507" t="n">
+        <v>1</v>
+      </c>
+      <c r="C507" t="s">
+        <v>317</v>
+      </c>
+      <c r="D507"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="s">
+        <v>161</v>
+      </c>
+      <c r="B508" t="n">
+        <v>1</v>
+      </c>
+      <c r="C508" t="s">
+        <v>317</v>
+      </c>
+      <c r="D508"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="s">
+        <v>161</v>
+      </c>
+      <c r="B509" t="n">
+        <v>1</v>
+      </c>
+      <c r="C509" t="s">
+        <v>283</v>
+      </c>
+      <c r="D509" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="s">
+        <v>163</v>
+      </c>
+      <c r="B510" t="n">
+        <v>1</v>
+      </c>
+      <c r="C510" t="s">
+        <v>317</v>
+      </c>
+      <c r="D510"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="s">
+        <v>163</v>
+      </c>
+      <c r="B511" t="n">
+        <v>1</v>
+      </c>
+      <c r="C511" t="s">
+        <v>442</v>
+      </c>
+      <c r="D511"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="s">
+        <v>163</v>
+      </c>
+      <c r="B512" t="n">
+        <v>1</v>
+      </c>
+      <c r="C512" t="s">
+        <v>312</v>
+      </c>
+      <c r="D512"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="s">
+        <v>164</v>
+      </c>
+      <c r="B513" t="n">
+        <v>1</v>
+      </c>
+      <c r="C513" t="s">
+        <v>442</v>
+      </c>
+      <c r="D513"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="s">
+        <v>164</v>
+      </c>
+      <c r="B514" t="n">
+        <v>1</v>
+      </c>
+      <c r="C514" t="s">
+        <v>317</v>
+      </c>
+      <c r="D514"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="s">
+        <v>164</v>
+      </c>
+      <c r="B515" t="n">
+        <v>1</v>
+      </c>
+      <c r="C515" t="s">
+        <v>342</v>
+      </c>
+      <c r="D515"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="s">
+        <v>164</v>
+      </c>
+      <c r="B516" t="n">
+        <v>1</v>
+      </c>
+      <c r="C516" t="s">
+        <v>348</v>
+      </c>
+      <c r="D516"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="s">
+        <v>164</v>
+      </c>
+      <c r="B517" t="n">
+        <v>1</v>
+      </c>
+      <c r="C517" t="s">
+        <v>312</v>
+      </c>
+      <c r="D517"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="s">
+        <v>164</v>
+      </c>
+      <c r="B518" t="n">
+        <v>1</v>
+      </c>
+      <c r="C518" t="s">
+        <v>320</v>
+      </c>
+      <c r="D518"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="s">
+        <v>164</v>
+      </c>
+      <c r="B519" t="n">
+        <v>1</v>
+      </c>
+      <c r="C519" t="s">
+        <v>330</v>
+      </c>
+      <c r="D519"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="s">
+        <v>165</v>
+      </c>
+      <c r="B520" t="n">
+        <v>1</v>
+      </c>
+      <c r="C520" t="s">
+        <v>442</v>
+      </c>
+      <c r="D520"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="s">
+        <v>165</v>
+      </c>
+      <c r="B521" t="n">
+        <v>1</v>
+      </c>
+      <c r="C521" t="s">
+        <v>330</v>
+      </c>
+      <c r="D521"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="s">
+        <v>165</v>
+      </c>
+      <c r="B522" t="n">
+        <v>1</v>
+      </c>
+      <c r="C522" t="s">
+        <v>317</v>
+      </c>
+      <c r="D522"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="s">
+        <v>166</v>
+      </c>
+      <c r="B523" t="n">
+        <v>1</v>
+      </c>
+      <c r="C523" t="s">
+        <v>442</v>
+      </c>
+      <c r="D523"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="s">
+        <v>166</v>
+      </c>
+      <c r="B524" t="n">
+        <v>1</v>
+      </c>
+      <c r="C524" t="s">
+        <v>317</v>
+      </c>
+      <c r="D524"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="s">
+        <v>166</v>
+      </c>
+      <c r="B525" t="n">
+        <v>1</v>
+      </c>
+      <c r="C525" t="s">
+        <v>330</v>
+      </c>
+      <c r="D525"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="s">
+        <v>166</v>
+      </c>
+      <c r="B526" t="n">
+        <v>1</v>
+      </c>
+      <c r="C526" t="s">
+        <v>342</v>
+      </c>
+      <c r="D526"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="s">
+        <v>166</v>
+      </c>
+      <c r="B527" t="n">
+        <v>1</v>
+      </c>
+      <c r="C527" t="s">
+        <v>348</v>
+      </c>
+      <c r="D527"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="s">
+        <v>166</v>
+      </c>
+      <c r="B528" t="n">
+        <v>1</v>
+      </c>
+      <c r="C528" t="s">
+        <v>312</v>
+      </c>
+      <c r="D528"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="s">
+        <v>167</v>
+      </c>
+      <c r="B529" t="n">
+        <v>1</v>
+      </c>
+      <c r="C529" t="s">
+        <v>317</v>
+      </c>
+      <c r="D529"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="s">
+        <v>170</v>
+      </c>
+      <c r="B530" t="n">
+        <v>1</v>
+      </c>
+      <c r="C530" t="s">
+        <v>413</v>
+      </c>
+      <c r="D530"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="s">
+        <v>170</v>
+      </c>
+      <c r="B531" t="n">
+        <v>1</v>
+      </c>
+      <c r="C531" t="s">
+        <v>317</v>
+      </c>
+      <c r="D531"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="s">
+        <v>170</v>
+      </c>
+      <c r="B532" t="n">
+        <v>1</v>
+      </c>
+      <c r="C532" t="s">
+        <v>320</v>
+      </c>
+      <c r="D532"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="s">
+        <v>170</v>
+      </c>
+      <c r="B533" t="n">
+        <v>1</v>
+      </c>
+      <c r="C533" t="s">
+        <v>318</v>
+      </c>
+      <c r="D533"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="s">
+        <v>170</v>
+      </c>
+      <c r="B534" t="n">
+        <v>1</v>
+      </c>
+      <c r="C534" t="s">
+        <v>443</v>
+      </c>
+      <c r="D534"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="s">
+        <v>171</v>
+      </c>
+      <c r="B535" t="n">
+        <v>1</v>
+      </c>
+      <c r="C535" t="s">
+        <v>317</v>
+      </c>
+      <c r="D535"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="s">
+        <v>171</v>
+      </c>
+      <c r="B536" t="n">
+        <v>1</v>
+      </c>
+      <c r="C536" t="s">
+        <v>357</v>
+      </c>
+      <c r="D536" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="s">
+        <v>171</v>
+      </c>
+      <c r="B537" t="n">
+        <v>1</v>
+      </c>
+      <c r="C537" t="s">
+        <v>283</v>
+      </c>
+      <c r="D537" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="s">
+        <v>171</v>
+      </c>
+      <c r="B538" t="n">
+        <v>1</v>
+      </c>
+      <c r="C538" t="s">
+        <v>291</v>
+      </c>
+      <c r="D538"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="s">
+        <v>172</v>
+      </c>
+      <c r="B539" t="n">
+        <v>1</v>
+      </c>
+      <c r="C539" t="s">
+        <v>376</v>
+      </c>
+      <c r="D539" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="s">
+        <v>175</v>
+      </c>
+      <c r="B540" t="n">
+        <v>1</v>
+      </c>
+      <c r="C540" t="s">
+        <v>348</v>
+      </c>
+      <c r="D540"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="s">
+        <v>175</v>
+      </c>
+      <c r="B541" t="n">
+        <v>1</v>
+      </c>
+      <c r="C541" t="s">
+        <v>317</v>
+      </c>
+      <c r="D541"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="s">
+        <v>176</v>
+      </c>
+      <c r="B542" t="n">
+        <v>1</v>
+      </c>
+      <c r="C542" t="s">
+        <v>390</v>
+      </c>
+      <c r="D542"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="s">
+        <v>176</v>
+      </c>
+      <c r="B543" t="n">
+        <v>1</v>
+      </c>
+      <c r="C543" t="s">
+        <v>444</v>
+      </c>
+      <c r="D543"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="s">
+        <v>177</v>
+      </c>
+      <c r="B544" t="n">
+        <v>1</v>
+      </c>
+      <c r="C544" t="s">
+        <v>390</v>
+      </c>
+      <c r="D544"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="s">
+        <v>178</v>
+      </c>
+      <c r="B545" t="n">
+        <v>1</v>
+      </c>
+      <c r="C545" t="s">
+        <v>320</v>
+      </c>
+      <c r="D545"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="s">
+        <v>178</v>
+      </c>
+      <c r="B546" t="n">
+        <v>1</v>
+      </c>
+      <c r="C546" t="s">
+        <v>390</v>
+      </c>
+      <c r="D546"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="s">
+        <v>178</v>
+      </c>
+      <c r="B547" t="n">
+        <v>1</v>
+      </c>
+      <c r="C547" t="s">
+        <v>317</v>
+      </c>
+      <c r="D547"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="s">
+        <v>179</v>
+      </c>
+      <c r="B548" t="n">
+        <v>1</v>
+      </c>
+      <c r="C548" t="s">
+        <v>317</v>
+      </c>
+      <c r="D548"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="s">
+        <v>179</v>
+      </c>
+      <c r="B549" t="n">
+        <v>1</v>
+      </c>
+      <c r="C549" t="s">
+        <v>413</v>
+      </c>
+      <c r="D549"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="s">
+        <v>179</v>
+      </c>
+      <c r="B550" t="n">
+        <v>1</v>
+      </c>
+      <c r="C550" t="s">
+        <v>445</v>
+      </c>
+      <c r="D550"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="s">
+        <v>180</v>
+      </c>
+      <c r="B551" t="n">
+        <v>1</v>
+      </c>
+      <c r="C551" t="s">
+        <v>348</v>
+      </c>
+      <c r="D551"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="s">
+        <v>180</v>
+      </c>
+      <c r="B552" t="n">
+        <v>1</v>
+      </c>
+      <c r="C552" t="s">
+        <v>390</v>
+      </c>
+      <c r="D552"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="s">
+        <v>180</v>
+      </c>
+      <c r="B553" t="n">
+        <v>1</v>
+      </c>
+      <c r="C553" t="s">
+        <v>320</v>
+      </c>
+      <c r="D553"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="s">
+        <v>180</v>
+      </c>
+      <c r="B554" t="n">
+        <v>1</v>
+      </c>
+      <c r="C554" t="s">
+        <v>446</v>
+      </c>
+      <c r="D554"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="s">
+        <v>181</v>
+      </c>
+      <c r="B555" t="n">
+        <v>1</v>
+      </c>
+      <c r="C555" t="s">
+        <v>320</v>
+      </c>
+      <c r="D555"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="s">
+        <v>181</v>
+      </c>
+      <c r="B556" t="n">
+        <v>1</v>
+      </c>
+      <c r="C556" t="s">
+        <v>413</v>
+      </c>
+      <c r="D556"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="s">
+        <v>182</v>
+      </c>
+      <c r="B557" t="n">
+        <v>1</v>
+      </c>
+      <c r="C557" t="s">
+        <v>320</v>
+      </c>
+      <c r="D557"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="s">
+        <v>183</v>
+      </c>
+      <c r="B558" t="n">
+        <v>1</v>
+      </c>
+      <c r="C558" t="s">
+        <v>447</v>
+      </c>
+      <c r="D558"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="s">
+        <v>184</v>
+      </c>
+      <c r="B559" t="n">
+        <v>1</v>
+      </c>
+      <c r="C559" t="s">
+        <v>448</v>
+      </c>
+      <c r="D559"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="s">
+        <v>185</v>
+      </c>
+      <c r="B560" t="n">
+        <v>1</v>
+      </c>
+      <c r="C560" t="s">
+        <v>405</v>
+      </c>
+      <c r="D560"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="s">
+        <v>187</v>
+      </c>
+      <c r="B561" t="n">
+        <v>1</v>
+      </c>
+      <c r="C561" t="s">
+        <v>449</v>
+      </c>
+      <c r="D561"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="s">
+        <v>187</v>
+      </c>
+      <c r="B562" t="n">
+        <v>1</v>
+      </c>
+      <c r="C562" t="s">
+        <v>317</v>
+      </c>
+      <c r="D562"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="s">
+        <v>188</v>
+      </c>
+      <c r="B563" t="n">
+        <v>1</v>
+      </c>
+      <c r="C563" t="s">
+        <v>450</v>
+      </c>
+      <c r="D563" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="s">
+        <v>189</v>
+      </c>
+      <c r="B564" t="n">
+        <v>1</v>
+      </c>
+      <c r="C564" t="s">
+        <v>320</v>
+      </c>
+      <c r="D564"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="s">
+        <v>189</v>
+      </c>
+      <c r="B565" t="n">
+        <v>1</v>
+      </c>
+      <c r="C565" t="s">
+        <v>452</v>
+      </c>
+      <c r="D565"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="s">
+        <v>189</v>
+      </c>
+      <c r="B566" t="n">
+        <v>1</v>
+      </c>
+      <c r="C566" t="s">
+        <v>449</v>
+      </c>
+      <c r="D566"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="s">
+        <v>189</v>
+      </c>
+      <c r="B567" t="n">
+        <v>1</v>
+      </c>
+      <c r="C567" t="s">
+        <v>413</v>
+      </c>
+      <c r="D567"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="s">
+        <v>189</v>
+      </c>
+      <c r="B568" t="n">
+        <v>1</v>
+      </c>
+      <c r="C568" t="s">
+        <v>450</v>
+      </c>
+      <c r="D568" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="s">
+        <v>190</v>
+      </c>
+      <c r="B569" t="n">
+        <v>1</v>
+      </c>
+      <c r="C569" t="s">
+        <v>450</v>
+      </c>
+      <c r="D569" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="s">
+        <v>190</v>
+      </c>
+      <c r="B570" t="n">
+        <v>1</v>
+      </c>
+      <c r="C570" t="s">
+        <v>452</v>
+      </c>
+      <c r="D570"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="s">
+        <v>190</v>
+      </c>
+      <c r="B571" t="n">
+        <v>1</v>
+      </c>
+      <c r="C571" t="s">
+        <v>320</v>
+      </c>
+      <c r="D571"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="s">
+        <v>190</v>
+      </c>
+      <c r="B572" t="n">
+        <v>1</v>
+      </c>
+      <c r="C572" t="s">
+        <v>443</v>
+      </c>
+      <c r="D572"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="s">
+        <v>191</v>
+      </c>
+      <c r="B573" t="n">
+        <v>1</v>
+      </c>
+      <c r="C573" t="s">
+        <v>320</v>
+      </c>
+      <c r="D573"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="s">
+        <v>193</v>
+      </c>
+      <c r="B574" t="n">
+        <v>1</v>
+      </c>
+      <c r="C574" t="s">
+        <v>453</v>
+      </c>
+      <c r="D574"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="s">
+        <v>194</v>
+      </c>
+      <c r="B575" t="n">
+        <v>1</v>
+      </c>
+      <c r="C575" t="s">
+        <v>454</v>
+      </c>
+      <c r="D575"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="s">
+        <v>195</v>
+      </c>
+      <c r="B576" t="n">
+        <v>1</v>
+      </c>
+      <c r="C576" t="s">
+        <v>349</v>
+      </c>
+      <c r="D576"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="s">
+        <v>196</v>
+      </c>
+      <c r="B577" t="n">
+        <v>1</v>
+      </c>
+      <c r="C577" t="s">
+        <v>455</v>
+      </c>
+      <c r="D577"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="s">
+        <v>196</v>
+      </c>
+      <c r="B578" t="n">
+        <v>1</v>
+      </c>
+      <c r="C578" t="s">
+        <v>317</v>
+      </c>
+      <c r="D578"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="s">
+        <v>196</v>
+      </c>
+      <c r="B579" t="n">
+        <v>1</v>
+      </c>
+      <c r="C579" t="s">
+        <v>456</v>
+      </c>
+      <c r="D579"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="s">
+        <v>196</v>
+      </c>
+      <c r="B580" t="n">
+        <v>1</v>
+      </c>
+      <c r="C580" t="s">
+        <v>346</v>
+      </c>
+      <c r="D580"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="s">
+        <v>196</v>
+      </c>
+      <c r="B581" t="n">
+        <v>1</v>
+      </c>
+      <c r="C581" t="s">
+        <v>293</v>
+      </c>
+      <c r="D581" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="s">
+        <v>196</v>
+      </c>
+      <c r="B582" t="n">
+        <v>1</v>
+      </c>
+      <c r="C582" t="s">
+        <v>342</v>
+      </c>
+      <c r="D582"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="s">
+        <v>198</v>
+      </c>
+      <c r="B583" t="n">
+        <v>1</v>
+      </c>
+      <c r="C583" t="s">
+        <v>317</v>
+      </c>
+      <c r="D583"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="s">
+        <v>198</v>
+      </c>
+      <c r="B584" t="n">
+        <v>1</v>
+      </c>
+      <c r="C584" t="s">
+        <v>348</v>
+      </c>
+      <c r="D584"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="s">
+        <v>198</v>
+      </c>
+      <c r="B585" t="n">
+        <v>1</v>
+      </c>
+      <c r="C585" t="s">
+        <v>457</v>
+      </c>
+      <c r="D585"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="s">
+        <v>198</v>
+      </c>
+      <c r="B586" t="n">
+        <v>1</v>
+      </c>
+      <c r="C586" t="s">
+        <v>320</v>
+      </c>
+      <c r="D586"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="s">
+        <v>200</v>
+      </c>
+      <c r="B587" t="n">
+        <v>1</v>
+      </c>
+      <c r="C587" t="s">
+        <v>458</v>
+      </c>
+      <c r="D587"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="s">
+        <v>200</v>
+      </c>
+      <c r="B588" t="n">
+        <v>1</v>
+      </c>
+      <c r="C588" t="s">
+        <v>459</v>
+      </c>
+      <c r="D588"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="s">
+        <v>200</v>
+      </c>
+      <c r="B589" t="n">
+        <v>1</v>
+      </c>
+      <c r="C589" t="s">
+        <v>460</v>
+      </c>
+      <c r="D589"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="s">
+        <v>200</v>
+      </c>
+      <c r="B590" t="n">
+        <v>1</v>
+      </c>
+      <c r="C590" t="s">
+        <v>461</v>
+      </c>
+      <c r="D590"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="s">
+        <v>203</v>
+      </c>
+      <c r="B591" t="n">
+        <v>1</v>
+      </c>
+      <c r="C591" t="s">
+        <v>376</v>
+      </c>
+      <c r="D591" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="s">
+        <v>205</v>
+      </c>
+      <c r="B592" t="n">
+        <v>1</v>
+      </c>
+      <c r="C592" t="s">
+        <v>462</v>
+      </c>
+      <c r="D592"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="s">
+        <v>207</v>
+      </c>
+      <c r="B593" t="n">
+        <v>1</v>
+      </c>
+      <c r="C593" t="s">
+        <v>463</v>
+      </c>
+      <c r="D593"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="s">
+        <v>207</v>
+      </c>
+      <c r="B594" t="n">
+        <v>1</v>
+      </c>
+      <c r="C594" t="s">
+        <v>320</v>
+      </c>
+      <c r="D594"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="s">
+        <v>211</v>
+      </c>
+      <c r="B595" t="n">
+        <v>1</v>
+      </c>
+      <c r="C595" t="s">
+        <v>317</v>
+      </c>
+      <c r="D595"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="s">
+        <v>212</v>
+      </c>
+      <c r="B596" t="n">
+        <v>1</v>
+      </c>
+      <c r="C596" t="s">
+        <v>464</v>
+      </c>
+      <c r="D596"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="s">
+        <v>212</v>
+      </c>
+      <c r="B597" t="n">
+        <v>1</v>
+      </c>
+      <c r="C597" t="s">
+        <v>465</v>
+      </c>
+      <c r="D597" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="s">
+        <v>214</v>
+      </c>
+      <c r="B598" t="n">
+        <v>1</v>
+      </c>
+      <c r="C598" t="s">
+        <v>342</v>
+      </c>
+      <c r="D598"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="s">
+        <v>214</v>
+      </c>
+      <c r="B599" t="n">
+        <v>1</v>
+      </c>
+      <c r="C599" t="s">
+        <v>317</v>
+      </c>
+      <c r="D599"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="s">
+        <v>214</v>
+      </c>
+      <c r="B600" t="n">
+        <v>2</v>
+      </c>
+      <c r="C600" t="s">
+        <v>317</v>
+      </c>
+      <c r="D600"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="s">
+        <v>214</v>
+      </c>
+      <c r="B601" t="n">
+        <v>2</v>
+      </c>
+      <c r="C601" t="s">
+        <v>467</v>
+      </c>
+      <c r="D601"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="s">
+        <v>214</v>
+      </c>
+      <c r="B602" t="n">
+        <v>2</v>
+      </c>
+      <c r="C602" t="s">
+        <v>342</v>
+      </c>
+      <c r="D602"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="s">
+        <v>214</v>
+      </c>
+      <c r="B603" t="n">
+        <v>2</v>
+      </c>
+      <c r="C603" t="s">
+        <v>320</v>
+      </c>
+      <c r="D603"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="s">
+        <v>216</v>
+      </c>
+      <c r="B604" t="n">
+        <v>1</v>
+      </c>
+      <c r="C604" t="s">
+        <v>280</v>
+      </c>
+      <c r="D604"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="s">
+        <v>216</v>
+      </c>
+      <c r="B605" t="n">
+        <v>1</v>
+      </c>
+      <c r="C605" t="s">
+        <v>285</v>
+      </c>
+      <c r="D605"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="s">
+        <v>216</v>
+      </c>
+      <c r="B606" t="n">
+        <v>1</v>
+      </c>
+      <c r="C606" t="s">
+        <v>287</v>
+      </c>
+      <c r="D606"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="s">
+        <v>216</v>
+      </c>
+      <c r="B607" t="n">
+        <v>1</v>
+      </c>
+      <c r="C607" t="s">
+        <v>467</v>
+      </c>
+      <c r="D607"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="s">
+        <v>216</v>
+      </c>
+      <c r="B608" t="n">
+        <v>1</v>
+      </c>
+      <c r="C608" t="s">
+        <v>347</v>
+      </c>
+      <c r="D608"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="s">
+        <v>216</v>
+      </c>
+      <c r="B609" t="n">
+        <v>1</v>
+      </c>
+      <c r="C609" t="s">
+        <v>468</v>
+      </c>
+      <c r="D609" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="s">
+        <v>216</v>
+      </c>
+      <c r="B610" t="n">
+        <v>1</v>
+      </c>
+      <c r="C610" t="s">
+        <v>425</v>
+      </c>
+      <c r="D610"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="s">
+        <v>217</v>
+      </c>
+      <c r="B611" t="n">
+        <v>1</v>
+      </c>
+      <c r="C611" t="s">
+        <v>307</v>
+      </c>
+      <c r="D611"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="s">
+        <v>217</v>
+      </c>
+      <c r="B612" t="n">
+        <v>1</v>
+      </c>
+      <c r="C612" t="s">
+        <v>291</v>
+      </c>
+      <c r="D612"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="s">
+        <v>218</v>
+      </c>
+      <c r="B613" t="n">
+        <v>1</v>
+      </c>
+      <c r="C613" t="s">
+        <v>354</v>
+      </c>
+      <c r="D613" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="s">
+        <v>218</v>
+      </c>
+      <c r="B614" t="n">
+        <v>1</v>
+      </c>
+      <c r="C614" t="s">
+        <v>375</v>
+      </c>
+      <c r="D614"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="s">
+        <v>218</v>
+      </c>
+      <c r="B615" t="n">
+        <v>1</v>
+      </c>
+      <c r="C615" t="s">
+        <v>318</v>
+      </c>
+      <c r="D615"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="s">
+        <v>218</v>
+      </c>
+      <c r="B616" t="n">
+        <v>1</v>
+      </c>
+      <c r="C616" t="s">
+        <v>317</v>
+      </c>
+      <c r="D616"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="s">
+        <v>218</v>
+      </c>
+      <c r="B617" t="n">
+        <v>1</v>
+      </c>
+      <c r="C617" t="s">
+        <v>424</v>
+      </c>
+      <c r="D617"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="s">
+        <v>218</v>
+      </c>
+      <c r="B618" t="n">
+        <v>1</v>
+      </c>
+      <c r="C618" t="s">
+        <v>390</v>
+      </c>
+      <c r="D618"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="s">
+        <v>218</v>
+      </c>
+      <c r="B619" t="n">
+        <v>1</v>
+      </c>
+      <c r="C619" t="s">
+        <v>287</v>
+      </c>
+      <c r="D619"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="s">
+        <v>219</v>
+      </c>
+      <c r="B620" t="n">
+        <v>1</v>
+      </c>
+      <c r="C620" t="s">
+        <v>333</v>
+      </c>
+      <c r="D620" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="621">
+      <c r="A621" t="s">
+        <v>219</v>
+      </c>
+      <c r="B621" t="n">
+        <v>1</v>
+      </c>
+      <c r="C621" t="s">
+        <v>414</v>
+      </c>
+      <c r="D621"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="s">
+        <v>219</v>
+      </c>
+      <c r="B622" t="n">
+        <v>1</v>
+      </c>
+      <c r="C622" t="s">
+        <v>285</v>
+      </c>
+      <c r="D622"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="s">
+        <v>219</v>
+      </c>
+      <c r="B623" t="n">
+        <v>1</v>
+      </c>
+      <c r="C623" t="s">
+        <v>324</v>
+      </c>
+      <c r="D623"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="s">
+        <v>219</v>
+      </c>
+      <c r="B624" t="n">
+        <v>1</v>
+      </c>
+      <c r="C624" t="s">
+        <v>470</v>
+      </c>
+      <c r="D624"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="s">
+        <v>219</v>
+      </c>
+      <c r="B625" t="n">
+        <v>1</v>
+      </c>
+      <c r="C625" t="s">
+        <v>471</v>
+      </c>
+      <c r="D625"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="s">
+        <v>219</v>
+      </c>
+      <c r="B626" t="n">
+        <v>1</v>
+      </c>
+      <c r="C626" t="s">
+        <v>368</v>
+      </c>
+      <c r="D626"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="s">
+        <v>219</v>
+      </c>
+      <c r="B627" t="n">
+        <v>1</v>
+      </c>
+      <c r="C627" t="s">
+        <v>472</v>
+      </c>
+      <c r="D627"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="s">
+        <v>219</v>
+      </c>
+      <c r="B628" t="n">
+        <v>1</v>
+      </c>
+      <c r="C628" t="s">
+        <v>473</v>
+      </c>
+      <c r="D628"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="s">
+        <v>220</v>
+      </c>
+      <c r="B629" t="n">
+        <v>1</v>
+      </c>
+      <c r="C629" t="s">
+        <v>320</v>
+      </c>
+      <c r="D629"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="s">
+        <v>220</v>
+      </c>
+      <c r="B630" t="n">
+        <v>1</v>
+      </c>
+      <c r="C630" t="s">
+        <v>317</v>
+      </c>
+      <c r="D630"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="s">
+        <v>220</v>
+      </c>
+      <c r="B631" t="n">
+        <v>1</v>
+      </c>
+      <c r="C631" t="s">
+        <v>368</v>
+      </c>
+      <c r="D631"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="s">
+        <v>220</v>
+      </c>
+      <c r="B632" t="n">
+        <v>1</v>
+      </c>
+      <c r="C632" t="s">
+        <v>333</v>
+      </c>
+      <c r="D632" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="633">
+      <c r="A633" t="s">
+        <v>220</v>
+      </c>
+      <c r="B633" t="n">
+        <v>1</v>
+      </c>
+      <c r="C633" t="s">
+        <v>450</v>
+      </c>
+      <c r="D633" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="634">
+      <c r="A634" t="s">
+        <v>220</v>
+      </c>
+      <c r="B634" t="n">
+        <v>1</v>
+      </c>
+      <c r="C634" t="s">
+        <v>420</v>
+      </c>
+      <c r="D634"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="s">
+        <v>220</v>
+      </c>
+      <c r="B635" t="n">
+        <v>1</v>
+      </c>
+      <c r="C635" t="s">
+        <v>474</v>
+      </c>
+      <c r="D635"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="s">
+        <v>221</v>
+      </c>
+      <c r="B636" t="n">
+        <v>1</v>
+      </c>
+      <c r="C636" t="s">
+        <v>458</v>
+      </c>
+      <c r="D636"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="s">
+        <v>222</v>
+      </c>
+      <c r="B637" t="n">
+        <v>1</v>
+      </c>
+      <c r="C637" t="s">
+        <v>348</v>
+      </c>
+      <c r="D637"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="s">
+        <v>223</v>
+      </c>
+      <c r="B638" t="n">
+        <v>1</v>
+      </c>
+      <c r="C638" t="s">
+        <v>320</v>
+      </c>
+      <c r="D638"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="s">
+        <v>223</v>
+      </c>
+      <c r="B639" t="n">
+        <v>1</v>
+      </c>
+      <c r="C639" t="s">
+        <v>318</v>
+      </c>
+      <c r="D639"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="s">
+        <v>223</v>
+      </c>
+      <c r="B640" t="n">
+        <v>1</v>
+      </c>
+      <c r="C640" t="s">
+        <v>314</v>
+      </c>
+      <c r="D640"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="s">
+        <v>223</v>
+      </c>
+      <c r="B641" t="n">
+        <v>1</v>
+      </c>
+      <c r="C641" t="s">
+        <v>475</v>
+      </c>
+      <c r="D641"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="s">
+        <v>223</v>
+      </c>
+      <c r="B642" t="n">
+        <v>1</v>
+      </c>
+      <c r="C642" t="s">
+        <v>457</v>
+      </c>
+      <c r="D642"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="s">
+        <v>223</v>
+      </c>
+      <c r="B643" t="n">
+        <v>1</v>
+      </c>
+      <c r="C643" t="s">
+        <v>476</v>
+      </c>
+      <c r="D643"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="s">
+        <v>225</v>
+      </c>
+      <c r="B644" t="n">
+        <v>1</v>
+      </c>
+      <c r="C644" t="s">
+        <v>376</v>
+      </c>
+      <c r="D644" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="645">
+      <c r="A645" t="s">
+        <v>225</v>
+      </c>
+      <c r="B645" t="n">
+        <v>1</v>
+      </c>
+      <c r="C645" t="s">
+        <v>460</v>
+      </c>
+      <c r="D645"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="s">
+        <v>226</v>
+      </c>
+      <c r="B646" t="n">
+        <v>1</v>
+      </c>
+      <c r="C646" t="s">
+        <v>376</v>
+      </c>
+      <c r="D646" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="647">
+      <c r="A647" t="s">
+        <v>226</v>
+      </c>
+      <c r="B647" t="n">
+        <v>1</v>
+      </c>
+      <c r="C647" t="s">
+        <v>477</v>
+      </c>
+      <c r="D647"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="s">
+        <v>226</v>
+      </c>
+      <c r="B648" t="n">
+        <v>1</v>
+      </c>
+      <c r="C648" t="s">
+        <v>460</v>
+      </c>
+      <c r="D648"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="s">
+        <v>227</v>
+      </c>
+      <c r="B649" t="n">
+        <v>1</v>
+      </c>
+      <c r="C649" t="s">
+        <v>318</v>
+      </c>
+      <c r="D649"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="s">
+        <v>228</v>
+      </c>
+      <c r="B650" t="n">
+        <v>1</v>
+      </c>
+      <c r="C650" t="s">
+        <v>376</v>
+      </c>
+      <c r="D650" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" t="s">
+        <v>228</v>
+      </c>
+      <c r="B651" t="n">
+        <v>1</v>
+      </c>
+      <c r="C651" t="s">
+        <v>478</v>
+      </c>
+      <c r="D651"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>